--- a/粽子销售数据.xlsx
+++ b/粽子销售数据.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t>序号</t>
   </si>
@@ -271,6 +271,10 @@
 VS 
 26年收入目标
 完成度%</t>
+  </si>
+  <si>
+    <t>香港喜來登</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -284,7 +288,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,6 +404,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri Light"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -475,7 +484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -575,6 +584,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3"/>
@@ -591,7 +630,7 @@
     <xf numFmtId="9" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -821,6 +860,66 @@
     <xf numFmtId="179" fontId="14" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -860,71 +959,20 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1234,47 +1282,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="81" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81" t="s">
+      <c r="E2" s="101"/>
+      <c r="F2" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81" t="s">
+      <c r="G2" s="101"/>
+      <c r="H2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81" t="s">
+      <c r="I2" s="101"/>
+      <c r="J2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="81"/>
+      <c r="K2" s="101"/>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="83"/>
+      <c r="A3" s="103"/>
       <c r="B3" s="11">
         <v>2025</v>
       </c>
@@ -1324,7 +1372,7 @@
       </c>
       <c r="E4" s="7">
         <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(F1),0)</f>
-        <v>0</v>
+        <v>132578</v>
       </c>
       <c r="F4" s="7">
         <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(G1),0)</f>
@@ -1369,7 +1417,7 @@
       </c>
       <c r="E5" s="7">
         <f>VLOOKUP($A5,原表!$A$4:$O$25,COLUMN(F2),0)</f>
-        <v>0</v>
+        <v>119613.62</v>
       </c>
       <c r="F5" s="7">
         <f>VLOOKUP($A5,原表!$A$4:$O$25,COLUMN(G2),0)</f>
@@ -1414,7 +1462,7 @@
       </c>
       <c r="E6" s="7">
         <f>VLOOKUP($A6,原表!$A$4:$O$25,COLUMN(F3),0)</f>
-        <v>0</v>
+        <v>820850</v>
       </c>
       <c r="F6" s="7">
         <f>VLOOKUP($A6,原表!$A$4:$O$25,COLUMN(G3),0)</f>
@@ -1459,7 +1507,7 @@
       </c>
       <c r="E7" s="7">
         <f>VLOOKUP($A7,原表!$A$4:$O$25,COLUMN(F4),0)</f>
-        <v>0</v>
+        <v>279964</v>
       </c>
       <c r="F7" s="7">
         <f>VLOOKUP($A7,原表!$A$4:$O$25,COLUMN(G4),0)</f>
@@ -1504,7 +1552,7 @@
       </c>
       <c r="E8" s="7">
         <f>VLOOKUP($A8,原表!$A$4:$O$25,COLUMN(F5),0)</f>
-        <v>0</v>
+        <v>391500</v>
       </c>
       <c r="F8" s="7">
         <f>VLOOKUP($A8,原表!$A$4:$O$25,COLUMN(G5),0)</f>
@@ -1549,7 +1597,7 @@
       </c>
       <c r="E9" s="7">
         <f>VLOOKUP($A9,原表!$A$4:$O$25,COLUMN(F6),0)</f>
-        <v>0</v>
+        <v>289147</v>
       </c>
       <c r="F9" s="7">
         <f>VLOOKUP($A9,原表!$A$4:$O$25,COLUMN(G6),0)</f>
@@ -1594,7 +1642,7 @@
       </c>
       <c r="E10" s="7">
         <f>VLOOKUP($A10,原表!$A$4:$O$25,COLUMN(F7),0)</f>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="F10" s="7">
         <f>VLOOKUP($A10,原表!$A$4:$O$25,COLUMN(G7),0)</f>
@@ -1639,7 +1687,7 @@
       </c>
       <c r="E11" s="7">
         <f>VLOOKUP($A11,原表!$A$4:$O$25,COLUMN(F8),0)</f>
-        <v>0</v>
+        <v>5082</v>
       </c>
       <c r="F11" s="7">
         <f>VLOOKUP($A11,原表!$A$4:$O$25,COLUMN(G8),0)</f>
@@ -1729,7 +1777,7 @@
       </c>
       <c r="E13" s="7">
         <f>VLOOKUP($A13,原表!$A$4:$O$25,COLUMN(F10),0)</f>
-        <v>0</v>
+        <v>29894</v>
       </c>
       <c r="F13" s="7">
         <f>VLOOKUP($A13,原表!$A$4:$O$25,COLUMN(G10),0)</f>
@@ -1774,7 +1822,7 @@
       </c>
       <c r="E14" s="7">
         <f>VLOOKUP($A14,原表!$A$4:$O$25,COLUMN(F11),0)</f>
-        <v>0</v>
+        <v>7240</v>
       </c>
       <c r="F14" s="7">
         <f>VLOOKUP($A14,原表!$A$4:$O$25,COLUMN(G11),0)</f>
@@ -1819,7 +1867,7 @@
       </c>
       <c r="E15" s="7">
         <f>VLOOKUP($A15,原表!$A$4:$O$25,COLUMN(F12),0)</f>
-        <v>0</v>
+        <v>105021</v>
       </c>
       <c r="F15" s="7">
         <f>VLOOKUP($A15,原表!$A$4:$O$25,COLUMN(G12),0)</f>
@@ -1864,7 +1912,7 @@
       </c>
       <c r="E16" s="7">
         <f>VLOOKUP($A16,原表!$A$4:$O$25,COLUMN(F13),0)</f>
-        <v>0</v>
+        <v>27139</v>
       </c>
       <c r="F16" s="7">
         <f>VLOOKUP($A16,原表!$A$4:$O$25,COLUMN(G13),0)</f>
@@ -1909,7 +1957,7 @@
       </c>
       <c r="E17" s="7">
         <f>VLOOKUP($A17,原表!$A$4:$O$25,COLUMN(F14),0)</f>
-        <v>0</v>
+        <v>18146.2</v>
       </c>
       <c r="F17" s="7">
         <f>VLOOKUP($A17,原表!$A$4:$O$25,COLUMN(G14),0)</f>
@@ -1954,7 +2002,7 @@
       </c>
       <c r="E18" s="7">
         <f>VLOOKUP($A18,原表!$A$4:$O$25,COLUMN(F15),0)</f>
-        <v>0</v>
+        <v>48850</v>
       </c>
       <c r="F18" s="7">
         <f>VLOOKUP($A18,原表!$A$4:$O$25,COLUMN(G15),0)</f>
@@ -1999,7 +2047,7 @@
       </c>
       <c r="E19" s="7">
         <f>VLOOKUP($A19,原表!$A$4:$O$25,COLUMN(F16),0)</f>
-        <v>0</v>
+        <v>476520</v>
       </c>
       <c r="F19" s="7">
         <f>VLOOKUP($A19,原表!$A$4:$O$25,COLUMN(G16),0)</f>
@@ -2044,7 +2092,7 @@
       </c>
       <c r="E20" s="7">
         <f>VLOOKUP($A20,原表!$A$4:$O$25,COLUMN(F17),0)</f>
-        <v>0</v>
+        <v>37118</v>
       </c>
       <c r="F20" s="7">
         <f>VLOOKUP($A20,原表!$A$4:$O$25,COLUMN(G17),0)</f>
@@ -2134,7 +2182,7 @@
       </c>
       <c r="E22" s="7">
         <f>VLOOKUP($A22,原表!$A$4:$O$25,COLUMN(F19),0)</f>
-        <v>0</v>
+        <v>90033.11</v>
       </c>
       <c r="F22" s="7">
         <f>VLOOKUP($A22,原表!$A$4:$O$25,COLUMN(G19),0)</f>
@@ -2179,7 +2227,7 @@
       </c>
       <c r="E23" s="7">
         <f>VLOOKUP($A23,原表!$A$4:$O$25,COLUMN(F20),0)</f>
-        <v>0</v>
+        <v>166704</v>
       </c>
       <c r="F23" s="7">
         <f>VLOOKUP($A23,原表!$A$4:$O$25,COLUMN(G20),0)</f>
@@ -2224,7 +2272,7 @@
       </c>
       <c r="E24" s="7">
         <f>VLOOKUP($A24,原表!$A$4:$O$25,COLUMN(F21),0)</f>
-        <v>0</v>
+        <v>109815</v>
       </c>
       <c r="F24" s="7">
         <f>VLOOKUP($A24,原表!$A$4:$O$25,COLUMN(G21),0)</f>
@@ -2269,7 +2317,7 @@
       </c>
       <c r="E25" s="7">
         <f>VLOOKUP($A25,原表!$A$4:$O$25,COLUMN(F22),0)</f>
-        <v>0</v>
+        <v>15494</v>
       </c>
       <c r="F25" s="7">
         <f>VLOOKUP($A25,原表!$A$4:$O$25,COLUMN(G22),0)</f>
@@ -2314,7 +2362,7 @@
       </c>
       <c r="E26" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3195708.93</v>
       </c>
       <c r="F26" s="17">
         <f t="shared" si="0"/>
@@ -2384,31 +2432,31 @@
       <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="82" t="str">
-        <f>粽子销售PICKUP!B2:C2</f>
-        <v>节前38天</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="84" t="s">
+      <c r="B2" s="102" t="str">
+        <f>粽子销售PICKUP!D2</f>
+        <v>节前26天</v>
+      </c>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="104" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="83"/>
+      <c r="A3" s="103"/>
       <c r="B3" s="15" t="s">
         <v>43</v>
       </c>
@@ -2421,10 +2469,10 @@
       <c r="E3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="str">
@@ -2432,20 +2480,20 @@
         <v>香港喜來登</v>
       </c>
       <c r="B4" s="7">
-        <f>粽子销售PICKUP!B4</f>
-        <v>10261.700000000001</v>
+        <f>粽子销售PICKUP!D4</f>
+        <v>46531.88</v>
       </c>
       <c r="C4" s="7">
-        <f>粽子销售PICKUP!C4</f>
-        <v>94983</v>
+        <f>粽子销售PICKUP!E4</f>
+        <v>132578</v>
       </c>
       <c r="D4" s="7">
         <f>C4-B4</f>
-        <v>84721.3</v>
+        <v>86046.12</v>
       </c>
       <c r="E4" s="22">
         <f>C4/B4-1</f>
-        <v>8.2560686825769611</v>
+        <v>1.8491864072545532</v>
       </c>
       <c r="F4" s="7">
         <f>VLOOKUP(A4,原表!$A$4:$B$25,2,0)</f>
@@ -2453,7 +2501,7 @@
       </c>
       <c r="G4" s="74">
         <f>C4/F4</f>
-        <v>0.79152500000000003</v>
+        <v>1.1048166666666666</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP(A4,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2461,7 +2509,7 @@
       </c>
       <c r="I4" s="74">
         <f>C4/H4</f>
-        <v>0.91947803022235985</v>
+        <v>1.283414487759073</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2470,20 +2518,20 @@
         <v>佘山艾美</v>
       </c>
       <c r="B5" s="7">
-        <f>粽子销售PICKUP!B5</f>
-        <v>76390.25</v>
+        <f>粽子销售PICKUP!D5</f>
+        <v>104565.47</v>
       </c>
       <c r="C5" s="7">
-        <f>粽子销售PICKUP!C5</f>
-        <v>90335</v>
+        <f>粽子销售PICKUP!E5</f>
+        <v>119613.62</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" ref="D5:D26" si="0">C5-B5</f>
-        <v>13944.75</v>
+        <v>15048.149999999994</v>
       </c>
       <c r="E5" s="22">
         <f t="shared" ref="E5:E26" si="1">C5/B5-1</f>
-        <v>0.1825462019040387</v>
+        <v>0.14391127396070602</v>
       </c>
       <c r="F5" s="7">
         <f>VLOOKUP(A5,原表!$A$4:$B$25,2,0)</f>
@@ -2491,7 +2539,7 @@
       </c>
       <c r="G5" s="74">
         <f t="shared" ref="G5:G26" si="2">C5/F5</f>
-        <v>0.52111936682280735</v>
+        <v>0.69002019059925701</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2499,7 +2547,7 @@
       </c>
       <c r="I5" s="74">
         <f t="shared" ref="I5:I26" si="3">C5/H5</f>
-        <v>0.57323283456862728</v>
+        <v>0.7590242369581518</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2508,20 +2556,20 @@
         <v>长沙希尔顿</v>
       </c>
       <c r="B6" s="7">
-        <f>粽子销售PICKUP!B6</f>
-        <v>157000</v>
+        <f>粽子销售PICKUP!D6</f>
+        <v>297052</v>
       </c>
       <c r="C6" s="7">
-        <f>粽子销售PICKUP!C6</f>
-        <v>120850</v>
+        <f>粽子销售PICKUP!E6</f>
+        <v>820850</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-36150</v>
+        <v>523798</v>
       </c>
       <c r="E6" s="22">
         <f t="shared" si="1"/>
-        <v>-0.2302547770700637</v>
+        <v>1.7633209000444365</v>
       </c>
       <c r="F6" s="7">
         <f>VLOOKUP(A6,原表!$A$4:$B$25,2,0)</f>
@@ -2529,7 +2577,7 @@
       </c>
       <c r="G6" s="74">
         <f t="shared" si="2"/>
-        <v>9.6674663558571572E-2</v>
+        <v>0.65664375326481983</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2537,7 +2585,7 @@
       </c>
       <c r="I6" s="74">
         <f t="shared" si="3"/>
-        <v>0.1007833329302556</v>
+        <v>0.68455108676706911</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2546,20 +2594,20 @@
         <v>烟台希尔顿</v>
       </c>
       <c r="B7" s="7">
-        <f>粽子销售PICKUP!B7</f>
-        <v>28123.89</v>
+        <f>粽子销售PICKUP!D7</f>
+        <v>46657</v>
       </c>
       <c r="C7" s="7">
-        <f>粽子销售PICKUP!C7</f>
-        <v>53385</v>
+        <f>粽子销售PICKUP!E7</f>
+        <v>279964</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>25261.11</v>
+        <v>233307</v>
       </c>
       <c r="E7" s="22">
         <f t="shared" si="1"/>
-        <v>0.89820824928557186</v>
+        <v>5.0004715262447217</v>
       </c>
       <c r="F7" s="7">
         <f>VLOOKUP(A7,原表!$A$4:$B$25,2,0)</f>
@@ -2567,7 +2615,7 @@
       </c>
       <c r="G7" s="74">
         <f t="shared" si="2"/>
-        <v>8.8107144625439421E-2</v>
+        <v>0.46205542077206185</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2575,7 +2623,7 @@
       </c>
       <c r="I7" s="74">
         <f t="shared" si="3"/>
-        <v>9.6917907074271961E-2</v>
+        <v>0.50826121450110473</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2584,20 +2632,20 @@
         <v>武汉希尔顿</v>
       </c>
       <c r="B8" s="7">
-        <f>粽子销售PICKUP!B8</f>
-        <v>25694</v>
+        <f>粽子销售PICKUP!D8</f>
+        <v>111210</v>
       </c>
       <c r="C8" s="7">
-        <f>粽子销售PICKUP!C8</f>
-        <v>144015</v>
+        <f>粽子销售PICKUP!E8</f>
+        <v>391500</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>118321</v>
+        <v>280290</v>
       </c>
       <c r="E8" s="22">
         <f t="shared" si="1"/>
-        <v>4.6050050595469756</v>
+        <v>2.5203668734826006</v>
       </c>
       <c r="F8" s="7">
         <f>VLOOKUP(A8,原表!$A$4:$B$25,2,0)</f>
@@ -2605,7 +2653,7 @@
       </c>
       <c r="G8" s="74">
         <f t="shared" si="2"/>
-        <v>0.13235310335700737</v>
+        <v>0.35979752084344258</v>
       </c>
       <c r="H8" s="7">
         <f>VLOOKUP(A8,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2613,7 +2661,7 @@
       </c>
       <c r="I8" s="74">
         <f t="shared" si="3"/>
-        <v>0.13235310335700737</v>
+        <v>0.35979752084344258</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2622,20 +2670,20 @@
         <v>芜湖希尔顿逸林</v>
       </c>
       <c r="B9" s="7">
-        <f>粽子销售PICKUP!B9</f>
-        <v>15909</v>
+        <f>粽子销售PICKUP!D9</f>
+        <v>724172</v>
       </c>
       <c r="C9" s="7">
-        <f>粽子销售PICKUP!C9</f>
-        <v>265486</v>
+        <f>粽子销售PICKUP!E9</f>
+        <v>289147</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>249577</v>
+        <v>-435025</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="1"/>
-        <v>15.687786787353069</v>
+        <v>-0.60072054705235778</v>
       </c>
       <c r="F9" s="7">
         <f>VLOOKUP(A9,原表!$A$4:$B$25,2,0)</f>
@@ -2643,7 +2691,7 @@
       </c>
       <c r="G9" s="74">
         <f t="shared" si="2"/>
-        <v>0.28068895591946602</v>
+        <v>0.30570489418367014</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2651,7 +2699,7 @@
       </c>
       <c r="I9" s="74">
         <f t="shared" si="3"/>
-        <v>0.29188563412342566</v>
+        <v>0.31789945778642248</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2660,20 +2708,20 @@
         <v>泰州茂御</v>
       </c>
       <c r="B10" s="7">
-        <f>粽子销售PICKUP!B10</f>
-        <v>7436</v>
+        <f>粽子销售PICKUP!D10</f>
+        <v>76162</v>
       </c>
       <c r="C10" s="7">
-        <f>粽子销售PICKUP!C10</f>
-        <v>2900</v>
+        <f>粽子销售PICKUP!E10</f>
+        <v>25000</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-4536</v>
+        <v>-51162</v>
       </c>
       <c r="E10" s="22">
         <f t="shared" si="1"/>
-        <v>-0.61000537923614839</v>
+        <v>-0.67175231742863895</v>
       </c>
       <c r="F10" s="7">
         <f>VLOOKUP(A10,原表!$A$4:$B$25,2,0)</f>
@@ -2681,7 +2729,7 @@
       </c>
       <c r="G10" s="74">
         <f t="shared" si="2"/>
-        <v>1.0649118877215659E-2</v>
+        <v>9.1802748941514301E-2</v>
       </c>
       <c r="H10" s="7">
         <f>VLOOKUP(A10,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2689,7 +2737,7 @@
       </c>
       <c r="I10" s="74">
         <f t="shared" si="3"/>
-        <v>1.1714047971046105E-2</v>
+        <v>0.10098317216419056</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2698,20 +2746,20 @@
         <v>松江睿选</v>
       </c>
       <c r="B11" s="7">
-        <f>粽子销售PICKUP!B11</f>
-        <v>512</v>
+        <f>粽子销售PICKUP!D11</f>
+        <v>2688</v>
       </c>
       <c r="C11" s="7">
-        <f>粽子销售PICKUP!C11</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!E11</f>
+        <v>5082</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-512</v>
+        <v>2394</v>
       </c>
       <c r="E11" s="22">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.890625</v>
       </c>
       <c r="F11" s="7">
         <f>VLOOKUP(A11,原表!$A$4:$B$25,2,0)</f>
@@ -2719,7 +2767,7 @@
       </c>
       <c r="G11" s="74">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.22311981384730209</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP(A11,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2727,7 +2775,7 @@
       </c>
       <c r="I11" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.24543610547667344</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2736,11 +2784,11 @@
         <v>石狮睿选</v>
       </c>
       <c r="B12" s="7">
-        <f>粽子销售PICKUP!B12</f>
+        <f>粽子销售PICKUP!D12</f>
         <v>0</v>
       </c>
       <c r="C12" s="7">
-        <f>粽子销售PICKUP!C12</f>
+        <f>粽子销售PICKUP!E12</f>
         <v>0</v>
       </c>
       <c r="D12" s="7">
@@ -2774,20 +2822,20 @@
         <v>沈阳希尔顿</v>
       </c>
       <c r="B13" s="7">
-        <f>粽子销售PICKUP!B13</f>
-        <v>4028</v>
+        <f>粽子销售PICKUP!D13</f>
+        <v>8868</v>
       </c>
       <c r="C13" s="7">
-        <f>粽子销售PICKUP!C13</f>
-        <v>1584</v>
+        <f>粽子销售PICKUP!E13</f>
+        <v>29894</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2444</v>
+        <v>21026</v>
       </c>
       <c r="E13" s="22">
         <f t="shared" si="1"/>
-        <v>-0.60675273088381332</v>
+        <v>2.3709968425800629</v>
       </c>
       <c r="F13" s="7">
         <f>VLOOKUP(A13,原表!$A$4:$B$25,2,0)</f>
@@ -2795,7 +2843,7 @@
       </c>
       <c r="G13" s="74">
         <f t="shared" si="2"/>
-        <v>3.96E-3</v>
+        <v>7.4734999999999996E-2</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP(A13,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2803,7 +2851,7 @@
       </c>
       <c r="I13" s="74">
         <f t="shared" si="3"/>
-        <v>4.6374096085721817E-3</v>
+        <v>8.7519395731475241E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2812,20 +2860,20 @@
         <v>佘山洲际</v>
       </c>
       <c r="B14" s="7">
-        <f>粽子销售PICKUP!B14</f>
-        <v>32322</v>
+        <f>粽子销售PICKUP!D14</f>
+        <v>54270.796000000002</v>
       </c>
       <c r="C14" s="7">
-        <f>粽子销售PICKUP!C14</f>
+        <f>粽子销售PICKUP!E14</f>
         <v>7240</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-25082</v>
+        <v>-47030.796000000002</v>
       </c>
       <c r="E14" s="22">
         <f t="shared" si="1"/>
-        <v>-0.77600396015098072</v>
+        <v>-0.86659491782652309</v>
       </c>
       <c r="F14" s="7">
         <f>VLOOKUP(A14,原表!$A$4:$B$25,2,0)</f>
@@ -2850,20 +2898,20 @@
         <v>绍兴双店</v>
       </c>
       <c r="B15" s="7">
-        <f>粽子销售PICKUP!B15</f>
-        <v>4590</v>
+        <f>粽子销售PICKUP!D15</f>
+        <v>21562</v>
       </c>
       <c r="C15" s="7">
-        <f>粽子销售PICKUP!C15</f>
-        <v>25787</v>
+        <f>粽子销售PICKUP!E15</f>
+        <v>105021</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>21197</v>
+        <v>83459</v>
       </c>
       <c r="E15" s="22">
         <f t="shared" si="1"/>
-        <v>4.6180827886710238</v>
+        <v>3.8706520730915503</v>
       </c>
       <c r="F15" s="7">
         <f>VLOOKUP(A15,原表!$A$4:$B$25,2,0)</f>
@@ -2871,7 +2919,7 @@
       </c>
       <c r="G15" s="74">
         <f t="shared" si="2"/>
-        <v>5.9162135499116711E-2</v>
+        <v>0.24094569481726202</v>
       </c>
       <c r="H15" s="7">
         <f>VLOOKUP(A15,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2879,7 +2927,7 @@
       </c>
       <c r="I15" s="74">
         <f t="shared" si="3"/>
-        <v>6.5078423702507285E-2</v>
+        <v>0.26504056833524714</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2888,20 +2936,20 @@
         <v>上海康莱德</v>
       </c>
       <c r="B16" s="7">
-        <f>粽子销售PICKUP!B16</f>
-        <v>3500</v>
+        <f>粽子销售PICKUP!D16</f>
+        <v>52842</v>
       </c>
       <c r="C16" s="7">
-        <f>粽子销售PICKUP!C16</f>
+        <f>粽子销售PICKUP!E16</f>
         <v>27139</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>23639</v>
+        <v>-25703</v>
       </c>
       <c r="E16" s="22">
         <f t="shared" si="1"/>
-        <v>6.7539999999999996</v>
+        <v>-0.48641232353052499</v>
       </c>
       <c r="F16" s="7">
         <f>VLOOKUP(A16,原表!$A$4:$B$25,2,0)</f>
@@ -2926,20 +2974,20 @@
         <v>厦门康莱德</v>
       </c>
       <c r="B17" s="7">
-        <f>粽子销售PICKUP!B17</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!D17</f>
+        <v>13896</v>
       </c>
       <c r="C17" s="7">
-        <f>粽子销售PICKUP!C17</f>
-        <v>780</v>
+        <f>粽子销售PICKUP!E17</f>
+        <v>18146.2</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="E17" s="22" t="e">
+        <v>4250.2000000000007</v>
+      </c>
+      <c r="E17" s="22">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.30585780080598735</v>
       </c>
       <c r="F17" s="7">
         <f>VLOOKUP(A17,原表!$A$4:$B$25,2,0)</f>
@@ -2947,7 +2995,7 @@
       </c>
       <c r="G17" s="74">
         <f t="shared" si="2"/>
-        <v>1.5847184381990284E-3</v>
+        <v>3.6867458619547704E-2</v>
       </c>
       <c r="H17" s="7">
         <f>VLOOKUP(A17,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2955,7 +3003,7 @@
       </c>
       <c r="I17" s="74">
         <f t="shared" si="3"/>
-        <v>1.7431920528321284E-3</v>
+        <v>4.0554245678336369E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2964,20 +3012,20 @@
         <v>宁波双店</v>
       </c>
       <c r="B18" s="7">
-        <f>粽子销售PICKUP!B18</f>
-        <v>540</v>
+        <f>粽子销售PICKUP!D18</f>
+        <v>4068</v>
       </c>
       <c r="C18" s="7">
-        <f>粽子销售PICKUP!C18</f>
-        <v>11300</v>
+        <f>粽子销售PICKUP!E18</f>
+        <v>48850</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>10760</v>
+        <v>44782</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="1"/>
-        <v>19.925925925925927</v>
+        <v>11.008357915437561</v>
       </c>
       <c r="F18" s="7">
         <f>VLOOKUP(A18,原表!$A$4:$B$25,2,0)</f>
@@ -2985,7 +3033,7 @@
       </c>
       <c r="G18" s="74">
         <f t="shared" si="2"/>
-        <v>3.2557054076402477E-2</v>
+        <v>0.14074443288781069</v>
       </c>
       <c r="H18" s="7">
         <f>VLOOKUP(A18,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2993,7 +3041,7 @@
       </c>
       <c r="I18" s="74">
         <f t="shared" si="3"/>
-        <v>3.5812759484042722E-2</v>
+        <v>0.15481887617659176</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3002,20 +3050,20 @@
         <v>南京希尔顿</v>
       </c>
       <c r="B19" s="7">
-        <f>粽子销售PICKUP!B19</f>
-        <v>2474</v>
+        <f>粽子销售PICKUP!D19</f>
+        <v>54347</v>
       </c>
       <c r="C19" s="7">
-        <f>粽子销售PICKUP!C19</f>
-        <v>196331</v>
+        <f>粽子销售PICKUP!E19</f>
+        <v>476520</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>193857</v>
+        <v>422173</v>
       </c>
       <c r="E19" s="22">
         <f t="shared" si="1"/>
-        <v>78.357720291026681</v>
+        <v>7.768101275139383</v>
       </c>
       <c r="F19" s="7">
         <f>VLOOKUP(A19,原表!$A$4:$B$25,2,0)</f>
@@ -3023,7 +3071,7 @@
       </c>
       <c r="G19" s="74">
         <f t="shared" si="2"/>
-        <v>0.19633100000000001</v>
+        <v>0.47652</v>
       </c>
       <c r="H19" s="7">
         <f>VLOOKUP(A19,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3031,7 +3079,7 @@
       </c>
       <c r="I19" s="74">
         <f t="shared" si="3"/>
-        <v>0.25434598352582782</v>
+        <v>0.61732965282980001</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3040,20 +3088,20 @@
         <v>牡丹江假日</v>
       </c>
       <c r="B20" s="7">
-        <f>粽子销售PICKUP!B20</f>
-        <v>5040</v>
+        <f>粽子销售PICKUP!D20</f>
+        <v>8580</v>
       </c>
       <c r="C20" s="7">
-        <f>粽子销售PICKUP!C20</f>
-        <v>24998</v>
+        <f>粽子销售PICKUP!E20</f>
+        <v>37118</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>19958</v>
+        <v>28538</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" si="1"/>
-        <v>3.9599206349206346</v>
+        <v>3.3261072261072258</v>
       </c>
       <c r="F20" s="7">
         <f>VLOOKUP(A20,原表!$A$4:$B$25,2,0)</f>
@@ -3061,7 +3109,7 @@
       </c>
       <c r="G20" s="74">
         <f t="shared" si="2"/>
-        <v>0.17855714285714286</v>
+        <v>0.26512857142857144</v>
       </c>
       <c r="H20" s="7">
         <f>VLOOKUP(A20,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3069,7 +3117,7 @@
       </c>
       <c r="I20" s="74">
         <f t="shared" si="3"/>
-        <v>0.27515988068113023</v>
+        <v>0.40856806348996688</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3078,16 +3126,16 @@
         <v>虹桥睿选尚品</v>
       </c>
       <c r="B21" s="7">
-        <f>粽子销售PICKUP!B21</f>
-        <v>5713</v>
+        <f>粽子销售PICKUP!D21</f>
+        <v>11200</v>
       </c>
       <c r="C21" s="7">
-        <f>粽子销售PICKUP!C21</f>
+        <f>粽子销售PICKUP!E21</f>
         <v>0</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-5713</v>
+        <v>-11200</v>
       </c>
       <c r="E21" s="22">
         <f t="shared" si="1"/>
@@ -3116,20 +3164,20 @@
         <v>杭州艾美</v>
       </c>
       <c r="B22" s="7">
-        <f>粽子销售PICKUP!B22</f>
-        <v>1146.9000000000001</v>
+        <f>粽子销售PICKUP!D22</f>
+        <v>24966.04</v>
       </c>
       <c r="C22" s="7">
-        <f>粽子销售PICKUP!C22</f>
-        <v>26904</v>
+        <f>粽子销售PICKUP!E22</f>
+        <v>90033.11</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>25757.1</v>
+        <v>65067.07</v>
       </c>
       <c r="E22" s="22">
         <f t="shared" si="1"/>
-        <v>22.458017263928848</v>
+        <v>2.6062230934501427</v>
       </c>
       <c r="F22" s="7">
         <f>VLOOKUP(A22,原表!$A$4:$B$25,2,0)</f>
@@ -3137,7 +3185,7 @@
       </c>
       <c r="G22" s="74">
         <f t="shared" si="2"/>
-        <v>9.4030148084202139E-2</v>
+        <v>0.31466795516582147</v>
       </c>
       <c r="H22" s="7">
         <f>VLOOKUP(A22,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3145,7 +3193,7 @@
       </c>
       <c r="I22" s="74">
         <f t="shared" si="3"/>
-        <v>0.10343316289262235</v>
+        <v>0.34613475068240362</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3154,20 +3202,20 @@
         <v>福州洲际</v>
       </c>
       <c r="B23" s="7">
-        <f>粽子销售PICKUP!B23</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!D23</f>
+        <v>65282.02</v>
       </c>
       <c r="C23" s="7">
-        <f>粽子销售PICKUP!C23</f>
-        <v>73676</v>
+        <f>粽子销售PICKUP!E23</f>
+        <v>166704</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>73676</v>
-      </c>
-      <c r="E23" s="22" t="e">
+        <v>101421.98000000001</v>
+      </c>
+      <c r="E23" s="22">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.5535974530199894</v>
       </c>
       <c r="F23" s="7">
         <f>VLOOKUP(A23,原表!$A$4:$B$25,2,0)</f>
@@ -3175,7 +3223,7 @@
       </c>
       <c r="G23" s="74">
         <f t="shared" si="2"/>
-        <v>0.18418999999999999</v>
+        <v>0.41676000000000002</v>
       </c>
       <c r="H23" s="7">
         <f>VLOOKUP(A23,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3183,7 +3231,7 @@
       </c>
       <c r="I23" s="74">
         <f t="shared" si="3"/>
-        <v>0.2099450032770068</v>
+        <v>0.47503490724645941</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3192,20 +3240,20 @@
         <v>成都茂御</v>
       </c>
       <c r="B24" s="7">
-        <f>粽子销售PICKUP!B24</f>
-        <v>3016</v>
+        <f>粽子销售PICKUP!D24</f>
+        <v>15350</v>
       </c>
       <c r="C24" s="7">
-        <f>粽子销售PICKUP!C24</f>
-        <v>66814</v>
+        <f>粽子销售PICKUP!E24</f>
+        <v>109815</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>63798</v>
+        <v>94465</v>
       </c>
       <c r="E24" s="22">
         <f t="shared" si="1"/>
-        <v>21.153183023872678</v>
+        <v>6.1540716612377846</v>
       </c>
       <c r="F24" s="7">
         <f>VLOOKUP(A24,原表!$A$4:$B$25,2,0)</f>
@@ -3213,7 +3261,7 @@
       </c>
       <c r="G24" s="74">
         <f t="shared" si="2"/>
-        <v>0.20357398577108818</v>
+        <v>0.33459270882527686</v>
       </c>
       <c r="H24" s="7">
         <f>VLOOKUP(A24,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3221,7 +3269,7 @@
       </c>
       <c r="I24" s="74">
         <f t="shared" si="3"/>
-        <v>0.22393152080652082</v>
+        <v>0.36805220398970401</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3230,20 +3278,20 @@
         <v>成都龙泉驿睿选</v>
       </c>
       <c r="B25" s="7">
-        <f>粽子销售PICKUP!B25</f>
-        <v>1984</v>
+        <f>粽子销售PICKUP!D25</f>
+        <v>3126</v>
       </c>
       <c r="C25" s="7">
-        <f>粽子销售PICKUP!C25</f>
-        <v>1221</v>
+        <f>粽子销售PICKUP!E25</f>
+        <v>15494</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-763</v>
+        <v>12368</v>
       </c>
       <c r="E25" s="22">
         <f t="shared" si="1"/>
-        <v>-0.38457661290322576</v>
+        <v>3.9564939219449773</v>
       </c>
       <c r="F25" s="7">
         <f>VLOOKUP(A25,原表!$A$4:$B$25,2,0)</f>
@@ -3251,7 +3299,7 @@
       </c>
       <c r="G25" s="74">
         <f t="shared" si="2"/>
-        <v>3.8529504575575892E-2</v>
+        <v>0.48892395077311457</v>
       </c>
       <c r="H25" s="7">
         <f>VLOOKUP(A25,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3259,7 +3307,7 @@
       </c>
       <c r="I25" s="74">
         <f t="shared" si="3"/>
-        <v>4.2382588774341354E-2</v>
+        <v>0.5378180429726821</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3268,19 +3316,19 @@
       </c>
       <c r="B26" s="77">
         <f>SUM(B4:B25)</f>
-        <v>385680.74000000005</v>
+        <v>1747396.2060000002</v>
       </c>
       <c r="C26" s="77">
         <f>SUM(C4:C25)</f>
-        <v>1235728</v>
+        <v>3195708.93</v>
       </c>
       <c r="D26" s="78">
         <f t="shared" si="0"/>
-        <v>850047.26</v>
+        <v>1448312.7239999999</v>
       </c>
       <c r="E26" s="79">
         <f t="shared" si="1"/>
-        <v>2.2040179138839027</v>
+        <v>0.82884048793682674</v>
       </c>
       <c r="F26" s="77">
         <f>SUM(F4:F25)</f>
@@ -3288,7 +3336,7 @@
       </c>
       <c r="G26" s="80">
         <f t="shared" si="2"/>
-        <v>0.13818224188758235</v>
+        <v>0.3573522849426144</v>
       </c>
       <c r="H26" s="77">
         <f>SUM(H4:H25)</f>
@@ -3296,7 +3344,7 @@
       </c>
       <c r="I26" s="80">
         <f t="shared" si="3"/>
-        <v>0.15205417764591922</v>
+        <v>0.39322641661180324</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3304,7 +3352,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14"/>
       <c r="D27" s="24"/>
-      <c r="H27" s="115"/>
+      <c r="H27" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3552,56 +3600,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="26" customFormat="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
       <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:15" s="27" customFormat="1">
-      <c r="A2" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="91" t="s">
+      <c r="A2" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92" t="s">
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93" t="s">
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="86" t="s">
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="106" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="27" customFormat="1" ht="27.75">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
       <c r="C3" s="28" t="s">
         <v>52</v>
       </c>
@@ -3638,7 +3686,7 @@
       <c r="N3" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="86"/>
+      <c r="O3" s="106"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="34">
@@ -4846,8 +4894,8 @@
       <c r="O26" s="62"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="87"/>
-      <c r="B27" s="88"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="108"/>
       <c r="C27" s="64">
         <f>SUM(C4:C25)</f>
         <v>102490</v>
@@ -4928,119 +4976,119 @@
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" style="114" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.265625" style="114" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" style="105" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3984375" style="105" customWidth="1"/>
-    <col min="6" max="6" width="17.1328125" style="105" customWidth="1"/>
-    <col min="7" max="7" width="15.59765625" style="105" customWidth="1"/>
-    <col min="8" max="8" width="16" style="105" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" style="105" customWidth="1"/>
-    <col min="10" max="10" width="17.1328125" style="105" customWidth="1"/>
-    <col min="11" max="11" width="15.59765625" style="105" customWidth="1"/>
-    <col min="12" max="12" width="17.1328125" style="105" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" style="110" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.86328125" style="110" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1328125" style="105"/>
+    <col min="1" max="1" width="22" style="94" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.265625" style="94" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="94" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" style="85" customWidth="1"/>
+    <col min="5" max="5" width="14.3984375" style="85" customWidth="1"/>
+    <col min="6" max="6" width="17.1328125" style="85" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="85" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" style="90" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.86328125" style="90" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1328125" style="85"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="95" customFormat="1">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:15" s="81" customFormat="1">
+      <c r="A1" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-    </row>
-    <row r="2" spans="1:15" s="99" customFormat="1">
-      <c r="A2" s="96" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+    </row>
+    <row r="2" spans="1:15" s="82" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="94" t="s">
+      <c r="D2" s="118"/>
+      <c r="E2" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94" t="s">
+      <c r="F2" s="116"/>
+      <c r="G2" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94" t="s">
+      <c r="H2" s="116"/>
+      <c r="I2" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94" t="s">
+      <c r="J2" s="116"/>
+      <c r="K2" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="94"/>
-      <c r="M2" s="98" t="s">
+      <c r="L2" s="116"/>
+      <c r="M2" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="98" t="s">
+      <c r="N2" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="98" t="s">
+      <c r="O2" s="114" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="99" customFormat="1">
-      <c r="A3" s="96"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="100" t="s">
+    <row r="3" spans="1:15" s="82" customFormat="1">
+      <c r="A3" s="117"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="100" t="s">
+      <c r="G3" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="101" t="s">
+      <c r="H3" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="101" t="s">
+      <c r="J3" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="100" t="s">
+      <c r="K3" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="101" t="s">
+      <c r="L3" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7">
         <v>120000</v>
@@ -5054,8 +5102,8 @@
       <c r="E4" s="1">
         <v>46531.88</v>
       </c>
-      <c r="F4" s="7">
-        <v>0</v>
+      <c r="F4" s="98">
+        <v>132578</v>
       </c>
       <c r="G4" s="1">
         <v>84571.199999999997</v>
@@ -5075,17 +5123,17 @@
       <c r="L4" s="7">
         <v>0</v>
       </c>
-      <c r="M4" s="103">
-        <f t="shared" ref="M4:M25" si="0">D4/C4</f>
-        <v>9.2560686825769611</v>
-      </c>
-      <c r="N4" s="104">
-        <f t="shared" ref="N4:N25" si="1">D4/K4</f>
-        <v>0.74809791597750575</v>
-      </c>
-      <c r="O4" s="104">
-        <f t="shared" ref="O4:O25" si="2">D4/B4</f>
-        <v>0.79152500000000003</v>
+      <c r="M4" s="83">
+        <f t="shared" ref="M4:M25" si="0">F4/E4</f>
+        <v>2.8491864072545532</v>
+      </c>
+      <c r="N4" s="84">
+        <f t="shared" ref="N4:N25" si="1">F4/K4</f>
+        <v>1.0442008096655797</v>
+      </c>
+      <c r="O4" s="84">
+        <f t="shared" ref="O4:O25" si="2">F4/B4</f>
+        <v>1.1048166666666666</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -5104,8 +5152,8 @@
       <c r="E5" s="1">
         <v>104565.47</v>
       </c>
-      <c r="F5" s="7">
-        <v>0</v>
+      <c r="F5" s="99">
+        <v>119613.62</v>
       </c>
       <c r="G5" s="1">
         <v>131239</v>
@@ -5125,17 +5173,17 @@
       <c r="L5" s="7">
         <v>0</v>
       </c>
-      <c r="M5" s="103">
-        <f t="shared" si="0"/>
-        <v>1.1825462019040387</v>
-      </c>
-      <c r="N5" s="104">
+      <c r="M5" s="83">
+        <f t="shared" si="0"/>
+        <v>1.143911273960706</v>
+      </c>
+      <c r="N5" s="84">
         <f t="shared" si="1"/>
-        <v>0.57323527172119704</v>
-      </c>
-      <c r="O5" s="104">
-        <f t="shared" si="2"/>
-        <v>0.52111936682280735</v>
+        <v>0.75902746402010302</v>
+      </c>
+      <c r="O5" s="84">
+        <f t="shared" si="2"/>
+        <v>0.69002019059925701</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -5154,8 +5202,8 @@
       <c r="E6" s="1">
         <v>297052</v>
       </c>
-      <c r="F6" s="7">
-        <v>0</v>
+      <c r="F6" s="99">
+        <v>820850</v>
       </c>
       <c r="G6" s="1">
         <v>845294.69</v>
@@ -5175,17 +5223,17 @@
       <c r="L6" s="7">
         <v>0</v>
       </c>
-      <c r="M6" s="103">
-        <f t="shared" si="0"/>
-        <v>0.7697452229299363</v>
-      </c>
-      <c r="N6" s="104">
+      <c r="M6" s="83">
+        <f t="shared" si="0"/>
+        <v>2.7633209000444365</v>
+      </c>
+      <c r="N6" s="84">
         <f t="shared" si="1"/>
-        <v>0.11149634834466902</v>
-      </c>
-      <c r="O6" s="104">
-        <f t="shared" si="2"/>
-        <v>9.6674663558571572E-2</v>
+        <v>0.75731714967911934</v>
+      </c>
+      <c r="O6" s="84">
+        <f t="shared" si="2"/>
+        <v>0.65664375326481983</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -5204,8 +5252,8 @@
       <c r="E7" s="1">
         <v>46657</v>
       </c>
-      <c r="F7" s="7">
-        <v>0</v>
+      <c r="F7" s="99">
+        <v>279964</v>
       </c>
       <c r="G7" s="1">
         <v>207865</v>
@@ -5225,17 +5273,17 @@
       <c r="L7" s="7">
         <v>0</v>
       </c>
-      <c r="M7" s="103">
-        <f t="shared" si="0"/>
-        <v>1.8982082492855719</v>
-      </c>
-      <c r="N7" s="104">
+      <c r="M7" s="83">
+        <f t="shared" si="0"/>
+        <v>6.0004715262447217</v>
+      </c>
+      <c r="N7" s="84">
         <f t="shared" si="1"/>
-        <v>9.3533019950557239E-2</v>
-      </c>
-      <c r="O7" s="104">
-        <f t="shared" si="2"/>
-        <v>8.8107144625439421E-2</v>
+        <v>0.49051003835230506</v>
+      </c>
+      <c r="O7" s="84">
+        <f t="shared" si="2"/>
+        <v>0.46205542077206185</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -5254,8 +5302,8 @@
       <c r="E8" s="1">
         <v>111210</v>
       </c>
-      <c r="F8" s="7">
-        <v>0</v>
+      <c r="F8" s="99">
+        <v>391500</v>
       </c>
       <c r="G8" s="1">
         <v>362901.92</v>
@@ -5275,17 +5323,17 @@
       <c r="L8" s="7">
         <v>0</v>
       </c>
-      <c r="M8" s="103">
-        <f t="shared" si="0"/>
-        <v>5.6050050595469756</v>
-      </c>
-      <c r="N8" s="104">
+      <c r="M8" s="83">
+        <f t="shared" si="0"/>
+        <v>3.5203668734826006</v>
+      </c>
+      <c r="N8" s="84">
         <f t="shared" si="1"/>
-        <v>0.13302820088860973</v>
-      </c>
-      <c r="O8" s="104">
-        <f t="shared" si="2"/>
-        <v>0.13235310335700737</v>
+        <v>0.3616327510876694</v>
+      </c>
+      <c r="O8" s="84">
+        <f t="shared" si="2"/>
+        <v>0.35979752084344258</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -5304,8 +5352,8 @@
       <c r="E9" s="1">
         <v>724172</v>
       </c>
-      <c r="F9" s="7">
-        <v>0</v>
+      <c r="F9" s="99">
+        <v>289147</v>
       </c>
       <c r="G9" s="1">
         <v>728417</v>
@@ -5325,17 +5373,17 @@
       <c r="L9" s="7">
         <v>0</v>
       </c>
-      <c r="M9" s="103">
-        <f t="shared" si="0"/>
-        <v>16.687786787353069</v>
-      </c>
-      <c r="N9" s="104">
+      <c r="M9" s="83">
+        <f t="shared" si="0"/>
+        <v>0.39927945294764228</v>
+      </c>
+      <c r="N9" s="84">
         <f t="shared" si="1"/>
-        <v>0.29200501989148497</v>
-      </c>
-      <c r="O9" s="104">
-        <f t="shared" si="2"/>
-        <v>0.28068895591946602</v>
+        <v>0.31802948361330996</v>
+      </c>
+      <c r="O9" s="84">
+        <f t="shared" si="2"/>
+        <v>0.30570489418367014</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -5354,8 +5402,8 @@
       <c r="E10" s="1">
         <v>76162</v>
       </c>
-      <c r="F10" s="7">
-        <v>0</v>
+      <c r="F10" s="99">
+        <v>25000</v>
       </c>
       <c r="G10" s="1">
         <v>79866</v>
@@ -5375,17 +5423,17 @@
       <c r="L10" s="7">
         <v>0</v>
       </c>
-      <c r="M10" s="103">
-        <f t="shared" si="0"/>
-        <v>0.38999462076385155</v>
-      </c>
-      <c r="N10" s="104">
+      <c r="M10" s="83">
+        <f t="shared" si="0"/>
+        <v>0.32824768257136105</v>
+      </c>
+      <c r="N10" s="84">
         <f t="shared" si="1"/>
-        <v>1.8091178541716262E-2</v>
-      </c>
-      <c r="O10" s="104">
-        <f t="shared" si="2"/>
-        <v>1.0649118877215659E-2</v>
+        <v>0.15595843570445053</v>
+      </c>
+      <c r="O10" s="84">
+        <f t="shared" si="2"/>
+        <v>9.1802748941514301E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -5405,8 +5453,8 @@
       <c r="E11" s="1">
         <v>2688</v>
       </c>
-      <c r="F11" s="7">
-        <v>0</v>
+      <c r="F11" s="99">
+        <v>5082</v>
       </c>
       <c r="G11" s="1">
         <v>2688</v>
@@ -5426,17 +5474,17 @@
       <c r="L11" s="7">
         <v>0</v>
       </c>
-      <c r="M11" s="103">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="104">
+      <c r="M11" s="83">
+        <f t="shared" si="0"/>
+        <v>1.890625</v>
+      </c>
+      <c r="N11" s="84">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="104">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.21601632236674317</v>
+      </c>
+      <c r="O11" s="84">
+        <f t="shared" si="2"/>
+        <v>0.22311981384730209</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -5476,15 +5524,15 @@
       <c r="L12" s="7">
         <v>0</v>
       </c>
-      <c r="M12" s="103" t="e">
+      <c r="M12" s="83" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N12" s="104">
+      <c r="N12" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="104">
+      <c r="O12" s="84">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5505,8 +5553,8 @@
       <c r="E13" s="1">
         <v>8868</v>
       </c>
-      <c r="F13" s="7">
-        <v>0</v>
+      <c r="F13" s="99">
+        <v>29894</v>
       </c>
       <c r="G13" s="1">
         <v>14718</v>
@@ -5526,17 +5574,17 @@
       <c r="L13" s="7">
         <v>0</v>
       </c>
-      <c r="M13" s="103">
-        <f t="shared" si="0"/>
-        <v>0.39324726911618668</v>
-      </c>
-      <c r="N13" s="104">
+      <c r="M13" s="83">
+        <f t="shared" si="0"/>
+        <v>3.3709968425800629</v>
+      </c>
+      <c r="N13" s="84">
         <f t="shared" si="1"/>
-        <v>4.1039778012109847E-3</v>
-      </c>
-      <c r="O13" s="104">
-        <f t="shared" si="2"/>
-        <v>3.96E-3</v>
+        <v>7.7452217417551247E-2</v>
+      </c>
+      <c r="O13" s="84">
+        <f t="shared" si="2"/>
+        <v>7.4734999999999996E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -5555,8 +5603,8 @@
       <c r="E14" s="1">
         <v>54270.796000000002</v>
       </c>
-      <c r="F14" s="7">
-        <v>0</v>
+      <c r="F14" s="99">
+        <v>7240</v>
       </c>
       <c r="G14" s="1">
         <v>85480</v>
@@ -5576,15 +5624,15 @@
       <c r="L14" s="7">
         <v>0</v>
       </c>
-      <c r="M14" s="103">
-        <f t="shared" si="0"/>
-        <v>0.22399603984901925</v>
-      </c>
-      <c r="N14" s="104">
+      <c r="M14" s="83">
+        <f t="shared" si="0"/>
+        <v>0.13340508217347688</v>
+      </c>
+      <c r="N14" s="84">
         <f t="shared" si="1"/>
         <v>3.0739967052190009E-2</v>
       </c>
-      <c r="O14" s="104">
+      <c r="O14" s="84">
         <f t="shared" si="2"/>
         <v>2.2904289176141575E-2</v>
       </c>
@@ -5605,8 +5653,8 @@
       <c r="E15" s="1">
         <v>21562</v>
       </c>
-      <c r="F15" s="7">
-        <v>0</v>
+      <c r="F15" s="98">
+        <v>105021</v>
       </c>
       <c r="G15" s="1">
         <v>81341</v>
@@ -5626,17 +5674,17 @@
       <c r="L15" s="7">
         <v>0</v>
       </c>
-      <c r="M15" s="103">
-        <f t="shared" si="0"/>
-        <v>5.6180827886710238</v>
-      </c>
-      <c r="N15" s="104">
+      <c r="M15" s="83">
+        <f t="shared" si="0"/>
+        <v>4.8706520730915503</v>
+      </c>
+      <c r="N15" s="84">
         <f t="shared" si="1"/>
-        <v>6.5307848743709679E-2</v>
-      </c>
-      <c r="O15" s="104">
-        <f t="shared" si="2"/>
-        <v>5.9162135499116711E-2</v>
+        <v>0.26597493244321302</v>
+      </c>
+      <c r="O15" s="84">
+        <f t="shared" si="2"/>
+        <v>0.24094569481726202</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -5655,8 +5703,8 @@
       <c r="E16" s="1">
         <v>52842</v>
       </c>
-      <c r="F16" s="7">
-        <v>0</v>
+      <c r="F16" s="99">
+        <v>27139</v>
       </c>
       <c r="G16" s="1">
         <v>91590</v>
@@ -5676,15 +5724,15 @@
       <c r="L16" s="7">
         <v>0</v>
       </c>
-      <c r="M16" s="103">
-        <f t="shared" si="0"/>
-        <v>7.7539999999999996</v>
-      </c>
-      <c r="N16" s="104">
+      <c r="M16" s="83">
+        <f t="shared" si="0"/>
+        <v>0.51358767646947501</v>
+      </c>
+      <c r="N16" s="84">
         <f t="shared" si="1"/>
         <v>0.12395973215672303</v>
       </c>
-      <c r="O16" s="104">
+      <c r="O16" s="84">
         <f t="shared" si="2"/>
         <v>0.12540316245714234</v>
       </c>
@@ -5705,8 +5753,8 @@
       <c r="E17" s="1">
         <v>13896</v>
       </c>
-      <c r="F17" s="7">
-        <v>0</v>
+      <c r="F17" s="99">
+        <v>18146.2</v>
       </c>
       <c r="G17" s="1">
         <v>134945</v>
@@ -5726,17 +5774,17 @@
       <c r="L17" s="7">
         <v>0</v>
       </c>
-      <c r="M17" s="103" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N17" s="104">
+      <c r="M17" s="83">
+        <f t="shared" si="0"/>
+        <v>1.3058578008059873</v>
+      </c>
+      <c r="N17" s="84">
         <f t="shared" si="1"/>
-        <v>1.5426461563289927E-3</v>
-      </c>
-      <c r="O17" s="104">
-        <f t="shared" si="2"/>
-        <v>1.5847184381990284E-3</v>
+        <v>3.5888673951252781E-2</v>
+      </c>
+      <c r="O17" s="84">
+        <f t="shared" si="2"/>
+        <v>3.6867458619547704E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -5755,8 +5803,8 @@
       <c r="E18" s="7">
         <v>4068</v>
       </c>
-      <c r="F18" s="7">
-        <v>0</v>
+      <c r="F18" s="99">
+        <v>48850</v>
       </c>
       <c r="G18" s="7">
         <v>109140</v>
@@ -5776,17 +5824,17 @@
       <c r="L18" s="7">
         <v>0</v>
       </c>
-      <c r="M18" s="103">
-        <f t="shared" si="0"/>
-        <v>20.925925925925927</v>
-      </c>
-      <c r="N18" s="104">
+      <c r="M18" s="83">
+        <f t="shared" si="0"/>
+        <v>12.008357915437561</v>
+      </c>
+      <c r="N18" s="84">
         <f t="shared" si="1"/>
-        <v>3.3289732621581171E-2</v>
-      </c>
-      <c r="O18" s="104">
-        <f t="shared" si="2"/>
-        <v>3.2557054076402477E-2</v>
+        <v>0.14391180872249915</v>
+      </c>
+      <c r="O18" s="84">
+        <f t="shared" si="2"/>
+        <v>0.14074443288781069</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -5805,8 +5853,8 @@
       <c r="E19" s="1">
         <v>54347</v>
       </c>
-      <c r="F19" s="7">
-        <v>0</v>
+      <c r="F19" s="99">
+        <v>476520</v>
       </c>
       <c r="G19" s="1">
         <v>383704</v>
@@ -5826,17 +5874,17 @@
       <c r="L19" s="7">
         <v>0</v>
       </c>
-      <c r="M19" s="103">
-        <f t="shared" si="0"/>
-        <v>79.357720291026681</v>
-      </c>
-      <c r="N19" s="104">
+      <c r="M19" s="83">
+        <f t="shared" si="0"/>
+        <v>8.768101275139383</v>
+      </c>
+      <c r="N19" s="84">
         <f t="shared" si="1"/>
-        <v>0.25444165808077862</v>
-      </c>
-      <c r="O19" s="104">
-        <f t="shared" si="2"/>
-        <v>0.19633100000000001</v>
+        <v>0.61756186699325444</v>
+      </c>
+      <c r="O19" s="84">
+        <f t="shared" si="2"/>
+        <v>0.47652</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -5855,8 +5903,8 @@
       <c r="E20" s="1">
         <v>8580</v>
       </c>
-      <c r="F20" s="7">
-        <v>0</v>
+      <c r="F20" s="99">
+        <v>37118</v>
       </c>
       <c r="G20" s="1">
         <v>11760</v>
@@ -5876,17 +5924,17 @@
       <c r="L20" s="7">
         <v>0</v>
       </c>
-      <c r="M20" s="103">
-        <f t="shared" si="0"/>
-        <v>4.9599206349206346</v>
-      </c>
-      <c r="N20" s="104">
+      <c r="M20" s="83">
+        <f t="shared" si="0"/>
+        <v>4.3261072261072258</v>
+      </c>
+      <c r="N20" s="84">
         <f t="shared" si="1"/>
-        <v>0.23554797553874132</v>
-      </c>
-      <c r="O20" s="104">
-        <f t="shared" si="2"/>
-        <v>0.17855714285714286</v>
+        <v>0.34975077030350427</v>
+      </c>
+      <c r="O20" s="84">
+        <f t="shared" si="2"/>
+        <v>0.26512857142857144</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -5926,15 +5974,15 @@
       <c r="L21" s="7">
         <v>0</v>
       </c>
-      <c r="M21" s="103">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="104">
+      <c r="M21" s="83">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O21" s="104">
+      <c r="O21" s="84">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5955,8 +6003,8 @@
       <c r="E22" s="1">
         <v>24966.04</v>
       </c>
-      <c r="F22" s="7">
-        <v>0</v>
+      <c r="F22" s="98">
+        <v>90033.11</v>
       </c>
       <c r="G22" s="1">
         <v>45398</v>
@@ -5976,17 +6024,17 @@
       <c r="L22" s="7">
         <v>0</v>
       </c>
-      <c r="M22" s="103">
-        <f t="shared" si="0"/>
-        <v>23.458017263928848</v>
-      </c>
-      <c r="N22" s="104">
+      <c r="M22" s="83">
+        <f t="shared" si="0"/>
+        <v>3.6062230934501427</v>
+      </c>
+      <c r="N22" s="84">
         <f t="shared" si="1"/>
-        <v>0.10396348016126859</v>
-      </c>
-      <c r="O22" s="104">
-        <f t="shared" si="2"/>
-        <v>9.4030148084202139E-2</v>
+        <v>0.34790943522681805</v>
+      </c>
+      <c r="O22" s="84">
+        <f t="shared" si="2"/>
+        <v>0.31466795516582147</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -6005,8 +6053,8 @@
       <c r="E23" s="1">
         <v>65282.02</v>
       </c>
-      <c r="F23" s="7">
-        <v>0</v>
+      <c r="F23" s="99">
+        <v>166704</v>
       </c>
       <c r="G23" s="1">
         <v>116328</v>
@@ -6026,17 +6074,17 @@
       <c r="L23" s="7">
         <v>0</v>
       </c>
-      <c r="M23" s="103" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N23" s="104">
+      <c r="M23" s="83">
+        <f t="shared" si="0"/>
+        <v>2.5535974530199894</v>
+      </c>
+      <c r="N23" s="84">
         <f t="shared" si="1"/>
-        <v>0.19313302470915755</v>
-      </c>
-      <c r="O23" s="104">
-        <f t="shared" si="2"/>
-        <v>0.18418999999999999</v>
+        <v>0.4369950560713855</v>
+      </c>
+      <c r="O23" s="84">
+        <f t="shared" si="2"/>
+        <v>0.41676000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -6055,8 +6103,8 @@
       <c r="E24" s="1">
         <v>15350</v>
       </c>
-      <c r="F24" s="7">
-        <v>0</v>
+      <c r="F24" s="100">
+        <v>109815</v>
       </c>
       <c r="G24" s="1">
         <v>46157</v>
@@ -6076,17 +6124,17 @@
       <c r="L24" s="7">
         <v>0</v>
       </c>
-      <c r="M24" s="103">
-        <f t="shared" si="0"/>
-        <v>22.153183023872678</v>
-      </c>
-      <c r="N24" s="104">
+      <c r="M24" s="83">
+        <f t="shared" si="0"/>
+        <v>7.1540716612377846</v>
+      </c>
+      <c r="N24" s="84">
         <f t="shared" si="1"/>
-        <v>8.4371018314019192E-2</v>
-      </c>
-      <c r="O24" s="104">
-        <f t="shared" si="2"/>
-        <v>0.20357398577108818</v>
+        <v>0.13867158643628608</v>
+      </c>
+      <c r="O24" s="84">
+        <f t="shared" si="2"/>
+        <v>0.33459270882527686</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -6105,8 +6153,8 @@
       <c r="E25" s="1">
         <v>3126</v>
       </c>
-      <c r="F25" s="7">
-        <v>0</v>
+      <c r="F25" s="99">
+        <v>15494</v>
       </c>
       <c r="G25" s="1">
         <v>4584</v>
@@ -6126,97 +6174,97 @@
       <c r="L25" s="7">
         <v>0</v>
       </c>
-      <c r="M25" s="103">
-        <f t="shared" si="0"/>
-        <v>0.61542338709677424</v>
-      </c>
-      <c r="N25" s="104">
+      <c r="M25" s="83">
+        <f t="shared" si="0"/>
+        <v>4.9564939219449773</v>
+      </c>
+      <c r="N25" s="84">
         <f t="shared" si="1"/>
-        <v>4.2382588774341354E-2</v>
-      </c>
-      <c r="O25" s="104">
-        <f t="shared" si="2"/>
-        <v>3.8529504575575892E-2</v>
+        <v>0.5378180429726821</v>
+      </c>
+      <c r="O25" s="84">
+        <f t="shared" si="2"/>
+        <v>0.48892395077311457</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="106"/>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="108"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="108"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="109"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="89"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="111"/>
-      <c r="B27" s="112">
+      <c r="A27" s="91"/>
+      <c r="B27" s="92">
         <f t="shared" ref="B27:L27" si="3">SUM(B4:B25)</f>
         <v>8942741</v>
       </c>
-      <c r="C27" s="112">
+      <c r="C27" s="92">
         <f t="shared" si="3"/>
         <v>385680.74000000005</v>
       </c>
-      <c r="D27" s="112">
+      <c r="D27" s="92">
         <f t="shared" si="3"/>
         <v>1235728</v>
       </c>
-      <c r="E27" s="112">
+      <c r="E27" s="92">
         <f t="shared" si="3"/>
         <v>1747396.2060000002</v>
       </c>
-      <c r="F27" s="113">
+      <c r="F27" s="93">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="112">
+        <v>3195708.93</v>
+      </c>
+      <c r="G27" s="92">
         <f t="shared" si="3"/>
         <v>3593461.8099999996</v>
       </c>
-      <c r="H27" s="112">
+      <c r="H27" s="92">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I27" s="112">
+      <c r="I27" s="92">
         <f t="shared" si="3"/>
         <v>6366957.46</v>
       </c>
-      <c r="J27" s="112">
+      <c r="J27" s="92">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K27" s="112">
+      <c r="K27" s="92">
         <f t="shared" si="3"/>
         <v>8597339</v>
       </c>
-      <c r="L27" s="112">
+      <c r="L27" s="92">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="110">
-        <f>D27/C27</f>
-        <v>3.2040179138839027</v>
-      </c>
-      <c r="N27" s="110">
-        <f t="shared" ref="N27" si="4">D27/K27</f>
-        <v>0.14373377623006375</v>
-      </c>
-      <c r="O27" s="110">
-        <f>D27/B27</f>
-        <v>0.13818224188758235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="110" customFormat="1">
-      <c r="A28" s="109"/>
-      <c r="B28" s="109"/>
-      <c r="C28" s="109"/>
+      <c r="M27" s="90">
+        <f>F27/E27</f>
+        <v>1.8288404879368267</v>
+      </c>
+      <c r="N27" s="90">
+        <f>F27/K27</f>
+        <v>0.37170907533133218</v>
+      </c>
+      <c r="O27" s="90">
+        <f>F27/B27</f>
+        <v>0.3573522849426144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="90" customFormat="1">
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/粽子销售数据.xlsx
+++ b/粽子销售数据.xlsx
@@ -9,12 +9,16 @@
   <sheets>
     <sheet name="粽子销售PICKUP" sheetId="3" r:id="rId1"/>
     <sheet name="最新数据" sheetId="6" r:id="rId2"/>
-    <sheet name="经验总结" sheetId="8" state="hidden" r:id="rId3"/>
-    <sheet name="2026年 粽子礼盒销售汇总" sheetId="7" state="hidden" r:id="rId4"/>
-    <sheet name="原表" sheetId="9" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="经验总结" sheetId="8" state="hidden" r:id="rId4"/>
+    <sheet name="2026年 粽子礼盒销售汇总" sheetId="7" state="hidden" r:id="rId5"/>
+    <sheet name="原表" sheetId="9" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2026年 粽子礼盒销售汇总'!$B$3:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2026年 粽子礼盒销售汇总'!$B$3:$O$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">粽子销售PICKUP!$A$3:$K$3</definedName>
     <definedName name="Dienstag">#REF!</definedName>
     <definedName name="Donnerstag">#REF!</definedName>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="73">
   <si>
     <t>序号</t>
   </si>
@@ -276,6 +280,9 @@
     <t>香港喜來登</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>26年(5.31）</t>
+  </si>
 </sst>
 </file>
 
@@ -288,7 +295,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,6 +415,49 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -630,7 +680,7 @@
     <xf numFmtId="9" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -920,6 +970,15 @@
     <xf numFmtId="177" fontId="16" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -973,6 +1032,57 @@
     </xf>
     <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="12" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="12" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -995,6 +1105,1129 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'[1]粽子销售 26年 VS 25年 同期收入 PICK UP'!$A$4:$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>沈阳希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>牡丹江假日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>松江睿选</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>成都龙泉驿睿选</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>杭州艾美</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>成都茂御</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>烟台希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>福州洲际</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>武汉希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>绍兴双店</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>香港世茂喜來登酒店</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>南京希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>上海康莱德</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>佘山洲际</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>长沙希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>泰州茂御</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>佘山艾美</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>宁波双店</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>厦门康莱德</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>虹桥睿选尚品</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>芜湖希尔顿逸林</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>石狮睿选</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]粽子销售 26年 VS 25年 同期收入 PICK UP'!$M$4:$M$25</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>6.9970104633781762</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0710034013605441</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0889136904761907</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.4563699825479932</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9963714260540111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.8820113958879476</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4062396266807782</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0698284162024621</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9977849662520386</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9682745478909776</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.954790756191233</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.9392239851552238</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6176547658041271</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2345343940102949</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.185270665784024</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.97733703954123152</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.97321992700340598</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.95076049111233274</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.9297565674904591</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.79625984251968507</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.52175882770446047</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FF48-4FAA-A126-0C404AB34B61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1908930096"/>
+        <c:axId val="1908936752"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1908930096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1908936752"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1908936752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1908930096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>549087</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="粽子销售 26年 VS 25年 同期收入 PICK UP"/>
+      <sheetName val="散客人数用餐比例%"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>沈阳希尔顿</v>
+          </cell>
+          <cell r="M4">
+            <v>6.9970104633781762</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>牡丹江假日</v>
+          </cell>
+          <cell r="M5">
+            <v>5.0710034013605441</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>松江睿选</v>
+          </cell>
+          <cell r="M6">
+            <v>4.0889136904761907</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>成都龙泉驿睿选</v>
+          </cell>
+          <cell r="M7">
+            <v>3.4563699825479932</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>杭州艾美</v>
+          </cell>
+          <cell r="M8">
+            <v>2.9963714260540111</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>成都茂御</v>
+          </cell>
+          <cell r="M9">
+            <v>2.8820113958879476</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>烟台希尔顿</v>
+          </cell>
+          <cell r="M10">
+            <v>2.4062396266807782</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>福州洲际</v>
+          </cell>
+          <cell r="M11">
+            <v>2.0698284162024621</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>武汉希尔顿</v>
+          </cell>
+          <cell r="M12">
+            <v>1.9977849662520386</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>绍兴双店</v>
+          </cell>
+          <cell r="M13">
+            <v>1.9682745478909776</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>香港世茂喜來登酒店</v>
+          </cell>
+          <cell r="M14">
+            <v>1.954790756191233</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>南京希尔顿</v>
+          </cell>
+          <cell r="M15">
+            <v>1.9392239851552238</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>上海康莱德</v>
+          </cell>
+          <cell r="M16">
+            <v>1.6176547658041271</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>佘山洲际</v>
+          </cell>
+          <cell r="M17">
+            <v>1.2345343940102949</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>长沙希尔顿</v>
+          </cell>
+          <cell r="M18">
+            <v>1.185270665784024</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>泰州茂御</v>
+          </cell>
+          <cell r="M19">
+            <v>0.97733703954123152</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>佘山艾美</v>
+          </cell>
+          <cell r="M20">
+            <v>0.97321992700340598</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>宁波双店</v>
+          </cell>
+          <cell r="M21">
+            <v>0.95076049111233274</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>厦门康莱德</v>
+          </cell>
+          <cell r="M22">
+            <v>0.9297565674904591</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>虹桥睿选尚品</v>
+          </cell>
+          <cell r="M23">
+            <v>0.79625984251968507</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>芜湖希尔顿逸林</v>
+          </cell>
+          <cell r="M24">
+            <v>0.52175882770446047</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>石狮睿选</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1282,47 +2515,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="101" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="104"/>
+      <c r="F2" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101" t="s">
+      <c r="G2" s="104"/>
+      <c r="H2" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101" t="s">
+      <c r="I2" s="104"/>
+      <c r="J2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="101"/>
+      <c r="K2" s="104"/>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="103"/>
+      <c r="A3" s="106"/>
       <c r="B3" s="11">
         <v>2025</v>
       </c>
@@ -1380,7 +2613,7 @@
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(H1),0)</f>
-        <v>0</v>
+        <v>165319</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(I1),0)</f>
@@ -1425,7 +2658,7 @@
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP($A5,原表!$A$4:$O$25,COLUMN(H2),0)</f>
-        <v>0</v>
+        <v>127724.41</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP($A5,原表!$A$4:$O$25,COLUMN(I2),0)</f>
@@ -1470,7 +2703,7 @@
       </c>
       <c r="G6" s="7">
         <f>VLOOKUP($A6,原表!$A$4:$O$25,COLUMN(H3),0)</f>
-        <v>0</v>
+        <v>1001903</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP($A6,原表!$A$4:$O$25,COLUMN(I3),0)</f>
@@ -1515,7 +2748,7 @@
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP($A7,原表!$A$4:$O$25,COLUMN(H4),0)</f>
-        <v>0</v>
+        <v>500173</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP($A7,原表!$A$4:$O$25,COLUMN(I4),0)</f>
@@ -1560,7 +2793,7 @@
       </c>
       <c r="G8" s="7">
         <f>VLOOKUP($A8,原表!$A$4:$O$25,COLUMN(H5),0)</f>
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="H8" s="7">
         <f>VLOOKUP($A8,原表!$A$4:$O$25,COLUMN(I5),0)</f>
@@ -1605,7 +2838,7 @@
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP($A9,原表!$A$4:$O$25,COLUMN(H6),0)</f>
-        <v>0</v>
+        <v>380058</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP($A9,原表!$A$4:$O$25,COLUMN(I6),0)</f>
@@ -1650,7 +2883,7 @@
       </c>
       <c r="G10" s="7">
         <f>VLOOKUP($A10,原表!$A$4:$O$25,COLUMN(H7),0)</f>
-        <v>0</v>
+        <v>78056</v>
       </c>
       <c r="H10" s="7">
         <f>VLOOKUP($A10,原表!$A$4:$O$25,COLUMN(I7),0)</f>
@@ -1695,7 +2928,7 @@
       </c>
       <c r="G11" s="7">
         <f>VLOOKUP($A11,原表!$A$4:$O$25,COLUMN(H8),0)</f>
-        <v>0</v>
+        <v>10991</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP($A11,原表!$A$4:$O$25,COLUMN(I8),0)</f>
@@ -1785,7 +3018,7 @@
       </c>
       <c r="G13" s="7">
         <f>VLOOKUP($A13,原表!$A$4:$O$25,COLUMN(H10),0)</f>
-        <v>0</v>
+        <v>102982</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP($A13,原表!$A$4:$O$25,COLUMN(I10),0)</f>
@@ -1830,7 +3063,7 @@
       </c>
       <c r="G14" s="7">
         <f>VLOOKUP($A14,原表!$A$4:$O$25,COLUMN(H11),0)</f>
-        <v>0</v>
+        <v>105528</v>
       </c>
       <c r="H14" s="7">
         <f>VLOOKUP($A14,原表!$A$4:$O$25,COLUMN(I11),0)</f>
@@ -1875,7 +3108,7 @@
       </c>
       <c r="G15" s="7">
         <f>VLOOKUP($A15,原表!$A$4:$O$25,COLUMN(H12),0)</f>
-        <v>0</v>
+        <v>160101.42000000001</v>
       </c>
       <c r="H15" s="7">
         <f>VLOOKUP($A15,原表!$A$4:$O$25,COLUMN(I12),0)</f>
@@ -1920,7 +3153,7 @@
       </c>
       <c r="G16" s="7">
         <f>VLOOKUP($A16,原表!$A$4:$O$25,COLUMN(H13),0)</f>
-        <v>0</v>
+        <v>148161</v>
       </c>
       <c r="H16" s="7">
         <f>VLOOKUP($A16,原表!$A$4:$O$25,COLUMN(I13),0)</f>
@@ -1965,7 +3198,7 @@
       </c>
       <c r="G17" s="7">
         <f>VLOOKUP($A17,原表!$A$4:$O$25,COLUMN(H14),0)</f>
-        <v>0</v>
+        <v>125466</v>
       </c>
       <c r="H17" s="7">
         <f>VLOOKUP($A17,原表!$A$4:$O$25,COLUMN(I14),0)</f>
@@ -2010,7 +3243,7 @@
       </c>
       <c r="G18" s="7">
         <f>VLOOKUP($A18,原表!$A$4:$O$25,COLUMN(H15),0)</f>
-        <v>0</v>
+        <v>103766</v>
       </c>
       <c r="H18" s="7">
         <f>VLOOKUP($A18,原表!$A$4:$O$25,COLUMN(I15),0)</f>
@@ -2055,7 +3288,7 @@
       </c>
       <c r="G19" s="7">
         <f>VLOOKUP($A19,原表!$A$4:$O$25,COLUMN(H16),0)</f>
-        <v>0</v>
+        <v>744088</v>
       </c>
       <c r="H19" s="7">
         <f>VLOOKUP($A19,原表!$A$4:$O$25,COLUMN(I16),0)</f>
@@ -2100,7 +3333,7 @@
       </c>
       <c r="G20" s="7">
         <f>VLOOKUP($A20,原表!$A$4:$O$25,COLUMN(H17),0)</f>
-        <v>0</v>
+        <v>59635</v>
       </c>
       <c r="H20" s="7">
         <f>VLOOKUP($A20,原表!$A$4:$O$25,COLUMN(I17),0)</f>
@@ -2145,7 +3378,7 @@
       </c>
       <c r="G21" s="7">
         <f>VLOOKUP($A21,原表!$A$4:$O$25,COLUMN(H18),0)</f>
-        <v>0</v>
+        <v>18607</v>
       </c>
       <c r="H21" s="7">
         <f>VLOOKUP($A21,原表!$A$4:$O$25,COLUMN(I18),0)</f>
@@ -2190,7 +3423,7 @@
       </c>
       <c r="G22" s="7">
         <f>VLOOKUP($A22,原表!$A$4:$O$25,COLUMN(H19),0)</f>
-        <v>0</v>
+        <v>136029.26999999999</v>
       </c>
       <c r="H22" s="7">
         <f>VLOOKUP($A22,原表!$A$4:$O$25,COLUMN(I19),0)</f>
@@ -2235,7 +3468,7 @@
       </c>
       <c r="G23" s="7">
         <f>VLOOKUP($A23,原表!$A$4:$O$25,COLUMN(H20),0)</f>
-        <v>0</v>
+        <v>240779</v>
       </c>
       <c r="H23" s="7">
         <f>VLOOKUP($A23,原表!$A$4:$O$25,COLUMN(I20),0)</f>
@@ -2280,7 +3513,7 @@
       </c>
       <c r="G24" s="7">
         <f>VLOOKUP($A24,原表!$A$4:$O$25,COLUMN(H21),0)</f>
-        <v>0</v>
+        <v>133025</v>
       </c>
       <c r="H24" s="7">
         <f>VLOOKUP($A24,原表!$A$4:$O$25,COLUMN(I21),0)</f>
@@ -2325,7 +3558,7 @@
       </c>
       <c r="G25" s="7">
         <f>VLOOKUP($A25,原表!$A$4:$O$25,COLUMN(H22),0)</f>
-        <v>0</v>
+        <v>15844</v>
       </c>
       <c r="H25" s="7">
         <f>VLOOKUP($A25,原表!$A$4:$O$25,COLUMN(I22),0)</f>
@@ -2370,7 +3603,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5083236.0999999996</v>
       </c>
       <c r="H26" s="17">
         <f t="shared" si="0"/>
@@ -2412,7 +3645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" style="3" bestFit="1" customWidth="1"/>
@@ -2425,38 +3658,38 @@
     <col min="9" max="9" width="16.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.9">
+    <row r="1" spans="1:11" ht="13.9">
       <c r="A1"/>
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1" s="23"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="103" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="102" t="str">
-        <f>粽子销售PICKUP!D2</f>
-        <v>节前26天</v>
-      </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="104" t="s">
+      <c r="B2" s="105" t="str">
+        <f>粽子销售PICKUP!F2</f>
+        <v>节前19天</v>
+      </c>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="104" t="s">
+      <c r="G2" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="104" t="s">
+      <c r="H2" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="104" t="s">
+      <c r="I2" s="107" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="103"/>
+    <row r="3" spans="1:11">
+      <c r="A3" s="106"/>
       <c r="B3" s="15" t="s">
         <v>43</v>
       </c>
@@ -2469,31 +3702,31 @@
       <c r="E3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2" t="str">
         <f>粽子销售PICKUP!A4</f>
         <v>香港喜來登</v>
       </c>
       <c r="B4" s="7">
-        <f>粽子销售PICKUP!D4</f>
-        <v>46531.88</v>
+        <f>粽子销售PICKUP!F4</f>
+        <v>84571.199999999997</v>
       </c>
       <c r="C4" s="7">
-        <f>粽子销售PICKUP!E4</f>
-        <v>132578</v>
+        <f>粽子销售PICKUP!G4</f>
+        <v>165319</v>
       </c>
       <c r="D4" s="7">
         <f>C4-B4</f>
-        <v>86046.12</v>
+        <v>80747.8</v>
       </c>
       <c r="E4" s="22">
         <f>C4/B4-1</f>
-        <v>1.8491864072545532</v>
+        <v>0.95479075619123299</v>
       </c>
       <c r="F4" s="7">
         <f>VLOOKUP(A4,原表!$A$4:$B$25,2,0)</f>
@@ -2501,7 +3734,7 @@
       </c>
       <c r="G4" s="74">
         <f>C4/F4</f>
-        <v>1.1048166666666666</v>
+        <v>1.3776583333333334</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP(A4,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2509,29 +3742,30 @@
       </c>
       <c r="I4" s="74">
         <f>C4/H4</f>
-        <v>1.283414487759073</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>1.6003620487700991</v>
+      </c>
+      <c r="K4" s="103"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2" t="str">
         <f>粽子销售PICKUP!A5</f>
         <v>佘山艾美</v>
       </c>
       <c r="B5" s="7">
-        <f>粽子销售PICKUP!D5</f>
-        <v>104565.47</v>
+        <f>粽子销售PICKUP!F5</f>
+        <v>131239</v>
       </c>
       <c r="C5" s="7">
-        <f>粽子销售PICKUP!E5</f>
-        <v>119613.62</v>
+        <f>粽子销售PICKUP!G5</f>
+        <v>127724.41</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" ref="D5:D26" si="0">C5-B5</f>
-        <v>15048.149999999994</v>
+        <v>-3514.5899999999965</v>
       </c>
       <c r="E5" s="22">
         <f t="shared" ref="E5:E26" si="1">C5/B5-1</f>
-        <v>0.14391127396070602</v>
+        <v>-2.6780072996594018E-2</v>
       </c>
       <c r="F5" s="7">
         <f>VLOOKUP(A5,原表!$A$4:$B$25,2,0)</f>
@@ -2539,7 +3773,7 @@
       </c>
       <c r="G5" s="74">
         <f t="shared" ref="G5:G26" si="2">C5/F5</f>
-        <v>0.69002019059925701</v>
+        <v>0.73680925075570536</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2547,29 +3781,30 @@
       </c>
       <c r="I5" s="74">
         <f t="shared" ref="I5:I26" si="3">C5/H5</f>
-        <v>0.7590242369581518</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.81049234059783604</v>
+      </c>
+      <c r="K5" s="103"/>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2" t="str">
         <f>粽子销售PICKUP!A6</f>
         <v>长沙希尔顿</v>
       </c>
       <c r="B6" s="7">
-        <f>粽子销售PICKUP!D6</f>
-        <v>297052</v>
+        <f>粽子销售PICKUP!F6</f>
+        <v>845294.69</v>
       </c>
       <c r="C6" s="7">
-        <f>粽子销售PICKUP!E6</f>
-        <v>820850</v>
+        <f>粽子销售PICKUP!G6</f>
+        <v>1001903</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>523798</v>
+        <v>156608.31000000006</v>
       </c>
       <c r="E6" s="22">
         <f t="shared" si="1"/>
-        <v>1.7633209000444365</v>
+        <v>0.18527066578402396</v>
       </c>
       <c r="F6" s="7">
         <f>VLOOKUP(A6,原表!$A$4:$B$25,2,0)</f>
@@ -2577,7 +3812,7 @@
       </c>
       <c r="G6" s="74">
         <f t="shared" si="2"/>
-        <v>0.65664375326481983</v>
+        <v>0.80147815840565606</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2585,29 +3820,30 @@
       </c>
       <c r="I6" s="74">
         <f t="shared" si="3"/>
-        <v>0.68455108676706911</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.83554094838909287</v>
+      </c>
+      <c r="K6" s="103"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2" t="str">
         <f>粽子销售PICKUP!A7</f>
         <v>烟台希尔顿</v>
       </c>
       <c r="B7" s="7">
-        <f>粽子销售PICKUP!D7</f>
-        <v>46657</v>
+        <f>粽子销售PICKUP!F7</f>
+        <v>207865</v>
       </c>
       <c r="C7" s="7">
-        <f>粽子销售PICKUP!E7</f>
-        <v>279964</v>
+        <f>粽子销售PICKUP!G7</f>
+        <v>500173</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>233307</v>
+        <v>292308</v>
       </c>
       <c r="E7" s="22">
         <f t="shared" si="1"/>
-        <v>5.0004715262447217</v>
+        <v>1.4062396266807782</v>
       </c>
       <c r="F7" s="7">
         <f>VLOOKUP(A7,原表!$A$4:$B$25,2,0)</f>
@@ -2615,7 +3851,7 @@
       </c>
       <c r="G7" s="74">
         <f t="shared" si="2"/>
-        <v>0.46205542077206185</v>
+        <v>0.82549058441022594</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2623,29 +3859,30 @@
       </c>
       <c r="I7" s="74">
         <f t="shared" si="3"/>
-        <v>0.50826121450110473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.9080400924428178</v>
+      </c>
+      <c r="K7" s="103"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2" t="str">
         <f>粽子销售PICKUP!A8</f>
         <v>武汉希尔顿</v>
       </c>
       <c r="B8" s="7">
-        <f>粽子销售PICKUP!D8</f>
-        <v>111210</v>
+        <f>粽子销售PICKUP!F8</f>
+        <v>362901.92</v>
       </c>
       <c r="C8" s="7">
-        <f>粽子销售PICKUP!E8</f>
-        <v>391500</v>
+        <f>粽子销售PICKUP!G8</f>
+        <v>725000</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>280290</v>
+        <v>362098.08</v>
       </c>
       <c r="E8" s="22">
         <f t="shared" si="1"/>
-        <v>2.5203668734826006</v>
+        <v>0.99778496625203861</v>
       </c>
       <c r="F8" s="7">
         <f>VLOOKUP(A8,原表!$A$4:$B$25,2,0)</f>
@@ -2653,7 +3890,7 @@
       </c>
       <c r="G8" s="74">
         <f t="shared" si="2"/>
-        <v>0.35979752084344258</v>
+        <v>0.66629170526563442</v>
       </c>
       <c r="H8" s="7">
         <f>VLOOKUP(A8,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2661,29 +3898,30 @@
       </c>
       <c r="I8" s="74">
         <f t="shared" si="3"/>
-        <v>0.35979752084344258</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.66629170526563442</v>
+      </c>
+      <c r="K8" s="103"/>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2" t="str">
         <f>粽子销售PICKUP!A9</f>
         <v>芜湖希尔顿逸林</v>
       </c>
       <c r="B9" s="7">
-        <f>粽子销售PICKUP!D9</f>
-        <v>724172</v>
+        <f>粽子销售PICKUP!F9</f>
+        <v>728417</v>
       </c>
       <c r="C9" s="7">
-        <f>粽子销售PICKUP!E9</f>
-        <v>289147</v>
+        <f>粽子销售PICKUP!G9</f>
+        <v>380058</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-435025</v>
+        <v>-348359</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="1"/>
-        <v>-0.60072054705235778</v>
+        <v>-0.47824117229553953</v>
       </c>
       <c r="F9" s="7">
         <f>VLOOKUP(A9,原表!$A$4:$B$25,2,0)</f>
@@ -2691,7 +3929,7 @@
       </c>
       <c r="G9" s="74">
         <f t="shared" si="2"/>
-        <v>0.30570489418367014</v>
+        <v>0.40182187839976657</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2699,29 +3937,30 @@
       </c>
       <c r="I9" s="74">
         <f t="shared" si="3"/>
-        <v>0.31789945778642248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.41785054704836005</v>
+      </c>
+      <c r="K9" s="103"/>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2" t="str">
         <f>粽子销售PICKUP!A10</f>
         <v>泰州茂御</v>
       </c>
       <c r="B10" s="7">
-        <f>粽子销售PICKUP!D10</f>
-        <v>76162</v>
+        <f>粽子销售PICKUP!F10</f>
+        <v>79866</v>
       </c>
       <c r="C10" s="7">
-        <f>粽子销售PICKUP!E10</f>
-        <v>25000</v>
+        <f>粽子销售PICKUP!G10</f>
+        <v>78056</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-51162</v>
+        <v>-1810</v>
       </c>
       <c r="E10" s="22">
         <f t="shared" si="1"/>
-        <v>-0.67175231742863895</v>
+        <v>-2.2662960458768477E-2</v>
       </c>
       <c r="F10" s="7">
         <f>VLOOKUP(A10,原表!$A$4:$B$25,2,0)</f>
@@ -2729,7 +3968,7 @@
       </c>
       <c r="G10" s="74">
         <f t="shared" si="2"/>
-        <v>9.1802748941514301E-2</v>
+        <v>0.28663021485515361</v>
       </c>
       <c r="H10" s="7">
         <f>VLOOKUP(A10,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2737,29 +3976,30 @@
       </c>
       <c r="I10" s="74">
         <f t="shared" si="3"/>
-        <v>0.10098317216419056</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.31529369945792235</v>
+      </c>
+      <c r="K10" s="103"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2" t="str">
         <f>粽子销售PICKUP!A11</f>
         <v>松江睿选</v>
       </c>
       <c r="B11" s="7">
-        <f>粽子销售PICKUP!D11</f>
+        <f>粽子销售PICKUP!F11</f>
         <v>2688</v>
       </c>
       <c r="C11" s="7">
-        <f>粽子销售PICKUP!E11</f>
-        <v>5082</v>
+        <f>粽子销售PICKUP!G11</f>
+        <v>10991</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>2394</v>
+        <v>8303</v>
       </c>
       <c r="E11" s="22">
         <f t="shared" si="1"/>
-        <v>0.890625</v>
+        <v>3.0889136904761907</v>
       </c>
       <c r="F11" s="7">
         <f>VLOOKUP(A11,原表!$A$4:$B$25,2,0)</f>
@@ -2767,7 +4007,7 @@
       </c>
       <c r="G11" s="74">
         <f t="shared" si="2"/>
-        <v>0.22311981384730209</v>
+        <v>0.48254818457215615</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP(A11,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2775,29 +4015,30 @@
       </c>
       <c r="I11" s="74">
         <f t="shared" si="3"/>
-        <v>0.24543610547667344</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.53081232492997199</v>
+      </c>
+      <c r="K11" s="103"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="str">
         <f>粽子销售PICKUP!A12</f>
         <v>石狮睿选</v>
       </c>
       <c r="B12" s="7">
-        <f>粽子销售PICKUP!D12</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!F12</f>
+        <v>2106</v>
       </c>
       <c r="C12" s="7">
-        <f>粽子销售PICKUP!E12</f>
+        <f>粽子销售PICKUP!G12</f>
         <v>0</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="22" t="e">
+        <v>-2106</v>
+      </c>
+      <c r="E12" s="22">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="F12" s="7">
         <f>VLOOKUP(A12,原表!$A$4:$B$25,2,0)</f>
@@ -2815,27 +4056,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="K12" s="103"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2" t="str">
         <f>粽子销售PICKUP!A13</f>
         <v>沈阳希尔顿</v>
       </c>
       <c r="B13" s="7">
-        <f>粽子销售PICKUP!D13</f>
-        <v>8868</v>
+        <f>粽子销售PICKUP!F13</f>
+        <v>14718</v>
       </c>
       <c r="C13" s="7">
-        <f>粽子销售PICKUP!E13</f>
-        <v>29894</v>
+        <f>粽子销售PICKUP!G13</f>
+        <v>102982</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>21026</v>
+        <v>88264</v>
       </c>
       <c r="E13" s="22">
         <f t="shared" si="1"/>
-        <v>2.3709968425800629</v>
+        <v>5.9970104633781762</v>
       </c>
       <c r="F13" s="7">
         <f>VLOOKUP(A13,原表!$A$4:$B$25,2,0)</f>
@@ -2843,7 +4085,7 @@
       </c>
       <c r="G13" s="74">
         <f t="shared" si="2"/>
-        <v>7.4734999999999996E-2</v>
+        <v>0.25745499999999999</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP(A13,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2851,29 +4093,30 @@
       </c>
       <c r="I13" s="74">
         <f t="shared" si="3"/>
-        <v>8.7519395731475241E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>0.30149603302397754</v>
+      </c>
+      <c r="K13" s="103"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2" t="str">
         <f>粽子销售PICKUP!A14</f>
         <v>佘山洲际</v>
       </c>
       <c r="B14" s="7">
-        <f>粽子销售PICKUP!D14</f>
-        <v>54270.796000000002</v>
+        <f>粽子销售PICKUP!F14</f>
+        <v>85480</v>
       </c>
       <c r="C14" s="7">
-        <f>粽子销售PICKUP!E14</f>
-        <v>7240</v>
+        <f>粽子销售PICKUP!G14</f>
+        <v>105528</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-47030.796000000002</v>
+        <v>20048</v>
       </c>
       <c r="E14" s="22">
         <f t="shared" si="1"/>
-        <v>-0.86659491782652309</v>
+        <v>0.23453439401029486</v>
       </c>
       <c r="F14" s="7">
         <f>VLOOKUP(A14,原表!$A$4:$B$25,2,0)</f>
@@ -2881,7 +4124,7 @@
       </c>
       <c r="G14" s="74">
         <f t="shared" si="2"/>
-        <v>2.2904289176141575E-2</v>
+        <v>0.33384583262152878</v>
       </c>
       <c r="H14" s="7">
         <f>VLOOKUP(A14,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2889,29 +4132,30 @@
       </c>
       <c r="I14" s="74">
         <f t="shared" si="3"/>
-        <v>2.5194702152685464E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>0.36723018353157344</v>
+      </c>
+      <c r="K14" s="103"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2" t="str">
         <f>粽子销售PICKUP!A15</f>
         <v>绍兴双店</v>
       </c>
       <c r="B15" s="7">
-        <f>粽子销售PICKUP!D15</f>
-        <v>21562</v>
+        <f>粽子销售PICKUP!F15</f>
+        <v>81341</v>
       </c>
       <c r="C15" s="7">
-        <f>粽子销售PICKUP!E15</f>
-        <v>105021</v>
+        <f>粽子销售PICKUP!G15</f>
+        <v>160101.42000000001</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>83459</v>
+        <v>78760.420000000013</v>
       </c>
       <c r="E15" s="22">
         <f t="shared" si="1"/>
-        <v>3.8706520730915503</v>
+        <v>0.96827454789097755</v>
       </c>
       <c r="F15" s="7">
         <f>VLOOKUP(A15,原表!$A$4:$B$25,2,0)</f>
@@ -2919,7 +4163,7 @@
       </c>
       <c r="G15" s="74">
         <f t="shared" si="2"/>
-        <v>0.24094569481726202</v>
+        <v>0.36731461215500039</v>
       </c>
       <c r="H15" s="7">
         <f>VLOOKUP(A15,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2927,29 +4171,30 @@
       </c>
       <c r="I15" s="74">
         <f t="shared" si="3"/>
-        <v>0.26504056833524714</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>0.40404653686481851</v>
+      </c>
+      <c r="K15" s="103"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2" t="str">
         <f>粽子销售PICKUP!A16</f>
         <v>上海康莱德</v>
       </c>
       <c r="B16" s="7">
-        <f>粽子销售PICKUP!D16</f>
-        <v>52842</v>
+        <f>粽子销售PICKUP!F16</f>
+        <v>91590</v>
       </c>
       <c r="C16" s="7">
-        <f>粽子销售PICKUP!E16</f>
-        <v>27139</v>
+        <f>粽子销售PICKUP!G16</f>
+        <v>148161</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-25703</v>
+        <v>56571</v>
       </c>
       <c r="E16" s="22">
         <f t="shared" si="1"/>
-        <v>-0.48641232353052499</v>
+        <v>0.61765476580412715</v>
       </c>
       <c r="F16" s="7">
         <f>VLOOKUP(A16,原表!$A$4:$B$25,2,0)</f>
@@ -2957,7 +4202,7 @@
       </c>
       <c r="G16" s="74">
         <f t="shared" si="2"/>
-        <v>0.12540316245714234</v>
+        <v>0.68461837034572626</v>
       </c>
       <c r="H16" s="7">
         <f>VLOOKUP(A16,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -2965,29 +4210,30 @@
       </c>
       <c r="I16" s="74">
         <f t="shared" si="3"/>
-        <v>0.13794347870285656</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>0.7530802073802989</v>
+      </c>
+      <c r="K16" s="103"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2" t="str">
         <f>粽子销售PICKUP!A17</f>
         <v>厦门康莱德</v>
       </c>
       <c r="B17" s="7">
-        <f>粽子销售PICKUP!D17</f>
-        <v>13896</v>
+        <f>粽子销售PICKUP!F17</f>
+        <v>134945</v>
       </c>
       <c r="C17" s="7">
-        <f>粽子销售PICKUP!E17</f>
-        <v>18146.2</v>
+        <f>粽子销售PICKUP!G17</f>
+        <v>125466</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>4250.2000000000007</v>
+        <v>-9479</v>
       </c>
       <c r="E17" s="22">
         <f t="shared" si="1"/>
-        <v>0.30585780080598735</v>
+        <v>-7.0243432509540904E-2</v>
       </c>
       <c r="F17" s="7">
         <f>VLOOKUP(A17,原表!$A$4:$B$25,2,0)</f>
@@ -2995,7 +4241,7 @@
       </c>
       <c r="G17" s="74">
         <f t="shared" si="2"/>
-        <v>3.6867458619547704E-2</v>
+        <v>0.25490805585522985</v>
       </c>
       <c r="H17" s="7">
         <f>VLOOKUP(A17,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3003,29 +4249,30 @@
       </c>
       <c r="I17" s="74">
         <f t="shared" si="3"/>
-        <v>4.0554245678336369E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>0.28039914628286644</v>
+      </c>
+      <c r="K17" s="103"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2" t="str">
         <f>粽子销售PICKUP!A18</f>
         <v>宁波双店</v>
       </c>
       <c r="B18" s="7">
-        <f>粽子销售PICKUP!D18</f>
-        <v>4068</v>
+        <f>粽子销售PICKUP!F18</f>
+        <v>109140</v>
       </c>
       <c r="C18" s="7">
-        <f>粽子销售PICKUP!E18</f>
-        <v>48850</v>
+        <f>粽子销售PICKUP!G18</f>
+        <v>103766</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>44782</v>
+        <v>-5374</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="1"/>
-        <v>11.008357915437561</v>
+        <v>-4.923950888766726E-2</v>
       </c>
       <c r="F18" s="7">
         <f>VLOOKUP(A18,原表!$A$4:$B$25,2,0)</f>
@@ -3033,7 +4280,7 @@
       </c>
       <c r="G18" s="74">
         <f t="shared" si="2"/>
-        <v>0.14074443288781069</v>
+        <v>0.29896595338867071</v>
       </c>
       <c r="H18" s="7">
         <f>VLOOKUP(A18,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3041,29 +4288,30 @@
       </c>
       <c r="I18" s="74">
         <f t="shared" si="3"/>
-        <v>0.15481887617659176</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>0.32886254872753778</v>
+      </c>
+      <c r="K18" s="103"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2" t="str">
         <f>粽子销售PICKUP!A19</f>
         <v>南京希尔顿</v>
       </c>
       <c r="B19" s="7">
-        <f>粽子销售PICKUP!D19</f>
-        <v>54347</v>
+        <f>粽子销售PICKUP!F19</f>
+        <v>383704</v>
       </c>
       <c r="C19" s="7">
-        <f>粽子销售PICKUP!E19</f>
-        <v>476520</v>
+        <f>粽子销售PICKUP!G19</f>
+        <v>744088</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>422173</v>
+        <v>360384</v>
       </c>
       <c r="E19" s="22">
         <f t="shared" si="1"/>
-        <v>7.768101275139383</v>
+        <v>0.93922398515522376</v>
       </c>
       <c r="F19" s="7">
         <f>VLOOKUP(A19,原表!$A$4:$B$25,2,0)</f>
@@ -3071,7 +4319,7 @@
       </c>
       <c r="G19" s="74">
         <f t="shared" si="2"/>
-        <v>0.47652</v>
+        <v>0.74408799999999997</v>
       </c>
       <c r="H19" s="7">
         <f>VLOOKUP(A19,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3079,29 +4327,30 @@
       </c>
       <c r="I19" s="74">
         <f t="shared" si="3"/>
-        <v>0.61732965282980001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>0.96396286979522416</v>
+      </c>
+      <c r="K19" s="103"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2" t="str">
         <f>粽子销售PICKUP!A20</f>
         <v>牡丹江假日</v>
       </c>
       <c r="B20" s="7">
-        <f>粽子销售PICKUP!D20</f>
-        <v>8580</v>
+        <f>粽子销售PICKUP!F20</f>
+        <v>11760</v>
       </c>
       <c r="C20" s="7">
-        <f>粽子销售PICKUP!E20</f>
-        <v>37118</v>
+        <f>粽子销售PICKUP!G20</f>
+        <v>59635</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>28538</v>
+        <v>47875</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" si="1"/>
-        <v>3.3261072261072258</v>
+        <v>4.0710034013605441</v>
       </c>
       <c r="F20" s="7">
         <f>VLOOKUP(A20,原表!$A$4:$B$25,2,0)</f>
@@ -3109,7 +4358,7 @@
       </c>
       <c r="G20" s="74">
         <f t="shared" si="2"/>
-        <v>0.26512857142857144</v>
+        <v>0.42596428571428574</v>
       </c>
       <c r="H20" s="7">
         <f>VLOOKUP(A20,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3117,29 +4366,30 @@
       </c>
       <c r="I20" s="74">
         <f t="shared" si="3"/>
-        <v>0.40856806348996688</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>0.6564188928881991</v>
+      </c>
+      <c r="K20" s="103"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="str">
         <f>粽子销售PICKUP!A21</f>
         <v>虹桥睿选尚品</v>
       </c>
       <c r="B21" s="7">
-        <f>粽子销售PICKUP!D21</f>
-        <v>11200</v>
+        <f>粽子销售PICKUP!F21</f>
+        <v>23368</v>
       </c>
       <c r="C21" s="7">
-        <f>粽子销售PICKUP!E21</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!G21</f>
+        <v>18607</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-11200</v>
+        <v>-4761</v>
       </c>
       <c r="E21" s="22">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.20374015748031493</v>
       </c>
       <c r="F21" s="7">
         <f>VLOOKUP(A21,原表!$A$4:$B$25,2,0)</f>
@@ -3147,7 +4397,7 @@
       </c>
       <c r="G21" s="74">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30755371900826445</v>
       </c>
       <c r="H21" s="7">
         <f>VLOOKUP(A21,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3155,29 +4405,30 @@
       </c>
       <c r="I21" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>0.33830909090909089</v>
+      </c>
+      <c r="K21" s="103"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="str">
         <f>粽子销售PICKUP!A22</f>
         <v>杭州艾美</v>
       </c>
       <c r="B22" s="7">
-        <f>粽子销售PICKUP!D22</f>
-        <v>24966.04</v>
+        <f>粽子销售PICKUP!F22</f>
+        <v>45398</v>
       </c>
       <c r="C22" s="7">
-        <f>粽子销售PICKUP!E22</f>
-        <v>90033.11</v>
+        <f>粽子销售PICKUP!G22</f>
+        <v>136029.26999999999</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>65067.07</v>
+        <v>90631.26999999999</v>
       </c>
       <c r="E22" s="22">
         <f t="shared" si="1"/>
-        <v>2.6062230934501427</v>
+        <v>1.9963714260540111</v>
       </c>
       <c r="F22" s="7">
         <f>VLOOKUP(A22,原表!$A$4:$B$25,2,0)</f>
@@ -3185,7 +4436,7 @@
       </c>
       <c r="G22" s="74">
         <f t="shared" si="2"/>
-        <v>0.31466795516582147</v>
+        <v>0.47542567654943185</v>
       </c>
       <c r="H22" s="7">
         <f>VLOOKUP(A22,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3193,29 +4444,30 @@
       </c>
       <c r="I22" s="74">
         <f t="shared" si="3"/>
-        <v>0.34613475068240362</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>0.52296824420437504</v>
+      </c>
+      <c r="K22" s="103"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2" t="str">
         <f>粽子销售PICKUP!A23</f>
         <v>福州洲际</v>
       </c>
       <c r="B23" s="7">
-        <f>粽子销售PICKUP!D23</f>
-        <v>65282.02</v>
+        <f>粽子销售PICKUP!F23</f>
+        <v>116328</v>
       </c>
       <c r="C23" s="7">
-        <f>粽子销售PICKUP!E23</f>
-        <v>166704</v>
+        <f>粽子销售PICKUP!G23</f>
+        <v>240779</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>101421.98000000001</v>
+        <v>124451</v>
       </c>
       <c r="E23" s="22">
         <f t="shared" si="1"/>
-        <v>1.5535974530199894</v>
+        <v>1.0698284162024621</v>
       </c>
       <c r="F23" s="7">
         <f>VLOOKUP(A23,原表!$A$4:$B$25,2,0)</f>
@@ -3223,7 +4475,7 @@
       </c>
       <c r="G23" s="74">
         <f t="shared" si="2"/>
-        <v>0.41676000000000002</v>
+        <v>0.60194749999999997</v>
       </c>
       <c r="H23" s="7">
         <f>VLOOKUP(A23,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3231,29 +4483,30 @@
       </c>
       <c r="I23" s="74">
         <f t="shared" si="3"/>
-        <v>0.47503490724645941</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>0.68611688940814408</v>
+      </c>
+      <c r="K23" s="103"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2" t="str">
         <f>粽子销售PICKUP!A24</f>
         <v>成都茂御</v>
       </c>
       <c r="B24" s="7">
-        <f>粽子销售PICKUP!D24</f>
-        <v>15350</v>
+        <f>粽子销售PICKUP!F24</f>
+        <v>46157</v>
       </c>
       <c r="C24" s="7">
-        <f>粽子销售PICKUP!E24</f>
-        <v>109815</v>
+        <f>粽子销售PICKUP!G24</f>
+        <v>133025</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>94465</v>
+        <v>86868</v>
       </c>
       <c r="E24" s="22">
         <f t="shared" si="1"/>
-        <v>6.1540716612377846</v>
+        <v>1.8820113958879476</v>
       </c>
       <c r="F24" s="7">
         <f>VLOOKUP(A24,原表!$A$4:$B$25,2,0)</f>
@@ -3261,7 +4514,7 @@
       </c>
       <c r="G24" s="74">
         <f t="shared" si="2"/>
-        <v>0.33459270882527686</v>
+        <v>0.40531070519949419</v>
       </c>
       <c r="H24" s="7">
         <f>VLOOKUP(A24,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3269,29 +4522,30 @@
       </c>
       <c r="I24" s="74">
         <f t="shared" si="3"/>
-        <v>0.36805220398970401</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>0.44584204740454741</v>
+      </c>
+      <c r="K24" s="103"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2" t="str">
         <f>粽子销售PICKUP!A25</f>
         <v>成都龙泉驿睿选</v>
       </c>
       <c r="B25" s="7">
-        <f>粽子销售PICKUP!D25</f>
-        <v>3126</v>
+        <f>粽子销售PICKUP!F25</f>
+        <v>4584</v>
       </c>
       <c r="C25" s="7">
-        <f>粽子销售PICKUP!E25</f>
-        <v>15494</v>
+        <f>粽子销售PICKUP!G25</f>
+        <v>15844</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>12368</v>
+        <v>11260</v>
       </c>
       <c r="E25" s="22">
         <f t="shared" si="1"/>
-        <v>3.9564939219449773</v>
+        <v>2.4563699825479932</v>
       </c>
       <c r="F25" s="7">
         <f>VLOOKUP(A25,原表!$A$4:$B$25,2,0)</f>
@@ -3299,7 +4553,7 @@
       </c>
       <c r="G25" s="74">
         <f t="shared" si="2"/>
-        <v>0.48892395077311457</v>
+        <v>0.4999684443041969</v>
       </c>
       <c r="H25" s="7">
         <f>VLOOKUP(A25,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3307,28 +4561,29 @@
       </c>
       <c r="I25" s="74">
         <f t="shared" si="3"/>
-        <v>0.5378180429726821</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>0.54996702419382837</v>
+      </c>
+      <c r="K25" s="103"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="77">
         <f>SUM(B4:B25)</f>
-        <v>1747396.2060000002</v>
+        <v>3593461.8099999996</v>
       </c>
       <c r="C26" s="77">
         <f>SUM(C4:C25)</f>
-        <v>3195708.93</v>
+        <v>5083236.0999999996</v>
       </c>
       <c r="D26" s="78">
         <f t="shared" si="0"/>
-        <v>1448312.7239999999</v>
+        <v>1489774.29</v>
       </c>
       <c r="E26" s="79">
         <f t="shared" si="1"/>
-        <v>0.82884048793682674</v>
+        <v>0.41457913532132418</v>
       </c>
       <c r="F26" s="77">
         <f>SUM(F4:F25)</f>
@@ -3336,7 +4591,7 @@
       </c>
       <c r="G26" s="80">
         <f t="shared" si="2"/>
-        <v>0.3573522849426144</v>
+        <v>0.56842036462869716</v>
       </c>
       <c r="H26" s="77">
         <f>SUM(H4:H25)</f>
@@ -3344,10 +4599,11 @@
       </c>
       <c r="I26" s="80">
         <f t="shared" si="3"/>
-        <v>0.39322641661180324</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>0.62548334663093297</v>
+      </c>
+      <c r="K26" s="103"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="14"/>
@@ -3371,6 +4627,1321 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" style="94" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.265625" style="94" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="94" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.3984375" style="85" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="85" customWidth="1"/>
+    <col min="8" max="8" width="16" style="85" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.59765625" style="85" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" style="90" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.3984375" style="90" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1328125" style="85"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="81" customFormat="1">
+      <c r="A1" s="119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+    </row>
+    <row r="2" spans="1:15" s="82" customFormat="1">
+      <c r="A2" s="120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="121"/>
+      <c r="E2" s="119" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="119"/>
+      <c r="M2" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="122" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="122" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="82" customFormat="1">
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="102" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="102" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="102" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="118"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7">
+        <v>400000</v>
+      </c>
+      <c r="C4" s="7">
+        <v>4028</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1584</v>
+      </c>
+      <c r="E4" s="1">
+        <v>8868</v>
+      </c>
+      <c r="F4" s="99">
+        <v>29894</v>
+      </c>
+      <c r="G4" s="1">
+        <v>14718</v>
+      </c>
+      <c r="H4" s="124">
+        <v>102982</v>
+      </c>
+      <c r="I4" s="1">
+        <v>307977</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>385967</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0</v>
+      </c>
+      <c r="M4" s="83">
+        <f t="shared" ref="M4:M25" si="0">H4/G4</f>
+        <v>6.9970104633781762</v>
+      </c>
+      <c r="N4" s="84">
+        <f t="shared" ref="N4:N25" si="1">H4/K4</f>
+        <v>0.26681555677039748</v>
+      </c>
+      <c r="O4" s="84">
+        <f t="shared" ref="O4:O25" si="2">H4/B4</f>
+        <v>0.25745499999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7">
+        <v>140000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5040</v>
+      </c>
+      <c r="D5" s="7">
+        <v>24998</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8580</v>
+      </c>
+      <c r="F5" s="99">
+        <v>37118</v>
+      </c>
+      <c r="G5" s="1">
+        <v>11760</v>
+      </c>
+      <c r="H5" s="124">
+        <v>59635</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46814</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>106127</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="83">
+        <f t="shared" si="0"/>
+        <v>5.0710034013605441</v>
+      </c>
+      <c r="N5" s="84">
+        <f t="shared" si="1"/>
+        <v>0.56192109453767658</v>
+      </c>
+      <c r="O5" s="84">
+        <f t="shared" si="2"/>
+        <v>0.42596428571428574</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7">
+        <v>22777</v>
+      </c>
+      <c r="C6" s="7">
+        <f>128*4</f>
+        <v>512</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2688</v>
+      </c>
+      <c r="F6" s="99">
+        <v>5082</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2688</v>
+      </c>
+      <c r="H6" s="124">
+        <v>10991</v>
+      </c>
+      <c r="I6" s="1">
+        <v>22246</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>23526</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="83">
+        <f t="shared" si="0"/>
+        <v>4.0889136904761907</v>
+      </c>
+      <c r="N6" s="84">
+        <f t="shared" si="1"/>
+        <v>0.46718524186006971</v>
+      </c>
+      <c r="O6" s="84">
+        <f t="shared" si="2"/>
+        <v>0.48254818457215615</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7">
+        <v>31690</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1984</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1221</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3126</v>
+      </c>
+      <c r="F7" s="99">
+        <v>15494</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4584</v>
+      </c>
+      <c r="H7" s="124">
+        <v>15844</v>
+      </c>
+      <c r="I7" s="1">
+        <v>19424</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>28809</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="83">
+        <f t="shared" si="0"/>
+        <v>3.4563699825479932</v>
+      </c>
+      <c r="N7" s="84">
+        <f t="shared" si="1"/>
+        <v>0.54996702419382837</v>
+      </c>
+      <c r="O7" s="84">
+        <f t="shared" si="2"/>
+        <v>0.4999684443041969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7">
+        <v>286121</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1146.9000000000001</v>
+      </c>
+      <c r="D8" s="7">
+        <v>26904</v>
+      </c>
+      <c r="E8" s="1">
+        <v>24966.04</v>
+      </c>
+      <c r="F8" s="98">
+        <v>90033.11</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45398</v>
+      </c>
+      <c r="H8" s="125">
+        <v>136029.26999999999</v>
+      </c>
+      <c r="I8" s="1">
+        <v>160280</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>258783.18</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="83">
+        <f t="shared" si="0"/>
+        <v>2.9963714260540111</v>
+      </c>
+      <c r="N8" s="84">
+        <f t="shared" si="1"/>
+        <v>0.52564958047118826</v>
+      </c>
+      <c r="O8" s="84">
+        <f t="shared" si="2"/>
+        <v>0.47542567654943185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7">
+        <v>328205</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3016</v>
+      </c>
+      <c r="D9" s="7">
+        <v>66814</v>
+      </c>
+      <c r="E9" s="1">
+        <v>15350</v>
+      </c>
+      <c r="F9" s="99">
+        <v>109815</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H9" s="124">
+        <v>133025</v>
+      </c>
+      <c r="I9" s="1">
+        <v>207772</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>791907</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="83">
+        <f t="shared" si="0"/>
+        <v>2.8820113958879476</v>
+      </c>
+      <c r="N9" s="84">
+        <f t="shared" si="1"/>
+        <v>0.1679805835786273</v>
+      </c>
+      <c r="O9" s="84">
+        <f t="shared" si="2"/>
+        <v>0.40531070519949419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.75">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7">
+        <v>605910</v>
+      </c>
+      <c r="C10" s="7">
+        <v>28123.89</v>
+      </c>
+      <c r="D10" s="7">
+        <v>53385</v>
+      </c>
+      <c r="E10" s="1">
+        <v>46657</v>
+      </c>
+      <c r="F10" s="99">
+        <v>279964</v>
+      </c>
+      <c r="G10" s="1">
+        <v>207865</v>
+      </c>
+      <c r="H10" s="124">
+        <v>500173</v>
+      </c>
+      <c r="I10" s="1">
+        <v>330575</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>570761</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="83">
+        <f t="shared" si="0"/>
+        <v>2.4062396266807782</v>
+      </c>
+      <c r="N10" s="84">
+        <f t="shared" si="1"/>
+        <v>0.87632651845518528</v>
+      </c>
+      <c r="O10" s="84">
+        <f t="shared" si="2"/>
+        <v>0.82549058441022594</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7">
+        <v>400000</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>73676</v>
+      </c>
+      <c r="E11" s="1">
+        <v>65282.02</v>
+      </c>
+      <c r="F11" s="99">
+        <v>166704</v>
+      </c>
+      <c r="G11" s="1">
+        <v>116328</v>
+      </c>
+      <c r="H11" s="124">
+        <v>240779</v>
+      </c>
+      <c r="I11" s="8">
+        <v>306475</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>381478</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="83">
+        <f t="shared" si="0"/>
+        <v>2.0698284162024621</v>
+      </c>
+      <c r="N11" s="84">
+        <f t="shared" si="1"/>
+        <v>0.63117401265603779</v>
+      </c>
+      <c r="O11" s="84">
+        <f t="shared" si="2"/>
+        <v>0.60194749999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.75">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1088112</v>
+      </c>
+      <c r="C12" s="7">
+        <v>25694</v>
+      </c>
+      <c r="D12" s="7">
+        <v>144015</v>
+      </c>
+      <c r="E12" s="1">
+        <v>111210</v>
+      </c>
+      <c r="F12" s="126">
+        <v>391500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>362901.92</v>
+      </c>
+      <c r="H12" s="127">
+        <v>725000</v>
+      </c>
+      <c r="I12" s="1">
+        <v>913227</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1082590</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="83">
+        <f t="shared" si="0"/>
+        <v>1.9977849662520386</v>
+      </c>
+      <c r="N12" s="84">
+        <f t="shared" si="1"/>
+        <v>0.66969027979198037</v>
+      </c>
+      <c r="O12" s="84">
+        <f t="shared" si="2"/>
+        <v>0.66629170526563442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.75">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7">
+        <v>435870</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4590</v>
+      </c>
+      <c r="D13" s="7">
+        <v>25787</v>
+      </c>
+      <c r="E13" s="1">
+        <v>21562</v>
+      </c>
+      <c r="F13" s="98">
+        <v>105021</v>
+      </c>
+      <c r="G13" s="1">
+        <v>81341</v>
+      </c>
+      <c r="H13" s="124">
+        <v>160101.42000000001</v>
+      </c>
+      <c r="I13" s="1">
+        <v>281954</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>394853</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="83">
+        <f t="shared" si="0"/>
+        <v>1.9682745478909776</v>
+      </c>
+      <c r="N13" s="84">
+        <f t="shared" si="1"/>
+        <v>0.40547094741587381</v>
+      </c>
+      <c r="O13" s="84">
+        <f t="shared" si="2"/>
+        <v>0.36731461215500039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7">
+        <v>120000</v>
+      </c>
+      <c r="C14" s="7">
+        <v>10261.700000000001</v>
+      </c>
+      <c r="D14" s="7">
+        <v>94983</v>
+      </c>
+      <c r="E14" s="1">
+        <v>46531.88</v>
+      </c>
+      <c r="F14" s="98">
+        <v>132578</v>
+      </c>
+      <c r="G14" s="1">
+        <v>84571.199999999997</v>
+      </c>
+      <c r="H14" s="124">
+        <v>165319</v>
+      </c>
+      <c r="I14" s="1">
+        <v>93456</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>126966</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0</v>
+      </c>
+      <c r="M14" s="83">
+        <f t="shared" si="0"/>
+        <v>1.954790756191233</v>
+      </c>
+      <c r="N14" s="84">
+        <f t="shared" si="1"/>
+        <v>1.3020729959201676</v>
+      </c>
+      <c r="O14" s="84">
+        <f t="shared" si="2"/>
+        <v>1.3776583333333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.75">
+      <c r="A15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2474</v>
+      </c>
+      <c r="D15" s="7">
+        <v>196331</v>
+      </c>
+      <c r="E15" s="1">
+        <v>54347</v>
+      </c>
+      <c r="F15" s="99">
+        <v>476520</v>
+      </c>
+      <c r="G15" s="1">
+        <v>383704</v>
+      </c>
+      <c r="H15" s="124">
+        <v>744088</v>
+      </c>
+      <c r="I15" s="1">
+        <v>641549</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>771615</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0</v>
+      </c>
+      <c r="M15" s="83">
+        <f t="shared" si="0"/>
+        <v>1.9392239851552238</v>
+      </c>
+      <c r="N15" s="84">
+        <f t="shared" si="1"/>
+        <v>0.96432547319582951</v>
+      </c>
+      <c r="O15" s="84">
+        <f t="shared" si="2"/>
+        <v>0.74408799999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.75">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7">
+        <v>216414</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3500</v>
+      </c>
+      <c r="D16" s="7">
+        <v>27139</v>
+      </c>
+      <c r="E16" s="1">
+        <v>52842</v>
+      </c>
+      <c r="F16" s="99">
+        <v>27139</v>
+      </c>
+      <c r="G16" s="1">
+        <v>91590</v>
+      </c>
+      <c r="H16" s="128">
+        <v>148161</v>
+      </c>
+      <c r="I16" s="1">
+        <v>151692</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>218934</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="83">
+        <f t="shared" si="0"/>
+        <v>1.6176547658041271</v>
+      </c>
+      <c r="N16" s="84">
+        <f t="shared" si="1"/>
+        <v>0.67673819507248756</v>
+      </c>
+      <c r="O16" s="84">
+        <f t="shared" si="2"/>
+        <v>0.68461837034572626</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7">
+        <v>316098</v>
+      </c>
+      <c r="C17" s="7">
+        <v>32322</v>
+      </c>
+      <c r="D17" s="7">
+        <v>7240</v>
+      </c>
+      <c r="E17" s="1">
+        <v>54270.796000000002</v>
+      </c>
+      <c r="F17" s="99">
+        <v>7240</v>
+      </c>
+      <c r="G17" s="1">
+        <v>85480</v>
+      </c>
+      <c r="H17" s="124">
+        <v>105528</v>
+      </c>
+      <c r="I17" s="1">
+        <v>235524</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>235524</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="83">
+        <f t="shared" si="0"/>
+        <v>1.2345343940102949</v>
+      </c>
+      <c r="N17" s="84">
+        <f t="shared" si="1"/>
+        <v>0.44805624904468333</v>
+      </c>
+      <c r="O17" s="84">
+        <f t="shared" si="2"/>
+        <v>0.33384583262152878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75">
+      <c r="A18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1250069</v>
+      </c>
+      <c r="C18" s="7">
+        <v>157000</v>
+      </c>
+      <c r="D18" s="7">
+        <v>120850</v>
+      </c>
+      <c r="E18" s="1">
+        <v>297052</v>
+      </c>
+      <c r="F18" s="99">
+        <v>820850</v>
+      </c>
+      <c r="G18" s="1">
+        <v>845294.69</v>
+      </c>
+      <c r="H18" s="124">
+        <v>1001903</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1083892</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1083892</v>
+      </c>
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="83">
+        <f t="shared" si="0"/>
+        <v>1.185270665784024</v>
+      </c>
+      <c r="N18" s="84">
+        <f t="shared" si="1"/>
+        <v>0.92435685474198537</v>
+      </c>
+      <c r="O18" s="84">
+        <f t="shared" si="2"/>
+        <v>0.80147815840565606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.75">
+      <c r="A19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="7">
+        <v>272323</v>
+      </c>
+      <c r="C19" s="7">
+        <v>7436</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2900</v>
+      </c>
+      <c r="E19" s="1">
+        <v>76162</v>
+      </c>
+      <c r="F19" s="99">
+        <v>25000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>79866</v>
+      </c>
+      <c r="H19" s="124">
+        <v>78056</v>
+      </c>
+      <c r="I19" s="1">
+        <v>110615</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>160299.12</v>
+      </c>
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="83">
+        <f t="shared" si="0"/>
+        <v>0.97733703954123152</v>
+      </c>
+      <c r="N19" s="84">
+        <f t="shared" si="1"/>
+        <v>0.48693966629386365</v>
+      </c>
+      <c r="O19" s="84">
+        <f t="shared" si="2"/>
+        <v>0.28663021485515361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75">
+      <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="7">
+        <v>173348</v>
+      </c>
+      <c r="C20" s="7">
+        <v>76390.25</v>
+      </c>
+      <c r="D20" s="7">
+        <v>90335</v>
+      </c>
+      <c r="E20" s="1">
+        <v>104565.47</v>
+      </c>
+      <c r="F20" s="99">
+        <v>119613.62</v>
+      </c>
+      <c r="G20" s="1">
+        <v>131239</v>
+      </c>
+      <c r="H20" s="124">
+        <v>127724.41</v>
+      </c>
+      <c r="I20" s="1">
+        <v>152953.26</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>157588</v>
+      </c>
+      <c r="L20" s="7">
+        <v>0</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="0"/>
+        <v>0.97321992700340598</v>
+      </c>
+      <c r="N20" s="84">
+        <f t="shared" si="1"/>
+        <v>0.81049578648120413</v>
+      </c>
+      <c r="O20" s="84">
+        <f t="shared" si="2"/>
+        <v>0.73680925075570536</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75">
+      <c r="A21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="7">
+        <v>347083</v>
+      </c>
+      <c r="C21" s="7">
+        <v>540</v>
+      </c>
+      <c r="D21" s="7">
+        <v>11300</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4068</v>
+      </c>
+      <c r="F21" s="126">
+        <v>48850</v>
+      </c>
+      <c r="G21" s="7">
+        <v>109140</v>
+      </c>
+      <c r="H21" s="124">
+        <v>103766</v>
+      </c>
+      <c r="I21" s="7">
+        <v>232119</v>
+      </c>
+      <c r="J21" s="7">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
+        <v>339444</v>
+      </c>
+      <c r="L21" s="7">
+        <v>0</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="0"/>
+        <v>0.95076049111233274</v>
+      </c>
+      <c r="N21" s="84">
+        <f t="shared" si="1"/>
+        <v>0.30569401727530904</v>
+      </c>
+      <c r="O21" s="84">
+        <f t="shared" si="2"/>
+        <v>0.29896595338867071</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.75">
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="7">
+        <v>492201</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7">
+        <v>780</v>
+      </c>
+      <c r="E22" s="1">
+        <v>13896</v>
+      </c>
+      <c r="F22" s="99">
+        <v>18146.2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>134945</v>
+      </c>
+      <c r="H22" s="124">
+        <v>125466</v>
+      </c>
+      <c r="I22" s="1">
+        <v>227158.2</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>505624.7</v>
+      </c>
+      <c r="L22" s="7">
+        <v>0</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="0"/>
+        <v>0.9297565674904591</v>
+      </c>
+      <c r="N22" s="84">
+        <f t="shared" si="1"/>
+        <v>0.24814056749996588</v>
+      </c>
+      <c r="O22" s="84">
+        <f t="shared" si="2"/>
+        <v>0.25490805585522985</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="135" customFormat="1" ht="15.75">
+      <c r="A23" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="130">
+        <v>60500</v>
+      </c>
+      <c r="C23" s="130">
+        <v>5713</v>
+      </c>
+      <c r="D23" s="130">
+        <v>0</v>
+      </c>
+      <c r="E23" s="130">
+        <v>11200</v>
+      </c>
+      <c r="F23" s="131">
+        <v>0</v>
+      </c>
+      <c r="G23" s="130">
+        <v>23368</v>
+      </c>
+      <c r="H23" s="132">
+        <v>18607</v>
+      </c>
+      <c r="I23" s="130">
+        <v>29237</v>
+      </c>
+      <c r="J23" s="130">
+        <v>0</v>
+      </c>
+      <c r="K23" s="130">
+        <v>60308</v>
+      </c>
+      <c r="L23" s="130">
+        <v>0</v>
+      </c>
+      <c r="M23" s="133">
+        <f t="shared" si="0"/>
+        <v>0.79625984251968507</v>
+      </c>
+      <c r="N23" s="134">
+        <f t="shared" si="1"/>
+        <v>0.3085328646282417</v>
+      </c>
+      <c r="O23" s="134">
+        <f t="shared" si="2"/>
+        <v>0.30755371900826445</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="135" customFormat="1" ht="15.75">
+      <c r="A24" s="129" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="130">
+        <v>945837</v>
+      </c>
+      <c r="C24" s="130">
+        <v>15909</v>
+      </c>
+      <c r="D24" s="130">
+        <v>265486</v>
+      </c>
+      <c r="E24" s="130">
+        <v>724172</v>
+      </c>
+      <c r="F24" s="136">
+        <v>289147</v>
+      </c>
+      <c r="G24" s="130">
+        <v>728417</v>
+      </c>
+      <c r="H24" s="137">
+        <v>380058</v>
+      </c>
+      <c r="I24" s="130">
+        <v>808858</v>
+      </c>
+      <c r="J24" s="130">
+        <v>0</v>
+      </c>
+      <c r="K24" s="130">
+        <v>909183</v>
+      </c>
+      <c r="L24" s="130">
+        <v>0</v>
+      </c>
+      <c r="M24" s="133">
+        <f t="shared" si="0"/>
+        <v>0.52175882770446047</v>
+      </c>
+      <c r="N24" s="134">
+        <f t="shared" si="1"/>
+        <v>0.41802145442666661</v>
+      </c>
+      <c r="O24" s="134">
+        <f t="shared" si="2"/>
+        <v>0.40182187839976657</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="135" customFormat="1">
+      <c r="A25" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="130">
+        <v>10183</v>
+      </c>
+      <c r="C25" s="130">
+        <v>0</v>
+      </c>
+      <c r="D25" s="130">
+        <v>0</v>
+      </c>
+      <c r="E25" s="130">
+        <v>0</v>
+      </c>
+      <c r="F25" s="131">
+        <v>0</v>
+      </c>
+      <c r="G25" s="130">
+        <v>2106</v>
+      </c>
+      <c r="H25" s="138">
+        <v>0</v>
+      </c>
+      <c r="I25" s="130">
+        <v>3160</v>
+      </c>
+      <c r="J25" s="130">
+        <v>0</v>
+      </c>
+      <c r="K25" s="130">
+        <v>3160</v>
+      </c>
+      <c r="L25" s="130">
+        <v>0</v>
+      </c>
+      <c r="M25" s="133">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="134">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="86"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="89"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="91"/>
+      <c r="B27" s="92">
+        <f t="shared" ref="B27:L27" si="3">SUM(B4:B25)</f>
+        <v>8942741</v>
+      </c>
+      <c r="C27" s="92">
+        <f t="shared" si="3"/>
+        <v>385680.74</v>
+      </c>
+      <c r="D27" s="92">
+        <f t="shared" si="3"/>
+        <v>1235728</v>
+      </c>
+      <c r="E27" s="92">
+        <f t="shared" si="3"/>
+        <v>1747396.206</v>
+      </c>
+      <c r="F27" s="93">
+        <f t="shared" si="3"/>
+        <v>3195708.93</v>
+      </c>
+      <c r="G27" s="92">
+        <f t="shared" si="3"/>
+        <v>3593461.8099999996</v>
+      </c>
+      <c r="H27" s="92">
+        <f t="shared" si="3"/>
+        <v>5083236.0999999996</v>
+      </c>
+      <c r="I27" s="92">
+        <f t="shared" si="3"/>
+        <v>6366957.46</v>
+      </c>
+      <c r="J27" s="92">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="92">
+        <f t="shared" si="3"/>
+        <v>8597339</v>
+      </c>
+      <c r="L27" s="92">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="90">
+        <f>H27/G27</f>
+        <v>1.4145791353213242</v>
+      </c>
+      <c r="N27" s="90">
+        <f>H27/K27</f>
+        <v>0.59125691100467248</v>
+      </c>
+      <c r="O27" s="90">
+        <f>H27/B27</f>
+        <v>0.56842036462869716</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="90" customFormat="1">
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:C24"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
@@ -3572,7 +6143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -3600,56 +6171,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="26" customFormat="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
       <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:15" s="27" customFormat="1">
-      <c r="A2" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="111" t="s">
+      <c r="A2" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112" t="s">
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="s">
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="106" t="s">
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="109" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="27" customFormat="1" ht="27.75">
-      <c r="A3" s="110"/>
-      <c r="B3" s="111"/>
+      <c r="A3" s="113"/>
+      <c r="B3" s="114"/>
       <c r="C3" s="28" t="s">
         <v>52</v>
       </c>
@@ -3686,7 +6257,7 @@
       <c r="N3" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="106"/>
+      <c r="O3" s="109"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="34">
@@ -4894,8 +7465,8 @@
       <c r="O26" s="62"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="107"/>
-      <c r="B27" s="108"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="111"/>
       <c r="C27" s="64">
         <f>SUM(C4:C25)</f>
         <v>102490</v>
@@ -4971,7 +7542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15"/>
@@ -4982,76 +7553,76 @@
     <col min="4" max="4" width="15.59765625" style="85" customWidth="1"/>
     <col min="5" max="5" width="14.3984375" style="85" customWidth="1"/>
     <col min="6" max="6" width="17.1328125" style="85" customWidth="1"/>
-    <col min="7" max="7" width="15.59765625" style="85" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="85" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" style="85" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1328125" style="85" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.59765625" style="85" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="85" customWidth="1"/>
+    <col min="8" max="8" width="16" style="85" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="85" customWidth="1"/>
+    <col min="10" max="10" width="17.1328125" style="85" customWidth="1"/>
+    <col min="11" max="11" width="15.59765625" style="85" customWidth="1"/>
+    <col min="12" max="12" width="17.1328125" style="85" customWidth="1"/>
     <col min="13" max="13" width="10.73046875" style="90" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="14.86328125" style="90" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9.1328125" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="81" customFormat="1">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
     </row>
     <row r="2" spans="1:15" s="82" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="118"/>
-      <c r="E2" s="116" t="s">
+      <c r="D2" s="121"/>
+      <c r="E2" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116" t="s">
+      <c r="F2" s="119"/>
+      <c r="G2" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116" t="s">
+      <c r="H2" s="119"/>
+      <c r="I2" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116" t="s">
+      <c r="J2" s="119"/>
+      <c r="K2" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="116"/>
-      <c r="M2" s="114" t="s">
+      <c r="L2" s="119"/>
+      <c r="M2" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="114" t="s">
+      <c r="N2" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="114" t="s">
+      <c r="O2" s="117" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="82" customFormat="1">
-      <c r="A3" s="117"/>
-      <c r="B3" s="117"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="97" t="s">
         <v>22</v>
       </c>
@@ -5082,9 +7653,9 @@
       <c r="L3" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
+      <c r="M3" s="118"/>
+      <c r="N3" s="118"/>
+      <c r="O3" s="118"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
@@ -5109,7 +7680,8 @@
         <v>84571.199999999997</v>
       </c>
       <c r="H4" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A4,Sheet1!$A$4:$H$25,COLUMN(H1),0)</f>
+        <v>165319</v>
       </c>
       <c r="I4" s="1">
         <v>93456</v>
@@ -5159,7 +7731,8 @@
         <v>131239</v>
       </c>
       <c r="H5" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A5,Sheet1!$A$4:$H$25,COLUMN(H2),0)</f>
+        <v>127724.41</v>
       </c>
       <c r="I5" s="1">
         <v>152953.26</v>
@@ -5209,7 +7782,8 @@
         <v>845294.69</v>
       </c>
       <c r="H6" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A6,Sheet1!$A$4:$H$25,COLUMN(H3),0)</f>
+        <v>1001903</v>
       </c>
       <c r="I6" s="1">
         <v>1083892</v>
@@ -5259,7 +7833,8 @@
         <v>207865</v>
       </c>
       <c r="H7" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A7,Sheet1!$A$4:$H$25,COLUMN(H4),0)</f>
+        <v>500173</v>
       </c>
       <c r="I7" s="1">
         <v>330575</v>
@@ -5309,7 +7884,8 @@
         <v>362901.92</v>
       </c>
       <c r="H8" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A8,Sheet1!$A$4:$H$25,COLUMN(H5),0)</f>
+        <v>725000</v>
       </c>
       <c r="I8" s="1">
         <v>913227</v>
@@ -5359,7 +7935,8 @@
         <v>728417</v>
       </c>
       <c r="H9" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A9,Sheet1!$A$4:$H$25,COLUMN(H6),0)</f>
+        <v>380058</v>
       </c>
       <c r="I9" s="1">
         <v>808858</v>
@@ -5409,7 +7986,8 @@
         <v>79866</v>
       </c>
       <c r="H10" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A10,Sheet1!$A$4:$H$25,COLUMN(H7),0)</f>
+        <v>78056</v>
       </c>
       <c r="I10" s="1">
         <v>110615</v>
@@ -5460,7 +8038,8 @@
         <v>2688</v>
       </c>
       <c r="H11" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A11,Sheet1!$A$4:$H$25,COLUMN(H8),0)</f>
+        <v>10991</v>
       </c>
       <c r="I11" s="1">
         <v>22246</v>
@@ -5510,6 +8089,7 @@
         <v>2106</v>
       </c>
       <c r="H12" s="7">
+        <f>VLOOKUP($A12,Sheet1!$A$4:$H$25,COLUMN(H9),0)</f>
         <v>0</v>
       </c>
       <c r="I12" s="1">
@@ -5560,7 +8140,8 @@
         <v>14718</v>
       </c>
       <c r="H13" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A13,Sheet1!$A$4:$H$25,COLUMN(H10),0)</f>
+        <v>102982</v>
       </c>
       <c r="I13" s="1">
         <v>307977</v>
@@ -5610,7 +8191,8 @@
         <v>85480</v>
       </c>
       <c r="H14" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A14,Sheet1!$A$4:$H$25,COLUMN(H11),0)</f>
+        <v>105528</v>
       </c>
       <c r="I14" s="1">
         <v>235524</v>
@@ -5660,7 +8242,8 @@
         <v>81341</v>
       </c>
       <c r="H15" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A15,Sheet1!$A$4:$H$25,COLUMN(H12),0)</f>
+        <v>160101.42000000001</v>
       </c>
       <c r="I15" s="1">
         <v>281954</v>
@@ -5710,7 +8293,8 @@
         <v>91590</v>
       </c>
       <c r="H16" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A16,Sheet1!$A$4:$H$25,COLUMN(H13),0)</f>
+        <v>148161</v>
       </c>
       <c r="I16" s="1">
         <v>151692</v>
@@ -5760,7 +8344,8 @@
         <v>134945</v>
       </c>
       <c r="H17" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A17,Sheet1!$A$4:$H$25,COLUMN(H14),0)</f>
+        <v>125466</v>
       </c>
       <c r="I17" s="1">
         <v>227158.2</v>
@@ -5810,7 +8395,8 @@
         <v>109140</v>
       </c>
       <c r="H18" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A18,Sheet1!$A$4:$H$25,COLUMN(H15),0)</f>
+        <v>103766</v>
       </c>
       <c r="I18" s="7">
         <v>232119</v>
@@ -5860,7 +8446,8 @@
         <v>383704</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A19,Sheet1!$A$4:$H$25,COLUMN(H16),0)</f>
+        <v>744088</v>
       </c>
       <c r="I19" s="1">
         <v>641549</v>
@@ -5910,7 +8497,8 @@
         <v>11760</v>
       </c>
       <c r="H20" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A20,Sheet1!$A$4:$H$25,COLUMN(H17),0)</f>
+        <v>59635</v>
       </c>
       <c r="I20" s="1">
         <v>46814</v>
@@ -5960,7 +8548,8 @@
         <v>23368</v>
       </c>
       <c r="H21" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A21,Sheet1!$A$4:$H$25,COLUMN(H18),0)</f>
+        <v>18607</v>
       </c>
       <c r="I21" s="1">
         <v>29237</v>
@@ -6010,7 +8599,8 @@
         <v>45398</v>
       </c>
       <c r="H22" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A22,Sheet1!$A$4:$H$25,COLUMN(H19),0)</f>
+        <v>136029.26999999999</v>
       </c>
       <c r="I22" s="1">
         <v>160280</v>
@@ -6060,7 +8650,8 @@
         <v>116328</v>
       </c>
       <c r="H23" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A23,Sheet1!$A$4:$H$25,COLUMN(H20),0)</f>
+        <v>240779</v>
       </c>
       <c r="I23" s="8">
         <v>306475</v>
@@ -6110,7 +8701,8 @@
         <v>46157</v>
       </c>
       <c r="H24" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A24,Sheet1!$A$4:$H$25,COLUMN(H21),0)</f>
+        <v>133025</v>
       </c>
       <c r="I24" s="1">
         <v>207772</v>
@@ -6160,7 +8752,8 @@
         <v>4584</v>
       </c>
       <c r="H25" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A25,Sheet1!$A$4:$H$25,COLUMN(H22),0)</f>
+        <v>15844</v>
       </c>
       <c r="I25" s="1">
         <v>19424</v>
@@ -6230,7 +8823,7 @@
       </c>
       <c r="H27" s="92">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5083236.0999999996</v>
       </c>
       <c r="I27" s="92">
         <f t="shared" si="3"/>

--- a/粽子销售数据.xlsx
+++ b/粽子销售数据.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8880" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="粽子销售PICKUP" sheetId="3" r:id="rId1"/>
     <sheet name="最新数据" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="10" state="hidden" r:id="rId3"/>
     <sheet name="经验总结" sheetId="8" state="hidden" r:id="rId4"/>
     <sheet name="2026年 粽子礼盒销售汇总" sheetId="7" state="hidden" r:id="rId5"/>
     <sheet name="原表" sheetId="9" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2026年 粽子礼盒销售汇总'!$B$3:$O$3</definedName>
@@ -32,8 +33,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+香港酒店25年实际收入10.3万元</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
   <si>
     <t>序号</t>
   </si>
@@ -150,10 +187,6 @@
   </si>
   <si>
     <t>累计收入</t>
-  </si>
-  <si>
-    <t>香港喜來登</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>合计</t>
@@ -277,10 +310,6 @@
 完成度%</t>
   </si>
   <si>
-    <t>香港喜來登</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>26年(5.31）</t>
   </si>
 </sst>
@@ -295,7 +324,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,33 +460,26 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="14">
@@ -680,7 +702,7 @@
     <xf numFmtId="9" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="4" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -970,14 +992,29 @@
     <xf numFmtId="177" fontId="16" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -994,6 +1031,21 @@
     <xf numFmtId="176" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="10" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1018,71 +1070,50 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="19" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="12" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="12" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="13" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="12" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="12" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="19" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1219,7 +1250,7 @@
             <c:numRef>
               <c:f>'[1]粽子销售 26年 VS 25年 同期收入 PICK UP'!$M$4:$M$25</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>6.9970104633781762</c:v>
@@ -1381,7 +1412,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1458,7 +1489,394 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'[2]粽子销售 26年 VS 25年 同期收入 PICK UP'!$A$4:$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>牡丹江假日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>烟台希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>石狮睿选</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>虹桥睿选尚品</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>杭州艾美</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>厦门康莱德</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>宁波双店</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>上海康莱德</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>南京希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>绍兴双店</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>成都茂御</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>成都龙泉驿睿选</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>泰州茂御</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>武汉希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>佘山艾美</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>长沙希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>福州洲际</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>佘山洲际</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>沈阳希尔顿</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>芜湖希尔顿逸林</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>松江睿选</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'[2]粽子销售 26年 VS 25年 同期收入 PICK UP'!$M$4:$M$24</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2.5287948049728715</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8107274899795811</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7822784810126582</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7503505831651673</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7025018093336661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6154345297682409</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4172773448102052</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.388866914537352</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.379119911339586</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3774764677926186</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2406435900891362</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2326503294892917</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1571667495366813</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1497688964518131</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1483931104181762</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0338511586025176</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0232253854311117</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.97303034934868637</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.91457803667156967</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.86887933357894709</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.85246785939045222</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B337-446D-8012-237E74CA04A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="727953152"/>
+        <c:axId val="727947328"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="727953152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="727947328"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="727947328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="727953152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2001,6 +2419,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2033,6 +2954,98 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>44825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>45944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>549088</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>33617</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="矩形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22060180" y="2778498"/>
+          <a:ext cx="1652308" cy="2445125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2221,6 +3234,190 @@
           </cell>
           <cell r="M25">
             <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="粽子销售 26年 VS 25年 同期收入 PICK UP"/>
+      <sheetName val="散客人数用餐比例%"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>牡丹江假日</v>
+          </cell>
+          <cell r="M4">
+            <v>2.5287948049728715</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>烟台希尔顿</v>
+          </cell>
+          <cell r="M5">
+            <v>1.8107274899795811</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>石狮睿选</v>
+          </cell>
+          <cell r="M6">
+            <v>1.7822784810126582</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>虹桥睿选尚品</v>
+          </cell>
+          <cell r="M7">
+            <v>1.7503505831651673</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>杭州艾美</v>
+          </cell>
+          <cell r="M8">
+            <v>1.7025018093336661</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>厦门康莱德</v>
+          </cell>
+          <cell r="M9">
+            <v>1.6154345297682409</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>宁波双店</v>
+          </cell>
+          <cell r="M10">
+            <v>1.4172773448102052</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>上海康莱德</v>
+          </cell>
+          <cell r="M11">
+            <v>1.388866914537352</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>南京希尔顿</v>
+          </cell>
+          <cell r="M12">
+            <v>1.379119911339586</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>绍兴双店</v>
+          </cell>
+          <cell r="M13">
+            <v>1.3774764677926186</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>成都茂御</v>
+          </cell>
+          <cell r="M14">
+            <v>1.2406435900891362</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>成都龙泉驿睿选</v>
+          </cell>
+          <cell r="M15">
+            <v>1.2326503294892917</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>泰州茂御</v>
+          </cell>
+          <cell r="M16">
+            <v>1.1571667495366813</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>武汉希尔顿</v>
+          </cell>
+          <cell r="M17">
+            <v>1.1497688964518131</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>佘山艾美</v>
+          </cell>
+          <cell r="M18">
+            <v>1.1483931104181762</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>长沙希尔顿</v>
+          </cell>
+          <cell r="M19">
+            <v>1.0338511586025176</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>福州洲际</v>
+          </cell>
+          <cell r="M20">
+            <v>1.0232253854311117</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>佘山洲际</v>
+          </cell>
+          <cell r="M21">
+            <v>0.97303034934868637</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>沈阳希尔顿</v>
+          </cell>
+          <cell r="M22">
+            <v>0.91457803667156967</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>芜湖希尔顿逸林</v>
+          </cell>
+          <cell r="M23">
+            <v>0.86887933357894709</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>松江睿选</v>
+          </cell>
+          <cell r="M24">
+            <v>0.85246785939045222</v>
           </cell>
         </row>
       </sheetData>
@@ -2515,47 +3712,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="106" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="105" t="s">
+      <c r="A2" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="104" t="s">
+      <c r="C2" s="110"/>
+      <c r="D2" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104" t="s">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104" t="s">
-        <v>66</v>
-      </c>
-      <c r="K2" s="104"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="109"/>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="106"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="11">
         <v>2025</v>
       </c>
@@ -2588,49 +3785,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(C1),0)</f>
-        <v>10261.700000000001</v>
-      </c>
-      <c r="C4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(D1),0)</f>
-        <v>94983</v>
-      </c>
-      <c r="D4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(E1),0)</f>
-        <v>46531.88</v>
-      </c>
-      <c r="E4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(F1),0)</f>
-        <v>132578</v>
-      </c>
-      <c r="F4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(G1),0)</f>
-        <v>84571.199999999997</v>
-      </c>
-      <c r="G4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(H1),0)</f>
-        <v>165319</v>
-      </c>
-      <c r="H4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(I1),0)</f>
-        <v>93456</v>
-      </c>
-      <c r="I4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(J1),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="7">
-        <f>VLOOKUP(A4,最新数据!$A$4:$H$25,8,0)</f>
-        <v>103301</v>
-      </c>
-      <c r="K4" s="7">
-        <f>VLOOKUP($A4,原表!$A$4:$O$25,COLUMN(L1),0)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -2666,7 +3831,7 @@
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP($A5,原表!$A$4:$O$25,COLUMN(J2),0)</f>
-        <v>0</v>
+        <v>175650.47</v>
       </c>
       <c r="J5" s="7">
         <f>VLOOKUP(A5,最新数据!$A$4:$H$25,8,0)</f>
@@ -2711,7 +3876,7 @@
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP($A6,原表!$A$4:$O$25,COLUMN(J3),0)</f>
-        <v>0</v>
+        <v>1120583</v>
       </c>
       <c r="J6" s="7">
         <f>VLOOKUP(A6,最新数据!$A$4:$H$25,8,0)</f>
@@ -2756,7 +3921,7 @@
       </c>
       <c r="I7" s="7">
         <f>VLOOKUP($A7,原表!$A$4:$O$25,COLUMN(J4),0)</f>
-        <v>0</v>
+        <v>598581.24</v>
       </c>
       <c r="J7" s="7">
         <f>VLOOKUP(A7,最新数据!$A$4:$H$25,8,0)</f>
@@ -2801,7 +3966,7 @@
       </c>
       <c r="I8" s="7">
         <f>VLOOKUP($A8,原表!$A$4:$O$25,COLUMN(J5),0)</f>
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="J8" s="7">
         <f>VLOOKUP(A8,最新数据!$A$4:$H$25,8,0)</f>
@@ -2846,7 +4011,7 @@
       </c>
       <c r="I9" s="7">
         <f>VLOOKUP($A9,原表!$A$4:$O$25,COLUMN(J6),0)</f>
-        <v>0</v>
+        <v>702800</v>
       </c>
       <c r="J9" s="7">
         <f>VLOOKUP(A9,最新数据!$A$4:$H$25,8,0)</f>
@@ -2891,7 +4056,7 @@
       </c>
       <c r="I10" s="7">
         <f>VLOOKUP($A10,原表!$A$4:$O$25,COLUMN(J7),0)</f>
-        <v>0</v>
+        <v>128000</v>
       </c>
       <c r="J10" s="7">
         <f>VLOOKUP(A10,最新数据!$A$4:$H$25,8,0)</f>
@@ -2936,7 +4101,7 @@
       </c>
       <c r="I11" s="7">
         <f>VLOOKUP($A11,原表!$A$4:$O$25,COLUMN(J8),0)</f>
-        <v>0</v>
+        <v>18964</v>
       </c>
       <c r="J11" s="7">
         <f>VLOOKUP(A11,最新数据!$A$4:$H$25,8,0)</f>
@@ -2981,7 +4146,7 @@
       </c>
       <c r="I12" s="7">
         <f>VLOOKUP($A12,原表!$A$4:$O$25,COLUMN(J9),0)</f>
-        <v>0</v>
+        <v>5632</v>
       </c>
       <c r="J12" s="7">
         <f>VLOOKUP(A12,最新数据!$A$4:$H$25,8,0)</f>
@@ -3026,7 +4191,7 @@
       </c>
       <c r="I13" s="7">
         <f>VLOOKUP($A13,原表!$A$4:$O$25,COLUMN(J10),0)</f>
-        <v>0</v>
+        <v>281669</v>
       </c>
       <c r="J13" s="7">
         <f>VLOOKUP(A13,最新数据!$A$4:$H$25,8,0)</f>
@@ -3071,7 +4236,7 @@
       </c>
       <c r="I14" s="7">
         <f>VLOOKUP($A14,原表!$A$4:$O$25,COLUMN(J11),0)</f>
-        <v>0</v>
+        <v>229172</v>
       </c>
       <c r="J14" s="7">
         <f>VLOOKUP(A14,最新数据!$A$4:$H$25,8,0)</f>
@@ -3116,7 +4281,7 @@
       </c>
       <c r="I15" s="7">
         <f>VLOOKUP($A15,原表!$A$4:$O$25,COLUMN(J12),0)</f>
-        <v>0</v>
+        <v>388385</v>
       </c>
       <c r="J15" s="7">
         <f>VLOOKUP(A15,最新数据!$A$4:$H$25,8,0)</f>
@@ -3161,7 +4326,7 @@
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP($A16,原表!$A$4:$O$25,COLUMN(J13),0)</f>
-        <v>0</v>
+        <v>210680</v>
       </c>
       <c r="J16" s="7">
         <f>VLOOKUP(A16,最新数据!$A$4:$H$25,8,0)</f>
@@ -3206,7 +4371,7 @@
       </c>
       <c r="I17" s="7">
         <f>VLOOKUP($A17,原表!$A$4:$O$25,COLUMN(J14),0)</f>
-        <v>0</v>
+        <v>366959.2</v>
       </c>
       <c r="J17" s="7">
         <f>VLOOKUP(A17,最新数据!$A$4:$H$25,8,0)</f>
@@ -3251,7 +4416,7 @@
       </c>
       <c r="I18" s="7">
         <f>VLOOKUP($A18,原表!$A$4:$O$25,COLUMN(J15),0)</f>
-        <v>0</v>
+        <v>328977</v>
       </c>
       <c r="J18" s="7">
         <f>VLOOKUP(A18,最新数据!$A$4:$H$25,8,0)</f>
@@ -3296,7 +4461,7 @@
       </c>
       <c r="I19" s="7">
         <f>VLOOKUP($A19,原表!$A$4:$O$25,COLUMN(J16),0)</f>
-        <v>0</v>
+        <v>884773</v>
       </c>
       <c r="J19" s="7">
         <f>VLOOKUP(A19,最新数据!$A$4:$H$25,8,0)</f>
@@ -3341,7 +4506,7 @@
       </c>
       <c r="I20" s="7">
         <f>VLOOKUP($A20,原表!$A$4:$O$25,COLUMN(J17),0)</f>
-        <v>0</v>
+        <v>118383</v>
       </c>
       <c r="J20" s="7">
         <f>VLOOKUP(A20,最新数据!$A$4:$H$25,8,0)</f>
@@ -3386,7 +4551,7 @@
       </c>
       <c r="I21" s="7">
         <f>VLOOKUP($A21,原表!$A$4:$O$25,COLUMN(J18),0)</f>
-        <v>0</v>
+        <v>51175</v>
       </c>
       <c r="J21" s="7">
         <f>VLOOKUP(A21,最新数据!$A$4:$H$25,8,0)</f>
@@ -3431,7 +4596,7 @@
       </c>
       <c r="I22" s="7">
         <f>VLOOKUP($A22,原表!$A$4:$O$25,COLUMN(J19),0)</f>
-        <v>0</v>
+        <v>272876.99</v>
       </c>
       <c r="J22" s="7">
         <f>VLOOKUP(A22,最新数据!$A$4:$H$25,8,0)</f>
@@ -3476,7 +4641,7 @@
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP($A23,原表!$A$4:$O$25,COLUMN(J20),0)</f>
-        <v>0</v>
+        <v>313593</v>
       </c>
       <c r="J23" s="7">
         <f>VLOOKUP(A23,最新数据!$A$4:$H$25,8,0)</f>
@@ -3521,7 +4686,7 @@
       </c>
       <c r="I24" s="7">
         <f>VLOOKUP($A24,原表!$A$4:$O$25,COLUMN(J21),0)</f>
-        <v>0</v>
+        <v>257771</v>
       </c>
       <c r="J24" s="7">
         <f>VLOOKUP(A24,最新数据!$A$4:$H$25,8,0)</f>
@@ -3566,7 +4731,7 @@
       </c>
       <c r="I25" s="7">
         <f>VLOOKUP($A25,原表!$A$4:$O$25,COLUMN(J22),0)</f>
-        <v>0</v>
+        <v>23943</v>
       </c>
       <c r="J25" s="7">
         <f>VLOOKUP(A25,最新数据!$A$4:$H$25,8,0)</f>
@@ -3579,43 +4744,43 @@
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="17">
         <f t="shared" ref="B26:K26" si="0">SUM(B4:B25)</f>
-        <v>385680.74000000005</v>
+        <v>375419.04000000004</v>
       </c>
       <c r="C26" s="17">
         <f t="shared" si="0"/>
-        <v>1235728</v>
+        <v>1140745</v>
       </c>
       <c r="D26" s="17">
         <f t="shared" si="0"/>
-        <v>1747396.2060000002</v>
+        <v>1700864.3260000001</v>
       </c>
       <c r="E26" s="7">
         <f t="shared" si="0"/>
-        <v>3195708.93</v>
+        <v>3063130.93</v>
       </c>
       <c r="F26" s="17">
         <f t="shared" si="0"/>
-        <v>3593461.8099999996</v>
+        <v>3508890.61</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="0"/>
-        <v>5083236.0999999996</v>
+        <v>4917917.0999999996</v>
       </c>
       <c r="H26" s="17">
         <f t="shared" si="0"/>
-        <v>6366957.46</v>
+        <v>6273501.46</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7528567.9000000004</v>
       </c>
       <c r="J26" s="17">
         <f t="shared" si="0"/>
-        <v>8126892.79</v>
+        <v>8023591.79</v>
       </c>
       <c r="K26" s="17">
         <f t="shared" si="0"/>
@@ -3665,86 +4830,59 @@
       <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="110" t="str">
+        <f>粽子销售PICKUP!H2</f>
+        <v>节前9天</v>
+      </c>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="112" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="112" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="111"/>
+      <c r="B3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="105" t="str">
-        <f>粽子销售PICKUP!F2</f>
-        <v>节前19天</v>
-      </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="107" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="107" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="106"/>
-      <c r="B3" s="15" t="s">
+      <c r="D3" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2" t="str">
-        <f>粽子销售PICKUP!A4</f>
-        <v>香港喜來登</v>
-      </c>
-      <c r="B4" s="7">
-        <f>粽子销售PICKUP!F4</f>
-        <v>84571.199999999997</v>
-      </c>
-      <c r="C4" s="7">
-        <f>粽子销售PICKUP!G4</f>
-        <v>165319</v>
-      </c>
-      <c r="D4" s="7">
-        <f>C4-B4</f>
-        <v>80747.8</v>
-      </c>
-      <c r="E4" s="22">
-        <f>C4/B4-1</f>
-        <v>0.95479075619123299</v>
-      </c>
-      <c r="F4" s="7">
-        <f>VLOOKUP(A4,原表!$A$4:$B$25,2,0)</f>
-        <v>120000</v>
-      </c>
-      <c r="G4" s="74">
-        <f>C4/F4</f>
-        <v>1.3776583333333334</v>
-      </c>
-      <c r="H4" s="7">
-        <f>VLOOKUP(A4,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
-        <v>103301</v>
-      </c>
-      <c r="I4" s="74">
-        <f>C4/H4</f>
-        <v>1.6003620487700991</v>
-      </c>
-      <c r="K4" s="103"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="74"/>
+      <c r="K4" s="101"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2" t="str">
@@ -3752,20 +4890,20 @@
         <v>佘山艾美</v>
       </c>
       <c r="B5" s="7">
-        <f>粽子销售PICKUP!F5</f>
-        <v>131239</v>
+        <f>粽子销售PICKUP!H5</f>
+        <v>152953.26</v>
       </c>
       <c r="C5" s="7">
-        <f>粽子销售PICKUP!G5</f>
-        <v>127724.41</v>
+        <f>粽子销售PICKUP!I5</f>
+        <v>175650.47</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" ref="D5:D26" si="0">C5-B5</f>
-        <v>-3514.5899999999965</v>
+        <v>22697.209999999992</v>
       </c>
       <c r="E5" s="22">
         <f t="shared" ref="E5:E26" si="1">C5/B5-1</f>
-        <v>-2.6780072996594018E-2</v>
+        <v>0.14839311041817616</v>
       </c>
       <c r="F5" s="7">
         <f>VLOOKUP(A5,原表!$A$4:$B$25,2,0)</f>
@@ -3773,7 +4911,7 @@
       </c>
       <c r="G5" s="74">
         <f t="shared" ref="G5:G26" si="2">C5/F5</f>
-        <v>0.73680925075570536</v>
+        <v>1.0132823568774949</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3781,9 +4919,9 @@
       </c>
       <c r="I5" s="74">
         <f t="shared" ref="I5:I26" si="3">C5/H5</f>
-        <v>0.81049234059783604</v>
-      </c>
-      <c r="K5" s="103"/>
+        <v>1.1146135696176633</v>
+      </c>
+      <c r="K5" s="101"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2" t="str">
@@ -3791,20 +4929,20 @@
         <v>长沙希尔顿</v>
       </c>
       <c r="B6" s="7">
-        <f>粽子销售PICKUP!F6</f>
-        <v>845294.69</v>
+        <f>粽子销售PICKUP!H6</f>
+        <v>1083892</v>
       </c>
       <c r="C6" s="7">
-        <f>粽子销售PICKUP!G6</f>
-        <v>1001903</v>
+        <f>粽子销售PICKUP!I6</f>
+        <v>1120583</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>156608.31000000006</v>
+        <v>36691</v>
       </c>
       <c r="E6" s="22">
         <f t="shared" si="1"/>
-        <v>0.18527066578402396</v>
+        <v>3.3851158602517639E-2</v>
       </c>
       <c r="F6" s="7">
         <f>VLOOKUP(A6,原表!$A$4:$B$25,2,0)</f>
@@ -3812,7 +4950,7 @@
       </c>
       <c r="G6" s="74">
         <f t="shared" si="2"/>
-        <v>0.80147815840565606</v>
+        <v>0.89641691778613819</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3820,9 +4958,9 @@
       </c>
       <c r="I6" s="74">
         <f t="shared" si="3"/>
-        <v>0.83554094838909287</v>
-      </c>
-      <c r="K6" s="103"/>
+        <v>0.93451460128245434</v>
+      </c>
+      <c r="K6" s="101"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2" t="str">
@@ -3830,20 +4968,20 @@
         <v>烟台希尔顿</v>
       </c>
       <c r="B7" s="7">
-        <f>粽子销售PICKUP!F7</f>
-        <v>207865</v>
+        <f>粽子销售PICKUP!H7</f>
+        <v>330575</v>
       </c>
       <c r="C7" s="7">
-        <f>粽子销售PICKUP!G7</f>
-        <v>500173</v>
+        <f>粽子销售PICKUP!I7</f>
+        <v>598581.24</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>292308</v>
+        <v>268006.24</v>
       </c>
       <c r="E7" s="22">
         <f t="shared" si="1"/>
-        <v>1.4062396266807782</v>
+        <v>0.81072748997958111</v>
       </c>
       <c r="F7" s="7">
         <f>VLOOKUP(A7,原表!$A$4:$B$25,2,0)</f>
@@ -3851,7 +4989,7 @@
       </c>
       <c r="G7" s="74">
         <f t="shared" si="2"/>
-        <v>0.82549058441022594</v>
+        <v>0.98790454027825914</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3859,9 +4997,9 @@
       </c>
       <c r="I7" s="74">
         <f t="shared" si="3"/>
-        <v>0.9080400924428178</v>
-      </c>
-      <c r="K7" s="103"/>
+        <v>1.0866955323540786</v>
+      </c>
+      <c r="K7" s="101"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2" t="str">
@@ -3869,20 +5007,20 @@
         <v>武汉希尔顿</v>
       </c>
       <c r="B8" s="7">
-        <f>粽子销售PICKUP!F8</f>
-        <v>362901.92</v>
+        <f>粽子销售PICKUP!H8</f>
+        <v>913227</v>
       </c>
       <c r="C8" s="7">
-        <f>粽子销售PICKUP!G8</f>
-        <v>725000</v>
+        <f>粽子销售PICKUP!I8</f>
+        <v>1050000</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>362098.08</v>
+        <v>136773</v>
       </c>
       <c r="E8" s="22">
         <f t="shared" si="1"/>
-        <v>0.99778496625203861</v>
+        <v>0.14976889645181313</v>
       </c>
       <c r="F8" s="7">
         <f>VLOOKUP(A8,原表!$A$4:$B$25,2,0)</f>
@@ -3890,7 +5028,7 @@
       </c>
       <c r="G8" s="74">
         <f t="shared" si="2"/>
-        <v>0.66629170526563442</v>
+        <v>0.96497419383298777</v>
       </c>
       <c r="H8" s="7">
         <f>VLOOKUP(A8,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3898,9 +5036,9 @@
       </c>
       <c r="I8" s="74">
         <f t="shared" si="3"/>
-        <v>0.66629170526563442</v>
-      </c>
-      <c r="K8" s="103"/>
+        <v>0.96497419383298777</v>
+      </c>
+      <c r="K8" s="101"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="str">
@@ -3908,20 +5046,20 @@
         <v>芜湖希尔顿逸林</v>
       </c>
       <c r="B9" s="7">
-        <f>粽子销售PICKUP!F9</f>
-        <v>728417</v>
+        <f>粽子销售PICKUP!H9</f>
+        <v>808858</v>
       </c>
       <c r="C9" s="7">
-        <f>粽子销售PICKUP!G9</f>
-        <v>380058</v>
+        <f>粽子销售PICKUP!I9</f>
+        <v>702800</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-348359</v>
+        <v>-106058</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="1"/>
-        <v>-0.47824117229553953</v>
+        <v>-0.13112066642105291</v>
       </c>
       <c r="F9" s="7">
         <f>VLOOKUP(A9,原表!$A$4:$B$25,2,0)</f>
@@ -3929,7 +5067,7 @@
       </c>
       <c r="G9" s="74">
         <f t="shared" si="2"/>
-        <v>0.40182187839976657</v>
+        <v>0.74304557762066825</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3937,9 +5075,9 @@
       </c>
       <c r="I9" s="74">
         <f t="shared" si="3"/>
-        <v>0.41785054704836005</v>
-      </c>
-      <c r="K9" s="103"/>
+        <v>0.77268565446744297</v>
+      </c>
+      <c r="K9" s="101"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2" t="str">
@@ -3947,20 +5085,20 @@
         <v>泰州茂御</v>
       </c>
       <c r="B10" s="7">
-        <f>粽子销售PICKUP!F10</f>
-        <v>79866</v>
+        <f>粽子销售PICKUP!H10</f>
+        <v>110615</v>
       </c>
       <c r="C10" s="7">
-        <f>粽子销售PICKUP!G10</f>
-        <v>78056</v>
+        <f>粽子销售PICKUP!I10</f>
+        <v>128000</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-1810</v>
+        <v>17385</v>
       </c>
       <c r="E10" s="22">
         <f t="shared" si="1"/>
-        <v>-2.2662960458768477E-2</v>
+        <v>0.1571667495366813</v>
       </c>
       <c r="F10" s="7">
         <f>VLOOKUP(A10,原表!$A$4:$B$25,2,0)</f>
@@ -3968,7 +5106,7 @@
       </c>
       <c r="G10" s="74">
         <f t="shared" si="2"/>
-        <v>0.28663021485515361</v>
+        <v>0.47003007458055324</v>
       </c>
       <c r="H10" s="7">
         <f>VLOOKUP(A10,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -3976,9 +5114,9 @@
       </c>
       <c r="I10" s="74">
         <f t="shared" si="3"/>
-        <v>0.31529369945792235</v>
-      </c>
-      <c r="K10" s="103"/>
+        <v>0.51703384148065568</v>
+      </c>
+      <c r="K10" s="101"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2" t="str">
@@ -3986,20 +5124,20 @@
         <v>松江睿选</v>
       </c>
       <c r="B11" s="7">
-        <f>粽子销售PICKUP!F11</f>
-        <v>2688</v>
+        <f>粽子销售PICKUP!H11</f>
+        <v>22246</v>
       </c>
       <c r="C11" s="7">
-        <f>粽子销售PICKUP!G11</f>
-        <v>10991</v>
+        <f>粽子销售PICKUP!I11</f>
+        <v>18964</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>8303</v>
+        <v>-3282</v>
       </c>
       <c r="E11" s="22">
         <f t="shared" si="1"/>
-        <v>3.0889136904761907</v>
+        <v>-0.14753214060954778</v>
       </c>
       <c r="F11" s="7">
         <f>VLOOKUP(A11,原表!$A$4:$B$25,2,0)</f>
@@ -4007,7 +5145,7 @@
       </c>
       <c r="G11" s="74">
         <f t="shared" si="2"/>
-        <v>0.48254818457215615</v>
+        <v>0.83259428370724853</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP(A11,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4015,9 +5153,9 @@
       </c>
       <c r="I11" s="74">
         <f t="shared" si="3"/>
-        <v>0.53081232492997199</v>
-      </c>
-      <c r="K11" s="103"/>
+        <v>0.91586979619433984</v>
+      </c>
+      <c r="K11" s="101"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2" t="str">
@@ -4025,20 +5163,20 @@
         <v>石狮睿选</v>
       </c>
       <c r="B12" s="7">
-        <f>粽子销售PICKUP!F12</f>
-        <v>2106</v>
+        <f>粽子销售PICKUP!H12</f>
+        <v>3160</v>
       </c>
       <c r="C12" s="7">
-        <f>粽子销售PICKUP!G12</f>
-        <v>0</v>
+        <f>粽子销售PICKUP!I12</f>
+        <v>5632</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-2106</v>
+        <v>2472</v>
       </c>
       <c r="E12" s="22">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.78227848101265818</v>
       </c>
       <c r="F12" s="7">
         <f>VLOOKUP(A12,原表!$A$4:$B$25,2,0)</f>
@@ -4046,7 +5184,7 @@
       </c>
       <c r="G12" s="74">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.55307866051261911</v>
       </c>
       <c r="H12" s="7">
         <f>VLOOKUP(A12,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4054,9 +5192,9 @@
       </c>
       <c r="I12" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="103"/>
+        <v>0.60840445068596738</v>
+      </c>
+      <c r="K12" s="101"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2" t="str">
@@ -4064,20 +5202,20 @@
         <v>沈阳希尔顿</v>
       </c>
       <c r="B13" s="7">
-        <f>粽子销售PICKUP!F13</f>
-        <v>14718</v>
+        <f>粽子销售PICKUP!H13</f>
+        <v>307977</v>
       </c>
       <c r="C13" s="7">
-        <f>粽子销售PICKUP!G13</f>
-        <v>102982</v>
+        <f>粽子销售PICKUP!I13</f>
+        <v>281669</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>88264</v>
+        <v>-26308</v>
       </c>
       <c r="E13" s="22">
         <f t="shared" si="1"/>
-        <v>5.9970104633781762</v>
+        <v>-8.5421963328430328E-2</v>
       </c>
       <c r="F13" s="7">
         <f>VLOOKUP(A13,原表!$A$4:$B$25,2,0)</f>
@@ -4085,7 +5223,7 @@
       </c>
       <c r="G13" s="74">
         <f t="shared" si="2"/>
-        <v>0.25745499999999999</v>
+        <v>0.70417249999999998</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP(A13,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4093,9 +5231,9 @@
       </c>
       <c r="I13" s="74">
         <f t="shared" si="3"/>
-        <v>0.30149603302397754</v>
-      </c>
-      <c r="K13" s="103"/>
+        <v>0.82463038323037741</v>
+      </c>
+      <c r="K13" s="101"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2" t="str">
@@ -4103,20 +5241,20 @@
         <v>佘山洲际</v>
       </c>
       <c r="B14" s="7">
-        <f>粽子销售PICKUP!F14</f>
-        <v>85480</v>
+        <f>粽子销售PICKUP!H14</f>
+        <v>235524</v>
       </c>
       <c r="C14" s="7">
-        <f>粽子销售PICKUP!G14</f>
-        <v>105528</v>
+        <f>粽子销售PICKUP!I14</f>
+        <v>229172</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>20048</v>
+        <v>-6352</v>
       </c>
       <c r="E14" s="22">
         <f t="shared" si="1"/>
-        <v>0.23453439401029486</v>
+        <v>-2.6969650651313626E-2</v>
       </c>
       <c r="F14" s="7">
         <f>VLOOKUP(A14,原表!$A$4:$B$25,2,0)</f>
@@ -4124,7 +5262,7 @@
       </c>
       <c r="G14" s="74">
         <f t="shared" si="2"/>
-        <v>0.33384583262152878</v>
+        <v>0.72500300539706042</v>
       </c>
       <c r="H14" s="7">
         <f>VLOOKUP(A14,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4132,9 +5270,9 @@
       </c>
       <c r="I14" s="74">
         <f t="shared" si="3"/>
-        <v>0.36723018353157344</v>
-      </c>
-      <c r="K14" s="103"/>
+        <v>0.79750280134464546</v>
+      </c>
+      <c r="K14" s="101"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2" t="str">
@@ -4142,20 +5280,20 @@
         <v>绍兴双店</v>
       </c>
       <c r="B15" s="7">
-        <f>粽子销售PICKUP!F15</f>
-        <v>81341</v>
+        <f>粽子销售PICKUP!H15</f>
+        <v>281954</v>
       </c>
       <c r="C15" s="7">
-        <f>粽子销售PICKUP!G15</f>
-        <v>160101.42000000001</v>
+        <f>粽子销售PICKUP!I15</f>
+        <v>388385</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>78760.420000000013</v>
+        <v>106431</v>
       </c>
       <c r="E15" s="22">
         <f t="shared" si="1"/>
-        <v>0.96827454789097755</v>
+        <v>0.37747646779261856</v>
       </c>
       <c r="F15" s="7">
         <f>VLOOKUP(A15,原表!$A$4:$B$25,2,0)</f>
@@ -4163,7 +5301,7 @@
       </c>
       <c r="G15" s="74">
         <f t="shared" si="2"/>
-        <v>0.36731461215500039</v>
+        <v>0.89105696652671673</v>
       </c>
       <c r="H15" s="7">
         <f>VLOOKUP(A15,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4171,9 +5309,9 @@
       </c>
       <c r="I15" s="74">
         <f t="shared" si="3"/>
-        <v>0.40404653686481851</v>
-      </c>
-      <c r="K15" s="103"/>
+        <v>0.9801637875556789</v>
+      </c>
+      <c r="K15" s="101"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2" t="str">
@@ -4181,20 +5319,20 @@
         <v>上海康莱德</v>
       </c>
       <c r="B16" s="7">
-        <f>粽子销售PICKUP!F16</f>
-        <v>91590</v>
+        <f>粽子销售PICKUP!H16</f>
+        <v>151692</v>
       </c>
       <c r="C16" s="7">
-        <f>粽子销售PICKUP!G16</f>
-        <v>148161</v>
+        <f>粽子销售PICKUP!I16</f>
+        <v>210680</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>56571</v>
+        <v>58988</v>
       </c>
       <c r="E16" s="22">
         <f t="shared" si="1"/>
-        <v>0.61765476580412715</v>
+        <v>0.388866914537352</v>
       </c>
       <c r="F16" s="7">
         <f>VLOOKUP(A16,原表!$A$4:$B$25,2,0)</f>
@@ -4202,7 +5340,7 @@
       </c>
       <c r="G16" s="74">
         <f t="shared" si="2"/>
-        <v>0.68461837034572626</v>
+        <v>0.97350448677072643</v>
       </c>
       <c r="H16" s="7">
         <f>VLOOKUP(A16,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4210,9 +5348,9 @@
       </c>
       <c r="I16" s="74">
         <f t="shared" si="3"/>
-        <v>0.7530802073802989</v>
-      </c>
-      <c r="K16" s="103"/>
+        <v>1.0708549354477992</v>
+      </c>
+      <c r="K16" s="101"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2" t="str">
@@ -4220,20 +5358,20 @@
         <v>厦门康莱德</v>
       </c>
       <c r="B17" s="7">
-        <f>粽子销售PICKUP!F17</f>
-        <v>134945</v>
+        <f>粽子销售PICKUP!H17</f>
+        <v>227158.2</v>
       </c>
       <c r="C17" s="7">
-        <f>粽子销售PICKUP!G17</f>
-        <v>125466</v>
+        <f>粽子销售PICKUP!I17</f>
+        <v>366959.2</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>-9479</v>
+        <v>139801</v>
       </c>
       <c r="E17" s="22">
         <f t="shared" si="1"/>
-        <v>-7.0243432509540904E-2</v>
+        <v>0.61543452976824087</v>
       </c>
       <c r="F17" s="7">
         <f>VLOOKUP(A17,原表!$A$4:$B$25,2,0)</f>
@@ -4241,7 +5379,7 @@
       </c>
       <c r="G17" s="74">
         <f t="shared" si="2"/>
-        <v>0.25490805585522985</v>
+        <v>0.74554744911123705</v>
       </c>
       <c r="H17" s="7">
         <f>VLOOKUP(A17,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4249,9 +5387,9 @@
       </c>
       <c r="I17" s="74">
         <f t="shared" si="3"/>
-        <v>0.28039914628286644</v>
-      </c>
-      <c r="K17" s="103"/>
+        <v>0.82010302712004557</v>
+      </c>
+      <c r="K17" s="101"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2" t="str">
@@ -4259,20 +5397,20 @@
         <v>宁波双店</v>
       </c>
       <c r="B18" s="7">
-        <f>粽子销售PICKUP!F18</f>
-        <v>109140</v>
+        <f>粽子销售PICKUP!H18</f>
+        <v>232119</v>
       </c>
       <c r="C18" s="7">
-        <f>粽子销售PICKUP!G18</f>
-        <v>103766</v>
+        <f>粽子销售PICKUP!I18</f>
+        <v>328977</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-5374</v>
+        <v>96858</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="1"/>
-        <v>-4.923950888766726E-2</v>
+        <v>0.41727734481020518</v>
       </c>
       <c r="F18" s="7">
         <f>VLOOKUP(A18,原表!$A$4:$B$25,2,0)</f>
@@ -4280,7 +5418,7 @@
       </c>
       <c r="G18" s="74">
         <f t="shared" si="2"/>
-        <v>0.29896595338867071</v>
+        <v>0.94783380344182799</v>
       </c>
       <c r="H18" s="7">
         <f>VLOOKUP(A18,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4288,9 +5426,9 @@
       </c>
       <c r="I18" s="74">
         <f t="shared" si="3"/>
-        <v>0.32886254872753778</v>
-      </c>
-      <c r="K18" s="103"/>
+        <v>1.0426171837860108</v>
+      </c>
+      <c r="K18" s="101"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2" t="str">
@@ -4298,20 +5436,20 @@
         <v>南京希尔顿</v>
       </c>
       <c r="B19" s="7">
-        <f>粽子销售PICKUP!F19</f>
-        <v>383704</v>
+        <f>粽子销售PICKUP!H19</f>
+        <v>641549</v>
       </c>
       <c r="C19" s="7">
-        <f>粽子销售PICKUP!G19</f>
-        <v>744088</v>
+        <f>粽子销售PICKUP!I19</f>
+        <v>884773</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>360384</v>
+        <v>243224</v>
       </c>
       <c r="E19" s="22">
         <f t="shared" si="1"/>
-        <v>0.93922398515522376</v>
+        <v>0.379119911339586</v>
       </c>
       <c r="F19" s="7">
         <f>VLOOKUP(A19,原表!$A$4:$B$25,2,0)</f>
@@ -4319,7 +5457,7 @@
       </c>
       <c r="G19" s="74">
         <f t="shared" si="2"/>
-        <v>0.74408799999999997</v>
+        <v>0.88477300000000003</v>
       </c>
       <c r="H19" s="7">
         <f>VLOOKUP(A19,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4327,9 +5465,9 @@
       </c>
       <c r="I19" s="74">
         <f t="shared" si="3"/>
-        <v>0.96396286979522416</v>
-      </c>
-      <c r="K19" s="103"/>
+        <v>1.1462196947099401</v>
+      </c>
+      <c r="K19" s="101"/>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2" t="str">
@@ -4337,20 +5475,20 @@
         <v>牡丹江假日</v>
       </c>
       <c r="B20" s="7">
-        <f>粽子销售PICKUP!F20</f>
-        <v>11760</v>
+        <f>粽子销售PICKUP!H20</f>
+        <v>46814</v>
       </c>
       <c r="C20" s="7">
-        <f>粽子销售PICKUP!G20</f>
-        <v>59635</v>
+        <f>粽子销售PICKUP!I20</f>
+        <v>118383</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>47875</v>
+        <v>71569</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" si="1"/>
-        <v>4.0710034013605441</v>
+        <v>1.5287948049728715</v>
       </c>
       <c r="F20" s="7">
         <f>VLOOKUP(A20,原表!$A$4:$B$25,2,0)</f>
@@ -4358,7 +5496,7 @@
       </c>
       <c r="G20" s="74">
         <f t="shared" si="2"/>
-        <v>0.42596428571428574</v>
+        <v>0.84559285714285715</v>
       </c>
       <c r="H20" s="7">
         <f>VLOOKUP(A20,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4366,9 +5504,9 @@
       </c>
       <c r="I20" s="74">
         <f t="shared" si="3"/>
-        <v>0.6564188928881991</v>
-      </c>
-      <c r="K20" s="103"/>
+        <v>1.3030743321335403</v>
+      </c>
+      <c r="K20" s="101"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="str">
@@ -4376,20 +5514,20 @@
         <v>虹桥睿选尚品</v>
       </c>
       <c r="B21" s="7">
-        <f>粽子销售PICKUP!F21</f>
-        <v>23368</v>
+        <f>粽子销售PICKUP!H21</f>
+        <v>29237</v>
       </c>
       <c r="C21" s="7">
-        <f>粽子销售PICKUP!G21</f>
-        <v>18607</v>
+        <f>粽子销售PICKUP!I21</f>
+        <v>51175</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-4761</v>
+        <v>21938</v>
       </c>
       <c r="E21" s="22">
         <f t="shared" si="1"/>
-        <v>-0.20374015748031493</v>
+        <v>0.75035058316516734</v>
       </c>
       <c r="F21" s="7">
         <f>VLOOKUP(A21,原表!$A$4:$B$25,2,0)</f>
@@ -4397,7 +5535,7 @@
       </c>
       <c r="G21" s="74">
         <f t="shared" si="2"/>
-        <v>0.30755371900826445</v>
+        <v>0.84586776859504131</v>
       </c>
       <c r="H21" s="7">
         <f>VLOOKUP(A21,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4405,9 +5543,9 @@
       </c>
       <c r="I21" s="74">
         <f t="shared" si="3"/>
-        <v>0.33830909090909089</v>
-      </c>
-      <c r="K21" s="103"/>
+        <v>0.93045454545454542</v>
+      </c>
+      <c r="K21" s="101"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2" t="str">
@@ -4415,20 +5553,20 @@
         <v>杭州艾美</v>
       </c>
       <c r="B22" s="7">
-        <f>粽子销售PICKUP!F22</f>
-        <v>45398</v>
+        <f>粽子销售PICKUP!H22</f>
+        <v>160280</v>
       </c>
       <c r="C22" s="7">
-        <f>粽子销售PICKUP!G22</f>
-        <v>136029.26999999999</v>
+        <f>粽子销售PICKUP!I22</f>
+        <v>272876.99</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>90631.26999999999</v>
+        <v>112596.98999999999</v>
       </c>
       <c r="E22" s="22">
         <f t="shared" si="1"/>
-        <v>1.9963714260540111</v>
+        <v>0.70250180933366613</v>
       </c>
       <c r="F22" s="7">
         <f>VLOOKUP(A22,原表!$A$4:$B$25,2,0)</f>
@@ -4436,7 +5574,7 @@
       </c>
       <c r="G22" s="74">
         <f t="shared" si="2"/>
-        <v>0.47542567654943185</v>
+        <v>0.95371185617273813</v>
       </c>
       <c r="H22" s="7">
         <f>VLOOKUP(A22,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4444,9 +5582,9 @@
       </c>
       <c r="I22" s="74">
         <f t="shared" si="3"/>
-        <v>0.52296824420437504</v>
-      </c>
-      <c r="K22" s="103"/>
+        <v>1.0490830417900119</v>
+      </c>
+      <c r="K22" s="101"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="str">
@@ -4454,20 +5592,20 @@
         <v>福州洲际</v>
       </c>
       <c r="B23" s="7">
-        <f>粽子销售PICKUP!F23</f>
-        <v>116328</v>
+        <f>粽子销售PICKUP!H23</f>
+        <v>306475</v>
       </c>
       <c r="C23" s="7">
-        <f>粽子销售PICKUP!G23</f>
-        <v>240779</v>
+        <f>粽子销售PICKUP!I23</f>
+        <v>313593</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>124451</v>
+        <v>7118</v>
       </c>
       <c r="E23" s="22">
         <f t="shared" si="1"/>
-        <v>1.0698284162024621</v>
+        <v>2.3225385431111745E-2</v>
       </c>
       <c r="F23" s="7">
         <f>VLOOKUP(A23,原表!$A$4:$B$25,2,0)</f>
@@ -4475,7 +5613,7 @@
       </c>
       <c r="G23" s="74">
         <f t="shared" si="2"/>
-        <v>0.60194749999999997</v>
+        <v>0.78398250000000003</v>
       </c>
       <c r="H23" s="7">
         <f>VLOOKUP(A23,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4483,9 +5621,9 @@
       </c>
       <c r="I23" s="74">
         <f t="shared" si="3"/>
-        <v>0.68611688940814408</v>
-      </c>
-      <c r="K23" s="103"/>
+        <v>0.89360556236286437</v>
+      </c>
+      <c r="K23" s="101"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2" t="str">
@@ -4493,20 +5631,20 @@
         <v>成都茂御</v>
       </c>
       <c r="B24" s="7">
-        <f>粽子销售PICKUP!F24</f>
-        <v>46157</v>
+        <f>粽子销售PICKUP!H24</f>
+        <v>207772</v>
       </c>
       <c r="C24" s="7">
-        <f>粽子销售PICKUP!G24</f>
-        <v>133025</v>
+        <f>粽子销售PICKUP!I24</f>
+        <v>257771</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>86868</v>
+        <v>49999</v>
       </c>
       <c r="E24" s="22">
         <f t="shared" si="1"/>
-        <v>1.8820113958879476</v>
+        <v>0.24064359008913616</v>
       </c>
       <c r="F24" s="7">
         <f>VLOOKUP(A24,原表!$A$4:$B$25,2,0)</f>
@@ -4514,7 +5652,7 @@
       </c>
       <c r="G24" s="74">
         <f t="shared" si="2"/>
-        <v>0.40531070519949419</v>
+        <v>0.78539632242043844</v>
       </c>
       <c r="H24" s="7">
         <f>VLOOKUP(A24,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4522,9 +5660,9 @@
       </c>
       <c r="I24" s="74">
         <f t="shared" si="3"/>
-        <v>0.44584204740454741</v>
-      </c>
-      <c r="K24" s="103"/>
+        <v>0.86393648112398114</v>
+      </c>
+      <c r="K24" s="101"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2" t="str">
@@ -4532,20 +5670,20 @@
         <v>成都龙泉驿睿选</v>
       </c>
       <c r="B25" s="7">
-        <f>粽子销售PICKUP!F25</f>
-        <v>4584</v>
+        <f>粽子销售PICKUP!H25</f>
+        <v>19424</v>
       </c>
       <c r="C25" s="7">
-        <f>粽子销售PICKUP!G25</f>
-        <v>15844</v>
+        <f>粽子销售PICKUP!I25</f>
+        <v>23943</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>11260</v>
+        <v>4519</v>
       </c>
       <c r="E25" s="22">
         <f t="shared" si="1"/>
-        <v>2.4563699825479932</v>
+        <v>0.23265032948929165</v>
       </c>
       <c r="F25" s="7">
         <f>VLOOKUP(A25,原表!$A$4:$B$25,2,0)</f>
@@ -4553,7 +5691,7 @@
       </c>
       <c r="G25" s="74">
         <f t="shared" si="2"/>
-        <v>0.4999684443041969</v>
+        <v>0.75553802461344277</v>
       </c>
       <c r="H25" s="7">
         <f>VLOOKUP(A25,'2026年 粽子礼盒销售汇总'!$B$4:$N$27,7,0)</f>
@@ -4561,47 +5699,47 @@
       </c>
       <c r="I25" s="74">
         <f t="shared" si="3"/>
-        <v>0.54996702419382837</v>
-      </c>
-      <c r="K25" s="103"/>
+        <v>0.83109444965115065</v>
+      </c>
+      <c r="K25" s="101"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="77">
         <f>SUM(B4:B25)</f>
-        <v>3593461.8099999996</v>
+        <v>6273501.46</v>
       </c>
       <c r="C26" s="77">
         <f>SUM(C4:C25)</f>
-        <v>5083236.0999999996</v>
+        <v>7528567.9000000004</v>
       </c>
       <c r="D26" s="78">
         <f t="shared" si="0"/>
-        <v>1489774.29</v>
+        <v>1255066.4400000004</v>
       </c>
       <c r="E26" s="79">
         <f t="shared" si="1"/>
-        <v>0.41457913532132418</v>
+        <v>0.2000583642169107</v>
       </c>
       <c r="F26" s="77">
         <f>SUM(F4:F25)</f>
-        <v>8942741</v>
+        <v>8822741</v>
       </c>
       <c r="G26" s="80">
         <f t="shared" si="2"/>
-        <v>0.56842036462869716</v>
+        <v>0.85331394177841113</v>
       </c>
       <c r="H26" s="77">
         <f>SUM(H4:H25)</f>
-        <v>8126892.79</v>
+        <v>8023591.79</v>
       </c>
       <c r="I26" s="80">
         <f t="shared" si="3"/>
-        <v>0.62548334663093297</v>
-      </c>
-      <c r="K26" s="103"/>
+        <v>0.93830395377080866</v>
+      </c>
+      <c r="K26" s="101"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="12"/>
@@ -4626,8 +5764,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" style="94" bestFit="1" customWidth="1"/>
@@ -4638,8 +5776,8 @@
     <col min="6" max="6" width="17.1328125" style="85" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.59765625" style="85" customWidth="1"/>
     <col min="8" max="8" width="16" style="85" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" style="85" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1328125" style="85" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="85" customWidth="1"/>
+    <col min="10" max="10" width="17.1328125" style="85" customWidth="1"/>
     <col min="11" max="11" width="15.59765625" style="85" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="17.1328125" style="85" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="10.73046875" style="90" bestFit="1" customWidth="1"/>
@@ -4647,298 +5785,297 @@
     <col min="16" max="16384" width="9.1328125" style="85"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="81" customFormat="1">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:15" s="81" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A1" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-    </row>
-    <row r="2" spans="1:15" s="82" customFormat="1">
-      <c r="A2" s="120" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="136"/>
+    </row>
+    <row r="2" spans="1:15" s="82" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="139" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="137" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="138"/>
+      <c r="E2" s="135" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="136"/>
+      <c r="G2" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="136"/>
+      <c r="I2" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="136"/>
+      <c r="K2" s="135" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="136"/>
+      <c r="M2" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="121" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="121"/>
-      <c r="E2" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="117" t="s">
+      <c r="N2" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="122" t="s">
+      <c r="O2" s="131" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="122" t="s">
+    </row>
+    <row r="3" spans="1:15" s="82" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A3" s="140"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="102" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" s="82" customFormat="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="102" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="102" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="102" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="102" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="101" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="102" t="s">
+      <c r="I3" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="101" t="s">
+      <c r="J3" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="102" t="s">
+      <c r="K3" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="101" t="s">
+      <c r="L3" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="118"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="132"/>
     </row>
     <row r="4" spans="1:15" ht="15.75">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="7">
-        <v>400000</v>
+        <v>140000</v>
       </c>
       <c r="C4" s="7">
-        <v>4028</v>
+        <v>5040</v>
       </c>
       <c r="D4" s="7">
-        <v>1584</v>
+        <v>24998</v>
       </c>
       <c r="E4" s="1">
-        <v>8868</v>
+        <v>8580</v>
       </c>
       <c r="F4" s="99">
-        <v>29894</v>
+        <v>37118</v>
       </c>
       <c r="G4" s="1">
-        <v>14718</v>
-      </c>
-      <c r="H4" s="124">
-        <v>102982</v>
+        <v>11760</v>
+      </c>
+      <c r="H4" s="104">
+        <v>59635</v>
       </c>
       <c r="I4" s="1">
-        <v>307977</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0</v>
+        <v>46814</v>
+      </c>
+      <c r="J4" s="127">
+        <v>118383</v>
       </c>
       <c r="K4" s="1">
-        <v>385967</v>
+        <v>106127</v>
       </c>
       <c r="L4" s="7">
         <v>0</v>
       </c>
       <c r="M4" s="83">
-        <f t="shared" ref="M4:M25" si="0">H4/G4</f>
-        <v>6.9970104633781762</v>
+        <f t="shared" ref="M4:M24" si="0">J4/I4</f>
+        <v>2.5287948049728715</v>
       </c>
       <c r="N4" s="84">
-        <f t="shared" ref="N4:N25" si="1">H4/K4</f>
-        <v>0.26681555677039748</v>
+        <f t="shared" ref="N4:N24" si="1">J4/K4</f>
+        <v>1.1154842782703742</v>
       </c>
       <c r="O4" s="84">
-        <f t="shared" ref="O4:O25" si="2">H4/B4</f>
-        <v>0.25745499999999999</v>
+        <f t="shared" ref="O4:O24" si="2">J4/B4</f>
+        <v>0.84559285714285715</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7">
-        <v>140000</v>
+        <v>605910</v>
       </c>
       <c r="C5" s="7">
-        <v>5040</v>
+        <v>28123.89</v>
       </c>
       <c r="D5" s="7">
-        <v>24998</v>
+        <v>53385</v>
       </c>
       <c r="E5" s="1">
-        <v>8580</v>
+        <v>46657</v>
       </c>
       <c r="F5" s="99">
-        <v>37118</v>
+        <v>279964</v>
       </c>
       <c r="G5" s="1">
-        <v>11760</v>
-      </c>
-      <c r="H5" s="124">
-        <v>59635</v>
+        <v>207865</v>
+      </c>
+      <c r="H5" s="104">
+        <v>500173</v>
       </c>
       <c r="I5" s="1">
-        <v>46814</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
+        <v>330575</v>
+      </c>
+      <c r="J5" s="127">
+        <v>598581.24</v>
       </c>
       <c r="K5" s="1">
-        <v>106127</v>
+        <v>570761</v>
       </c>
       <c r="L5" s="7">
         <v>0</v>
       </c>
       <c r="M5" s="83">
         <f t="shared" si="0"/>
-        <v>5.0710034013605441</v>
+        <v>1.8107274899795811</v>
       </c>
       <c r="N5" s="84">
         <f t="shared" si="1"/>
-        <v>0.56192109453767658</v>
+        <v>1.0487423632658854</v>
       </c>
       <c r="O5" s="84">
         <f t="shared" si="2"/>
-        <v>0.42596428571428574</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.75">
+        <v>0.98790454027825914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="7">
-        <v>22777</v>
+        <v>10183</v>
       </c>
       <c r="C6" s="7">
-        <f>128*4</f>
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
-        <v>2688</v>
-      </c>
-      <c r="F6" s="99">
-        <v>5082</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2688</v>
-      </c>
-      <c r="H6" s="124">
-        <v>10991</v>
-      </c>
-      <c r="I6" s="1">
-        <v>22246</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>23526</v>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="128">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2106</v>
+      </c>
+      <c r="H6" s="129">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>3160</v>
+      </c>
+      <c r="J6" s="127">
+        <v>5632</v>
+      </c>
+      <c r="K6" s="7">
+        <v>3160</v>
       </c>
       <c r="L6" s="7">
         <v>0</v>
       </c>
       <c r="M6" s="83">
         <f t="shared" si="0"/>
-        <v>4.0889136904761907</v>
+        <v>1.7822784810126582</v>
       </c>
       <c r="N6" s="84">
         <f t="shared" si="1"/>
-        <v>0.46718524186006971</v>
+        <v>1.7822784810126582</v>
       </c>
       <c r="O6" s="84">
         <f t="shared" si="2"/>
-        <v>0.48254818457215615</v>
+        <v>0.55307866051261911</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
-        <v>31690</v>
+        <v>60500</v>
       </c>
       <c r="C7" s="7">
-        <v>1984</v>
+        <v>5713</v>
       </c>
       <c r="D7" s="7">
-        <v>1221</v>
-      </c>
-      <c r="E7" s="1">
-        <v>3126</v>
-      </c>
-      <c r="F7" s="99">
-        <v>15494</v>
-      </c>
-      <c r="G7" s="1">
-        <v>4584</v>
-      </c>
-      <c r="H7" s="124">
-        <v>15844</v>
-      </c>
-      <c r="I7" s="1">
-        <v>19424</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>28809</v>
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>11200</v>
+      </c>
+      <c r="F7" s="128">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>23368</v>
+      </c>
+      <c r="H7" s="104">
+        <v>18607</v>
+      </c>
+      <c r="I7" s="7">
+        <v>29237</v>
+      </c>
+      <c r="J7" s="127">
+        <v>51175</v>
+      </c>
+      <c r="K7" s="7">
+        <v>60308</v>
       </c>
       <c r="L7" s="7">
         <v>0</v>
       </c>
       <c r="M7" s="83">
         <f t="shared" si="0"/>
-        <v>3.4563699825479932</v>
+        <v>1.7503505831651673</v>
       </c>
       <c r="N7" s="84">
         <f t="shared" si="1"/>
-        <v>0.54996702419382837</v>
+        <v>0.84856072162897123</v>
       </c>
       <c r="O7" s="84">
         <f t="shared" si="2"/>
-        <v>0.4999684443041969</v>
+        <v>0.84586776859504131</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75">
@@ -4963,14 +6100,14 @@
       <c r="G8" s="1">
         <v>45398</v>
       </c>
-      <c r="H8" s="125">
+      <c r="H8" s="105">
         <v>136029.26999999999</v>
       </c>
       <c r="I8" s="1">
         <v>160280</v>
       </c>
-      <c r="J8" s="7">
-        <v>0</v>
+      <c r="J8" s="127">
+        <v>272876.99</v>
       </c>
       <c r="K8" s="1">
         <v>258783.18</v>
@@ -4980,215 +6117,215 @@
       </c>
       <c r="M8" s="83">
         <f t="shared" si="0"/>
-        <v>2.9963714260540111</v>
+        <v>1.7025018093336661</v>
       </c>
       <c r="N8" s="84">
         <f t="shared" si="1"/>
-        <v>0.52564958047118826</v>
+        <v>1.0544618471726022</v>
       </c>
       <c r="O8" s="84">
         <f t="shared" si="2"/>
-        <v>0.47542567654943185</v>
+        <v>0.95371185617273813</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7">
-        <v>328205</v>
+        <v>492201</v>
       </c>
       <c r="C9" s="7">
-        <v>3016</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7">
-        <v>66814</v>
+        <v>780</v>
       </c>
       <c r="E9" s="1">
-        <v>15350</v>
+        <v>13896</v>
       </c>
       <c r="F9" s="99">
-        <v>109815</v>
+        <v>18146.2</v>
       </c>
       <c r="G9" s="1">
-        <v>46157</v>
-      </c>
-      <c r="H9" s="124">
-        <v>133025</v>
+        <v>134945</v>
+      </c>
+      <c r="H9" s="104">
+        <v>125466</v>
       </c>
       <c r="I9" s="1">
-        <v>207772</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0</v>
+        <v>227158.2</v>
+      </c>
+      <c r="J9" s="130">
+        <v>366959.2</v>
       </c>
       <c r="K9" s="1">
-        <v>791907</v>
+        <v>505624.7</v>
       </c>
       <c r="L9" s="7">
         <v>0</v>
       </c>
       <c r="M9" s="83">
         <f t="shared" si="0"/>
-        <v>2.8820113958879476</v>
+        <v>1.6154345297682409</v>
       </c>
       <c r="N9" s="84">
         <f t="shared" si="1"/>
-        <v>0.1679805835786273</v>
+        <v>0.72575410180713085</v>
       </c>
       <c r="O9" s="84">
         <f t="shared" si="2"/>
-        <v>0.40531070519949419</v>
+        <v>0.74554744911123705</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7">
-        <v>605910</v>
+        <v>347083</v>
       </c>
       <c r="C10" s="7">
-        <v>28123.89</v>
+        <v>540</v>
       </c>
       <c r="D10" s="7">
-        <v>53385</v>
-      </c>
-      <c r="E10" s="1">
-        <v>46657</v>
+        <v>11300</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4068</v>
       </c>
       <c r="F10" s="99">
-        <v>279964</v>
-      </c>
-      <c r="G10" s="1">
-        <v>207865</v>
-      </c>
-      <c r="H10" s="124">
-        <v>500173</v>
-      </c>
-      <c r="I10" s="1">
-        <v>330575</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>570761</v>
+        <v>48850</v>
+      </c>
+      <c r="G10" s="7">
+        <v>109140</v>
+      </c>
+      <c r="H10" s="104">
+        <v>103766</v>
+      </c>
+      <c r="I10" s="7">
+        <v>232119</v>
+      </c>
+      <c r="J10" s="127">
+        <v>328977</v>
+      </c>
+      <c r="K10" s="7">
+        <v>339444</v>
       </c>
       <c r="L10" s="7">
         <v>0</v>
       </c>
       <c r="M10" s="83">
         <f t="shared" si="0"/>
-        <v>2.4062396266807782</v>
+        <v>1.4172773448102052</v>
       </c>
       <c r="N10" s="84">
         <f t="shared" si="1"/>
-        <v>0.87632651845518528</v>
+        <v>0.96916428041149649</v>
       </c>
       <c r="O10" s="84">
         <f t="shared" si="2"/>
-        <v>0.82549058441022594</v>
+        <v>0.94783380344182799</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B11" s="7">
-        <v>400000</v>
+        <v>216414</v>
       </c>
       <c r="C11" s="7">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D11" s="7">
-        <v>73676</v>
+        <v>27139</v>
       </c>
       <c r="E11" s="1">
-        <v>65282.02</v>
+        <v>52842</v>
       </c>
       <c r="F11" s="99">
-        <v>166704</v>
+        <v>27139</v>
       </c>
       <c r="G11" s="1">
-        <v>116328</v>
-      </c>
-      <c r="H11" s="124">
-        <v>240779</v>
-      </c>
-      <c r="I11" s="8">
-        <v>306475</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>381478</v>
+        <v>91590</v>
+      </c>
+      <c r="H11" s="108">
+        <v>148161</v>
+      </c>
+      <c r="I11" s="1">
+        <v>151692</v>
+      </c>
+      <c r="J11" s="127">
+        <v>210680</v>
+      </c>
+      <c r="K11" s="1">
+        <v>218934</v>
       </c>
       <c r="L11" s="7">
         <v>0</v>
       </c>
       <c r="M11" s="83">
         <f t="shared" si="0"/>
-        <v>2.0698284162024621</v>
+        <v>1.388866914537352</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="1"/>
-        <v>0.63117401265603779</v>
+        <v>0.96229914038020592</v>
       </c>
       <c r="O11" s="84">
         <f t="shared" si="2"/>
-        <v>0.60194749999999997</v>
+        <v>0.97350448677072643</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B12" s="7">
-        <v>1088112</v>
+        <v>1000000</v>
       </c>
       <c r="C12" s="7">
-        <v>25694</v>
+        <v>2474</v>
       </c>
       <c r="D12" s="7">
-        <v>144015</v>
+        <v>196331</v>
       </c>
       <c r="E12" s="1">
-        <v>111210</v>
-      </c>
-      <c r="F12" s="126">
-        <v>391500</v>
+        <v>54347</v>
+      </c>
+      <c r="F12" s="106">
+        <v>476520</v>
       </c>
       <c r="G12" s="1">
-        <v>362901.92</v>
-      </c>
-      <c r="H12" s="127">
-        <v>725000</v>
+        <v>383704</v>
+      </c>
+      <c r="H12" s="107">
+        <v>744088</v>
       </c>
       <c r="I12" s="1">
-        <v>913227</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0</v>
+        <v>641549</v>
+      </c>
+      <c r="J12" s="130">
+        <v>884773</v>
       </c>
       <c r="K12" s="1">
-        <v>1082590</v>
+        <v>771615</v>
       </c>
       <c r="L12" s="7">
         <v>0</v>
       </c>
       <c r="M12" s="83">
         <f t="shared" si="0"/>
-        <v>1.9977849662520386</v>
+        <v>1.379119911339586</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="1"/>
-        <v>0.66969027979198037</v>
+        <v>1.1466508556728421</v>
       </c>
       <c r="O12" s="84">
         <f t="shared" si="2"/>
-        <v>0.66629170526563442</v>
+        <v>0.88477300000000003</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75">
@@ -5213,14 +6350,14 @@
       <c r="G13" s="1">
         <v>81341</v>
       </c>
-      <c r="H13" s="124">
+      <c r="H13" s="104">
         <v>160101.42000000001</v>
       </c>
       <c r="I13" s="1">
         <v>281954</v>
       </c>
-      <c r="J13" s="7">
-        <v>0</v>
+      <c r="J13" s="127">
+        <v>388385</v>
       </c>
       <c r="K13" s="1">
         <v>394853</v>
@@ -5230,695 +6367,646 @@
       </c>
       <c r="M13" s="83">
         <f t="shared" si="0"/>
-        <v>1.9682745478909776</v>
+        <v>1.3774764677926186</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="1"/>
-        <v>0.40547094741587381</v>
+        <v>0.98361922031743454</v>
       </c>
       <c r="O13" s="84">
         <f t="shared" si="2"/>
-        <v>0.36731461215500039</v>
+        <v>0.89105696652671673</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B14" s="7">
-        <v>120000</v>
+        <v>328205</v>
       </c>
       <c r="C14" s="7">
-        <v>10261.700000000001</v>
+        <v>3016</v>
       </c>
       <c r="D14" s="7">
-        <v>94983</v>
+        <v>66814</v>
       </c>
       <c r="E14" s="1">
-        <v>46531.88</v>
-      </c>
-      <c r="F14" s="98">
-        <v>132578</v>
+        <v>15350</v>
+      </c>
+      <c r="F14" s="99">
+        <v>109815</v>
       </c>
       <c r="G14" s="1">
-        <v>84571.199999999997</v>
-      </c>
-      <c r="H14" s="124">
-        <v>165319</v>
+        <v>46157</v>
+      </c>
+      <c r="H14" s="104">
+        <v>133025</v>
       </c>
       <c r="I14" s="1">
-        <v>93456</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0</v>
+        <v>207772</v>
+      </c>
+      <c r="J14" s="127">
+        <v>257771</v>
       </c>
       <c r="K14" s="1">
-        <v>126966</v>
+        <v>791907</v>
       </c>
       <c r="L14" s="7">
         <v>0</v>
       </c>
       <c r="M14" s="83">
         <f t="shared" si="0"/>
-        <v>1.954790756191233</v>
+        <v>1.2406435900891362</v>
       </c>
       <c r="N14" s="84">
         <f t="shared" si="1"/>
-        <v>1.3020729959201676</v>
+        <v>0.32550665671600326</v>
       </c>
       <c r="O14" s="84">
         <f t="shared" si="2"/>
-        <v>1.3776583333333334</v>
+        <v>0.78539632242043844</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B15" s="7">
-        <v>1000000</v>
+        <v>31690</v>
       </c>
       <c r="C15" s="7">
-        <v>2474</v>
+        <v>1984</v>
       </c>
       <c r="D15" s="7">
-        <v>196331</v>
+        <v>1221</v>
       </c>
       <c r="E15" s="1">
-        <v>54347</v>
+        <v>3126</v>
       </c>
       <c r="F15" s="99">
-        <v>476520</v>
+        <v>15494</v>
       </c>
       <c r="G15" s="1">
-        <v>383704</v>
-      </c>
-      <c r="H15" s="124">
-        <v>744088</v>
+        <v>4584</v>
+      </c>
+      <c r="H15" s="104">
+        <v>15844</v>
       </c>
       <c r="I15" s="1">
-        <v>641549</v>
-      </c>
-      <c r="J15" s="7">
-        <v>0</v>
+        <v>19424</v>
+      </c>
+      <c r="J15" s="127">
+        <v>23943</v>
       </c>
       <c r="K15" s="1">
-        <v>771615</v>
+        <v>28809</v>
       </c>
       <c r="L15" s="7">
         <v>0</v>
       </c>
       <c r="M15" s="83">
         <f t="shared" si="0"/>
-        <v>1.9392239851552238</v>
+        <v>1.2326503294892917</v>
       </c>
       <c r="N15" s="84">
         <f t="shared" si="1"/>
-        <v>0.96432547319582951</v>
+        <v>0.83109444965115065</v>
       </c>
       <c r="O15" s="84">
         <f t="shared" si="2"/>
-        <v>0.74408799999999997</v>
+        <v>0.75553802461344277</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.75">
       <c r="A16" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B16" s="7">
-        <v>216414</v>
+        <v>272323</v>
       </c>
       <c r="C16" s="7">
-        <v>3500</v>
+        <v>7436</v>
       </c>
       <c r="D16" s="7">
-        <v>27139</v>
+        <v>2900</v>
       </c>
       <c r="E16" s="1">
-        <v>52842</v>
+        <v>76162</v>
       </c>
       <c r="F16" s="99">
-        <v>27139</v>
+        <v>25000</v>
       </c>
       <c r="G16" s="1">
-        <v>91590</v>
-      </c>
-      <c r="H16" s="128">
-        <v>148161</v>
+        <v>79866</v>
+      </c>
+      <c r="H16" s="104">
+        <v>78056</v>
       </c>
       <c r="I16" s="1">
-        <v>151692</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0</v>
+        <v>110615</v>
+      </c>
+      <c r="J16" s="127">
+        <v>128000</v>
       </c>
       <c r="K16" s="1">
-        <v>218934</v>
+        <v>160299.12</v>
       </c>
       <c r="L16" s="7">
         <v>0</v>
       </c>
       <c r="M16" s="83">
         <f t="shared" si="0"/>
-        <v>1.6176547658041271</v>
+        <v>1.1571667495366813</v>
       </c>
       <c r="N16" s="84">
         <f t="shared" si="1"/>
-        <v>0.67673819507248756</v>
+        <v>0.79850719080678678</v>
       </c>
       <c r="O16" s="84">
         <f t="shared" si="2"/>
-        <v>0.68461837034572626</v>
+        <v>0.47003007458055324</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.75">
       <c r="A17" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B17" s="7">
-        <v>316098</v>
+        <v>1088112</v>
       </c>
       <c r="C17" s="7">
-        <v>32322</v>
+        <v>25694</v>
       </c>
       <c r="D17" s="7">
-        <v>7240</v>
+        <v>144015</v>
       </c>
       <c r="E17" s="1">
-        <v>54270.796000000002</v>
+        <v>111210</v>
       </c>
       <c r="F17" s="99">
-        <v>7240</v>
+        <v>391500</v>
       </c>
       <c r="G17" s="1">
-        <v>85480</v>
-      </c>
-      <c r="H17" s="124">
-        <v>105528</v>
+        <v>362901.92</v>
+      </c>
+      <c r="H17" s="104">
+        <v>725000</v>
       </c>
       <c r="I17" s="1">
-        <v>235524</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0</v>
+        <v>913227</v>
+      </c>
+      <c r="J17" s="127">
+        <v>1050000</v>
       </c>
       <c r="K17" s="1">
-        <v>235524</v>
+        <v>1082590</v>
       </c>
       <c r="L17" s="7">
         <v>0</v>
       </c>
       <c r="M17" s="83">
         <f t="shared" si="0"/>
-        <v>1.2345343940102949</v>
+        <v>1.1497688964518131</v>
       </c>
       <c r="N17" s="84">
         <f t="shared" si="1"/>
-        <v>0.44805624904468333</v>
+        <v>0.96989626728493705</v>
       </c>
       <c r="O17" s="84">
         <f t="shared" si="2"/>
-        <v>0.33384583262152878</v>
+        <v>0.96497419383298777</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15.75">
       <c r="A18" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B18" s="7">
-        <v>1250069</v>
+        <v>173348</v>
       </c>
       <c r="C18" s="7">
-        <v>157000</v>
+        <v>76390.25</v>
       </c>
       <c r="D18" s="7">
-        <v>120850</v>
+        <v>90335</v>
       </c>
       <c r="E18" s="1">
-        <v>297052</v>
+        <v>104565.47</v>
       </c>
       <c r="F18" s="99">
-        <v>820850</v>
+        <v>119613.62</v>
       </c>
       <c r="G18" s="1">
-        <v>845294.69</v>
-      </c>
-      <c r="H18" s="124">
-        <v>1001903</v>
+        <v>131239</v>
+      </c>
+      <c r="H18" s="104">
+        <v>127724.41</v>
       </c>
       <c r="I18" s="1">
-        <v>1083892</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
+        <v>152953.26</v>
+      </c>
+      <c r="J18" s="127">
+        <v>175650.47</v>
       </c>
       <c r="K18" s="1">
-        <v>1083892</v>
+        <v>157588</v>
       </c>
       <c r="L18" s="7">
         <v>0</v>
       </c>
       <c r="M18" s="83">
         <f t="shared" si="0"/>
-        <v>1.185270665784024</v>
+        <v>1.1483931104181762</v>
       </c>
       <c r="N18" s="84">
         <f t="shared" si="1"/>
-        <v>0.92435685474198537</v>
+        <v>1.1146183085006474</v>
       </c>
       <c r="O18" s="84">
         <f t="shared" si="2"/>
-        <v>0.80147815840565606</v>
+        <v>1.0132823568774949</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15.75">
       <c r="A19" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B19" s="7">
-        <v>272323</v>
+        <v>1250069</v>
       </c>
       <c r="C19" s="7">
-        <v>7436</v>
+        <v>157000</v>
       </c>
       <c r="D19" s="7">
-        <v>2900</v>
+        <v>120850</v>
       </c>
       <c r="E19" s="1">
-        <v>76162</v>
+        <v>297052</v>
       </c>
       <c r="F19" s="99">
-        <v>25000</v>
+        <v>820850</v>
       </c>
       <c r="G19" s="1">
-        <v>79866</v>
-      </c>
-      <c r="H19" s="124">
-        <v>78056</v>
+        <v>845294.69</v>
+      </c>
+      <c r="H19" s="104">
+        <v>1001903</v>
       </c>
       <c r="I19" s="1">
-        <v>110615</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0</v>
+        <v>1083892</v>
+      </c>
+      <c r="J19" s="127">
+        <v>1120583</v>
       </c>
       <c r="K19" s="1">
-        <v>160299.12</v>
+        <v>1083892</v>
       </c>
       <c r="L19" s="7">
         <v>0</v>
       </c>
       <c r="M19" s="83">
         <f t="shared" si="0"/>
-        <v>0.97733703954123152</v>
+        <v>1.0338511586025176</v>
       </c>
       <c r="N19" s="84">
         <f t="shared" si="1"/>
-        <v>0.48693966629386365</v>
+        <v>1.0338511586025176</v>
       </c>
       <c r="O19" s="84">
         <f t="shared" si="2"/>
-        <v>0.28663021485515361</v>
+        <v>0.89641691778613819</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.75">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B20" s="7">
-        <v>173348</v>
+        <v>400000</v>
       </c>
       <c r="C20" s="7">
-        <v>76390.25</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7">
-        <v>90335</v>
+        <v>73676</v>
       </c>
       <c r="E20" s="1">
-        <v>104565.47</v>
-      </c>
-      <c r="F20" s="99">
-        <v>119613.62</v>
+        <v>65282.02</v>
+      </c>
+      <c r="F20" s="106">
+        <v>166704</v>
       </c>
       <c r="G20" s="1">
-        <v>131239</v>
-      </c>
-      <c r="H20" s="124">
-        <v>127724.41</v>
-      </c>
-      <c r="I20" s="1">
-        <v>152953.26</v>
-      </c>
-      <c r="J20" s="7">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>157588</v>
+        <v>116328</v>
+      </c>
+      <c r="H20" s="104">
+        <v>240779</v>
+      </c>
+      <c r="I20" s="8">
+        <v>306475</v>
+      </c>
+      <c r="J20" s="127">
+        <v>313593</v>
+      </c>
+      <c r="K20" s="8">
+        <v>381478</v>
       </c>
       <c r="L20" s="7">
         <v>0</v>
       </c>
       <c r="M20" s="83">
         <f t="shared" si="0"/>
-        <v>0.97321992700340598</v>
+        <v>1.0232253854311117</v>
       </c>
       <c r="N20" s="84">
         <f t="shared" si="1"/>
-        <v>0.81049578648120413</v>
+        <v>0.82204740509282315</v>
       </c>
       <c r="O20" s="84">
         <f t="shared" si="2"/>
-        <v>0.73680925075570536</v>
+        <v>0.78398250000000003</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15.75">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B21" s="7">
-        <v>347083</v>
+        <v>316098</v>
       </c>
       <c r="C21" s="7">
-        <v>540</v>
+        <v>32322</v>
       </c>
       <c r="D21" s="7">
-        <v>11300</v>
-      </c>
-      <c r="E21" s="7">
-        <v>4068</v>
-      </c>
-      <c r="F21" s="126">
-        <v>48850</v>
-      </c>
-      <c r="G21" s="7">
-        <v>109140</v>
-      </c>
-      <c r="H21" s="124">
-        <v>103766</v>
-      </c>
-      <c r="I21" s="7">
-        <v>232119</v>
-      </c>
-      <c r="J21" s="7">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7">
-        <v>339444</v>
+        <v>7240</v>
+      </c>
+      <c r="E21" s="1">
+        <v>54270.796000000002</v>
+      </c>
+      <c r="F21" s="99">
+        <v>7240</v>
+      </c>
+      <c r="G21" s="1">
+        <v>85480</v>
+      </c>
+      <c r="H21" s="104">
+        <v>105528</v>
+      </c>
+      <c r="I21" s="1">
+        <v>235524</v>
+      </c>
+      <c r="J21" s="127">
+        <v>229172</v>
+      </c>
+      <c r="K21" s="1">
+        <v>235524</v>
       </c>
       <c r="L21" s="7">
         <v>0</v>
       </c>
       <c r="M21" s="83">
         <f t="shared" si="0"/>
-        <v>0.95076049111233274</v>
+        <v>0.97303034934868637</v>
       </c>
       <c r="N21" s="84">
         <f t="shared" si="1"/>
-        <v>0.30569401727530904</v>
+        <v>0.97303034934868637</v>
       </c>
       <c r="O21" s="84">
         <f t="shared" si="2"/>
-        <v>0.29896595338867071</v>
+        <v>0.72500300539706042</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15.75">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7">
-        <v>492201</v>
+        <v>400000</v>
       </c>
       <c r="C22" s="7">
-        <v>0</v>
+        <v>4028</v>
       </c>
       <c r="D22" s="7">
-        <v>780</v>
+        <v>1584</v>
       </c>
       <c r="E22" s="1">
-        <v>13896</v>
+        <v>8868</v>
       </c>
       <c r="F22" s="99">
-        <v>18146.2</v>
+        <v>29894</v>
       </c>
       <c r="G22" s="1">
-        <v>134945</v>
-      </c>
-      <c r="H22" s="124">
-        <v>125466</v>
+        <v>14718</v>
+      </c>
+      <c r="H22" s="104">
+        <v>102982</v>
       </c>
       <c r="I22" s="1">
-        <v>227158.2</v>
-      </c>
-      <c r="J22" s="7">
-        <v>0</v>
+        <v>307977</v>
+      </c>
+      <c r="J22" s="127">
+        <v>281669</v>
       </c>
       <c r="K22" s="1">
-        <v>505624.7</v>
+        <v>385967</v>
       </c>
       <c r="L22" s="7">
         <v>0</v>
       </c>
       <c r="M22" s="83">
         <f t="shared" si="0"/>
-        <v>0.9297565674904591</v>
+        <v>0.91457803667156967</v>
       </c>
       <c r="N22" s="84">
         <f t="shared" si="1"/>
-        <v>0.24814056749996588</v>
+        <v>0.72977482530889948</v>
       </c>
       <c r="O22" s="84">
         <f t="shared" si="2"/>
-        <v>0.25490805585522985</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="135" customFormat="1" ht="15.75">
-      <c r="A23" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="130">
-        <v>60500</v>
-      </c>
-      <c r="C23" s="130">
-        <v>5713</v>
-      </c>
-      <c r="D23" s="130">
-        <v>0</v>
-      </c>
-      <c r="E23" s="130">
-        <v>11200</v>
-      </c>
-      <c r="F23" s="131">
-        <v>0</v>
-      </c>
-      <c r="G23" s="130">
-        <v>23368</v>
-      </c>
-      <c r="H23" s="132">
-        <v>18607</v>
-      </c>
-      <c r="I23" s="130">
-        <v>29237</v>
-      </c>
-      <c r="J23" s="130">
-        <v>0</v>
-      </c>
-      <c r="K23" s="130">
-        <v>60308</v>
-      </c>
-      <c r="L23" s="130">
-        <v>0</v>
-      </c>
-      <c r="M23" s="133">
+        <v>0.70417249999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="7">
+        <v>945837</v>
+      </c>
+      <c r="C23" s="7">
+        <v>15909</v>
+      </c>
+      <c r="D23" s="7">
+        <v>265486</v>
+      </c>
+      <c r="E23" s="7">
+        <v>724172</v>
+      </c>
+      <c r="F23" s="100">
+        <v>289147</v>
+      </c>
+      <c r="G23" s="7">
+        <v>728417</v>
+      </c>
+      <c r="H23" s="105">
+        <v>380058</v>
+      </c>
+      <c r="I23" s="7">
+        <v>808858</v>
+      </c>
+      <c r="J23" s="127">
+        <v>702800</v>
+      </c>
+      <c r="K23" s="7">
+        <v>909183</v>
+      </c>
+      <c r="L23" s="7">
+        <v>0</v>
+      </c>
+      <c r="M23" s="83">
         <f t="shared" si="0"/>
-        <v>0.79625984251968507</v>
-      </c>
-      <c r="N23" s="134">
+        <v>0.86887933357894709</v>
+      </c>
+      <c r="N23" s="84">
         <f t="shared" si="1"/>
-        <v>0.3085328646282417</v>
-      </c>
-      <c r="O23" s="134">
-        <f t="shared" si="2"/>
-        <v>0.30755371900826445</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="135" customFormat="1" ht="15.75">
-      <c r="A24" s="129" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="130">
-        <v>945837</v>
-      </c>
-      <c r="C24" s="130">
-        <v>15909</v>
-      </c>
-      <c r="D24" s="130">
-        <v>265486</v>
-      </c>
-      <c r="E24" s="130">
-        <v>724172</v>
-      </c>
-      <c r="F24" s="136">
-        <v>289147</v>
-      </c>
-      <c r="G24" s="130">
-        <v>728417</v>
-      </c>
-      <c r="H24" s="137">
-        <v>380058</v>
-      </c>
-      <c r="I24" s="130">
-        <v>808858</v>
-      </c>
-      <c r="J24" s="130">
-        <v>0</v>
-      </c>
-      <c r="K24" s="130">
-        <v>909183</v>
-      </c>
-      <c r="L24" s="130">
-        <v>0</v>
-      </c>
-      <c r="M24" s="133">
+        <v>0.77300169492830373</v>
+      </c>
+      <c r="O23" s="84">
+        <f t="shared" si="2"/>
+        <v>0.74304557762066825</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15.75">
+      <c r="A24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="7">
+        <v>22777</v>
+      </c>
+      <c r="C24" s="7">
+        <f>128*4</f>
+        <v>512</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2688</v>
+      </c>
+      <c r="F24" s="99">
+        <v>5082</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2688</v>
+      </c>
+      <c r="H24" s="104">
+        <v>10991</v>
+      </c>
+      <c r="I24" s="1">
+        <v>22246</v>
+      </c>
+      <c r="J24" s="127">
+        <v>18964</v>
+      </c>
+      <c r="K24" s="1">
+        <v>23526</v>
+      </c>
+      <c r="L24" s="7">
+        <v>0</v>
+      </c>
+      <c r="M24" s="83">
         <f t="shared" si="0"/>
-        <v>0.52175882770446047</v>
-      </c>
-      <c r="N24" s="134">
+        <v>0.85246785939045222</v>
+      </c>
+      <c r="N24" s="84">
         <f t="shared" si="1"/>
-        <v>0.41802145442666661</v>
-      </c>
-      <c r="O24" s="134">
-        <f t="shared" si="2"/>
-        <v>0.40182187839976657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="135" customFormat="1">
-      <c r="A25" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="130">
-        <v>10183</v>
-      </c>
-      <c r="C25" s="130">
-        <v>0</v>
-      </c>
-      <c r="D25" s="130">
-        <v>0</v>
-      </c>
-      <c r="E25" s="130">
-        <v>0</v>
-      </c>
-      <c r="F25" s="131">
-        <v>0</v>
-      </c>
-      <c r="G25" s="130">
-        <v>2106</v>
-      </c>
-      <c r="H25" s="138">
-        <v>0</v>
-      </c>
-      <c r="I25" s="130">
-        <v>3160</v>
-      </c>
-      <c r="J25" s="130">
-        <v>0</v>
-      </c>
-      <c r="K25" s="130">
-        <v>3160</v>
-      </c>
-      <c r="L25" s="130">
-        <v>0</v>
-      </c>
-      <c r="M25" s="133">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="134">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="134">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>0.80608688259797667</v>
+      </c>
+      <c r="O24" s="84">
+        <f t="shared" si="2"/>
+        <v>0.83259428370724853</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="86"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="89"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="86"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="89"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92">
-        <f t="shared" ref="B27:L27" si="3">SUM(B4:B25)</f>
-        <v>8942741</v>
-      </c>
-      <c r="C27" s="92">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92">
+        <f t="shared" ref="B26:L26" si="3">SUM(B4:B24)</f>
+        <v>8822741</v>
+      </c>
+      <c r="C26" s="92">
         <f t="shared" si="3"/>
-        <v>385680.74</v>
-      </c>
-      <c r="D27" s="92">
+        <v>375419.04000000004</v>
+      </c>
+      <c r="D26" s="92">
         <f t="shared" si="3"/>
-        <v>1235728</v>
-      </c>
-      <c r="E27" s="92">
+        <v>1140745</v>
+      </c>
+      <c r="E26" s="92">
         <f t="shared" si="3"/>
-        <v>1747396.206</v>
-      </c>
-      <c r="F27" s="93">
+        <v>1700864.3259999999</v>
+      </c>
+      <c r="F26" s="93">
         <f t="shared" si="3"/>
-        <v>3195708.93</v>
-      </c>
-      <c r="G27" s="92">
+        <v>3063130.93</v>
+      </c>
+      <c r="G26" s="92">
         <f t="shared" si="3"/>
-        <v>3593461.8099999996</v>
-      </c>
-      <c r="H27" s="92">
+        <v>3508890.61</v>
+      </c>
+      <c r="H26" s="92">
         <f t="shared" si="3"/>
-        <v>5083236.0999999996</v>
-      </c>
-      <c r="I27" s="92">
+        <v>4917917.0999999996</v>
+      </c>
+      <c r="I26" s="92">
         <f t="shared" si="3"/>
-        <v>6366957.46</v>
-      </c>
-      <c r="J27" s="92">
+        <v>6273501.46</v>
+      </c>
+      <c r="J26" s="92">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="92">
+        <v>7528567.8999999994</v>
+      </c>
+      <c r="K26" s="92">
         <f t="shared" si="3"/>
-        <v>8597339</v>
-      </c>
-      <c r="L27" s="92">
+        <v>8470373</v>
+      </c>
+      <c r="L26" s="92">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="90">
-        <f>H27/G27</f>
-        <v>1.4145791353213242</v>
-      </c>
-      <c r="N27" s="90">
-        <f>H27/K27</f>
-        <v>0.59125691100467248</v>
-      </c>
-      <c r="O27" s="90">
-        <f>H27/B27</f>
-        <v>0.56842036462869716</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="90" customFormat="1">
-      <c r="A28" s="89"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
+      <c r="M26" s="90">
+        <f>J26/I26</f>
+        <v>1.2000583642169105</v>
+      </c>
+      <c r="N26" s="90">
+        <f>J26/K26</f>
+        <v>0.88881185043444955</v>
+      </c>
+      <c r="O26" s="90">
+        <f>J26/B26</f>
+        <v>0.85331394177841102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="90" customFormat="1">
+      <c r="A27" s="89"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5937,6 +7025,7 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5952,19 +7041,19 @@
   <sheetData>
     <row r="2" spans="1:3" ht="21.75" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="3" spans="1:3" ht="23.35" customHeight="1">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="2">
         <f>粽子销售PICKUP!A4</f>
-        <v>香港喜來登</v>
+        <v>0</v>
       </c>
       <c r="B3" s="75"/>
       <c r="C3" s="75"/>
@@ -6171,93 +7260,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="26" customFormat="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="122" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="25"/>
+    </row>
+    <row r="2" spans="1:15" s="27" customFormat="1">
+      <c r="A2" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="124" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="25"/>
-    </row>
-    <row r="2" spans="1:15" s="27" customFormat="1">
-      <c r="A2" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="114" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="115" t="s">
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115" t="s">
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="116" t="s">
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="109" t="s">
+    </row>
+    <row r="3" spans="1:15" s="27" customFormat="1" ht="27.75">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="28" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" s="27" customFormat="1" ht="27.75">
-      <c r="A3" s="113"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="28" t="s">
+      <c r="D3" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="F3" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="G3" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="H3" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="29" t="s">
+      <c r="J3" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="31" t="s">
+      <c r="L3" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="L3" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="33" t="s">
-        <v>59</v>
-      </c>
       <c r="N3" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="O3" s="109"/>
+        <v>54</v>
+      </c>
+      <c r="O3" s="119"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="34">
@@ -6426,7 +7515,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="34">
         <v>1000</v>
@@ -7465,8 +8554,8 @@
       <c r="O26" s="62"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="110"/>
-      <c r="B27" s="111"/>
+      <c r="A27" s="120"/>
+      <c r="B27" s="121"/>
       <c r="C27" s="64">
         <f>SUM(C4:C25)</f>
         <v>102490</v>
@@ -7565,64 +8654,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="81" customFormat="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
     </row>
     <row r="2" spans="1:15" s="82" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="115" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="116"/>
+      <c r="E2" s="114" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="114"/>
+      <c r="M2" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="121" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="121"/>
-      <c r="E2" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="117" t="s">
+      <c r="N2" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="O2" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="117" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="3" spans="1:15" s="82" customFormat="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+      <c r="A3" s="115"/>
+      <c r="B3" s="115"/>
       <c r="C3" s="97" t="s">
         <v>22</v>
       </c>
@@ -7658,55 +8747,21 @@
       <c r="O3" s="118"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="7">
-        <v>120000</v>
-      </c>
-      <c r="C4" s="7">
-        <v>10261.700000000001</v>
-      </c>
-      <c r="D4" s="7">
-        <v>94983</v>
-      </c>
-      <c r="E4" s="1">
-        <v>46531.88</v>
-      </c>
-      <c r="F4" s="98">
-        <v>132578</v>
-      </c>
-      <c r="G4" s="1">
-        <v>84571.199999999997</v>
-      </c>
-      <c r="H4" s="7">
-        <f>VLOOKUP($A4,Sheet1!$A$4:$H$25,COLUMN(H1),0)</f>
-        <v>165319</v>
-      </c>
-      <c r="I4" s="1">
-        <v>93456</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>126966</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="83">
-        <f t="shared" ref="M4:M25" si="0">F4/E4</f>
-        <v>2.8491864072545532</v>
-      </c>
-      <c r="N4" s="84">
-        <f t="shared" ref="N4:N25" si="1">F4/K4</f>
-        <v>1.0442008096655797</v>
-      </c>
-      <c r="O4" s="84">
-        <f t="shared" ref="O4:O25" si="2">F4/B4</f>
-        <v>1.1048166666666666</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="84"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
@@ -7738,24 +8793,26 @@
         <v>152953.26</v>
       </c>
       <c r="J5" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A5,Sheet1!$A$4:$Z$25,COLUMN(J2),0)</f>
+        <v>175650.47</v>
       </c>
       <c r="K5" s="1">
         <v>157588</v>
       </c>
       <c r="L5" s="7">
+        <f>VLOOKUP($A5,Sheet1!$A$4:$Z$25,COLUMN(L2),0)</f>
         <v>0</v>
       </c>
       <c r="M5" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M4:M25" si="0">F5/E5</f>
         <v>1.143911273960706</v>
       </c>
       <c r="N5" s="84">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="N4:N25" si="1">F5/K5</f>
         <v>0.75902746402010302</v>
       </c>
       <c r="O5" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="O4:O25" si="2">F5/B5</f>
         <v>0.69002019059925701</v>
       </c>
     </row>
@@ -7789,12 +8846,14 @@
         <v>1083892</v>
       </c>
       <c r="J6" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A6,Sheet1!$A$4:$Z$25,COLUMN(J3),0)</f>
+        <v>1120583</v>
       </c>
       <c r="K6" s="1">
         <v>1083892</v>
       </c>
       <c r="L6" s="7">
+        <f>VLOOKUP($A6,Sheet1!$A$4:$Z$25,COLUMN(L3),0)</f>
         <v>0</v>
       </c>
       <c r="M6" s="83">
@@ -7840,12 +8899,14 @@
         <v>330575</v>
       </c>
       <c r="J7" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A7,Sheet1!$A$4:$Z$25,COLUMN(J4),0)</f>
+        <v>598581.24</v>
       </c>
       <c r="K7" s="1">
         <v>570761</v>
       </c>
       <c r="L7" s="7">
+        <f>VLOOKUP($A7,Sheet1!$A$4:$Z$25,COLUMN(L4),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="83">
@@ -7891,12 +8952,14 @@
         <v>913227</v>
       </c>
       <c r="J8" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A8,Sheet1!$A$4:$Z$25,COLUMN(J5),0)</f>
+        <v>1050000</v>
       </c>
       <c r="K8" s="1">
         <v>1082590</v>
       </c>
       <c r="L8" s="7">
+        <f>VLOOKUP($A8,Sheet1!$A$4:$Z$25,COLUMN(L5),0)</f>
         <v>0</v>
       </c>
       <c r="M8" s="83">
@@ -7942,12 +9005,14 @@
         <v>808858</v>
       </c>
       <c r="J9" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A9,Sheet1!$A$4:$Z$25,COLUMN(J6),0)</f>
+        <v>702800</v>
       </c>
       <c r="K9" s="1">
         <v>909183</v>
       </c>
       <c r="L9" s="7">
+        <f>VLOOKUP($A9,Sheet1!$A$4:$Z$25,COLUMN(L6),0)</f>
         <v>0</v>
       </c>
       <c r="M9" s="83">
@@ -7993,12 +9058,14 @@
         <v>110615</v>
       </c>
       <c r="J10" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A10,Sheet1!$A$4:$Z$25,COLUMN(J7),0)</f>
+        <v>128000</v>
       </c>
       <c r="K10" s="1">
         <v>160299.12</v>
       </c>
       <c r="L10" s="7">
+        <f>VLOOKUP($A10,Sheet1!$A$4:$Z$25,COLUMN(L7),0)</f>
         <v>0</v>
       </c>
       <c r="M10" s="83">
@@ -8045,12 +9112,14 @@
         <v>22246</v>
       </c>
       <c r="J11" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A11,Sheet1!$A$4:$Z$25,COLUMN(J8),0)</f>
+        <v>18964</v>
       </c>
       <c r="K11" s="1">
         <v>23526</v>
       </c>
       <c r="L11" s="7">
+        <f>VLOOKUP($A11,Sheet1!$A$4:$Z$25,COLUMN(L8),0)</f>
         <v>0</v>
       </c>
       <c r="M11" s="83">
@@ -8096,12 +9165,14 @@
         <v>3160</v>
       </c>
       <c r="J12" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A12,Sheet1!$A$4:$Z$25,COLUMN(J9),0)</f>
+        <v>5632</v>
       </c>
       <c r="K12" s="1">
         <v>3160</v>
       </c>
       <c r="L12" s="7">
+        <f>VLOOKUP($A12,Sheet1!$A$4:$Z$25,COLUMN(L9),0)</f>
         <v>0</v>
       </c>
       <c r="M12" s="83" t="e">
@@ -8147,12 +9218,14 @@
         <v>307977</v>
       </c>
       <c r="J13" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A13,Sheet1!$A$4:$Z$25,COLUMN(J10),0)</f>
+        <v>281669</v>
       </c>
       <c r="K13" s="1">
         <v>385967</v>
       </c>
       <c r="L13" s="7">
+        <f>VLOOKUP($A13,Sheet1!$A$4:$Z$25,COLUMN(L10),0)</f>
         <v>0</v>
       </c>
       <c r="M13" s="83">
@@ -8198,12 +9271,14 @@
         <v>235524</v>
       </c>
       <c r="J14" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A14,Sheet1!$A$4:$Z$25,COLUMN(J11),0)</f>
+        <v>229172</v>
       </c>
       <c r="K14" s="1">
         <v>235524</v>
       </c>
       <c r="L14" s="7">
+        <f>VLOOKUP($A14,Sheet1!$A$4:$Z$25,COLUMN(L11),0)</f>
         <v>0</v>
       </c>
       <c r="M14" s="83">
@@ -8249,12 +9324,14 @@
         <v>281954</v>
       </c>
       <c r="J15" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A15,Sheet1!$A$4:$Z$25,COLUMN(J12),0)</f>
+        <v>388385</v>
       </c>
       <c r="K15" s="1">
         <v>394853</v>
       </c>
       <c r="L15" s="7">
+        <f>VLOOKUP($A15,Sheet1!$A$4:$Z$25,COLUMN(L12),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="83">
@@ -8300,12 +9377,14 @@
         <v>151692</v>
       </c>
       <c r="J16" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A16,Sheet1!$A$4:$Z$25,COLUMN(J13),0)</f>
+        <v>210680</v>
       </c>
       <c r="K16" s="1">
         <v>218934</v>
       </c>
       <c r="L16" s="7">
+        <f>VLOOKUP($A16,Sheet1!$A$4:$Z$25,COLUMN(L13),0)</f>
         <v>0</v>
       </c>
       <c r="M16" s="83">
@@ -8351,12 +9430,14 @@
         <v>227158.2</v>
       </c>
       <c r="J17" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A17,Sheet1!$A$4:$Z$25,COLUMN(J14),0)</f>
+        <v>366959.2</v>
       </c>
       <c r="K17" s="1">
         <v>505624.7</v>
       </c>
       <c r="L17" s="7">
+        <f>VLOOKUP($A17,Sheet1!$A$4:$Z$25,COLUMN(L14),0)</f>
         <v>0</v>
       </c>
       <c r="M17" s="83">
@@ -8402,12 +9483,14 @@
         <v>232119</v>
       </c>
       <c r="J18" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A18,Sheet1!$A$4:$Z$25,COLUMN(J15),0)</f>
+        <v>328977</v>
       </c>
       <c r="K18" s="7">
         <v>339444</v>
       </c>
       <c r="L18" s="7">
+        <f>VLOOKUP($A18,Sheet1!$A$4:$Z$25,COLUMN(L15),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="83">
@@ -8453,12 +9536,14 @@
         <v>641549</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A19,Sheet1!$A$4:$Z$25,COLUMN(J16),0)</f>
+        <v>884773</v>
       </c>
       <c r="K19" s="1">
         <v>771615</v>
       </c>
       <c r="L19" s="7">
+        <f>VLOOKUP($A19,Sheet1!$A$4:$Z$25,COLUMN(L16),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="83">
@@ -8504,12 +9589,14 @@
         <v>46814</v>
       </c>
       <c r="J20" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A20,Sheet1!$A$4:$Z$25,COLUMN(J17),0)</f>
+        <v>118383</v>
       </c>
       <c r="K20" s="1">
         <v>106127</v>
       </c>
       <c r="L20" s="7">
+        <f>VLOOKUP($A20,Sheet1!$A$4:$Z$25,COLUMN(L17),0)</f>
         <v>0</v>
       </c>
       <c r="M20" s="83">
@@ -8555,12 +9642,14 @@
         <v>29237</v>
       </c>
       <c r="J21" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A21,Sheet1!$A$4:$Z$25,COLUMN(J18),0)</f>
+        <v>51175</v>
       </c>
       <c r="K21" s="1">
         <v>60308</v>
       </c>
       <c r="L21" s="7">
+        <f>VLOOKUP($A21,Sheet1!$A$4:$Z$25,COLUMN(L18),0)</f>
         <v>0</v>
       </c>
       <c r="M21" s="83">
@@ -8606,12 +9695,14 @@
         <v>160280</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A22,Sheet1!$A$4:$Z$25,COLUMN(J19),0)</f>
+        <v>272876.99</v>
       </c>
       <c r="K22" s="1">
         <v>258783.18</v>
       </c>
       <c r="L22" s="7">
+        <f>VLOOKUP($A22,Sheet1!$A$4:$Z$25,COLUMN(L19),0)</f>
         <v>0</v>
       </c>
       <c r="M22" s="83">
@@ -8657,12 +9748,14 @@
         <v>306475</v>
       </c>
       <c r="J23" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A23,Sheet1!$A$4:$Z$25,COLUMN(J20),0)</f>
+        <v>313593</v>
       </c>
       <c r="K23" s="8">
         <v>381478</v>
       </c>
       <c r="L23" s="7">
+        <f>VLOOKUP($A23,Sheet1!$A$4:$Z$25,COLUMN(L20),0)</f>
         <v>0</v>
       </c>
       <c r="M23" s="83">
@@ -8708,12 +9801,14 @@
         <v>207772</v>
       </c>
       <c r="J24" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A24,Sheet1!$A$4:$Z$25,COLUMN(J21),0)</f>
+        <v>257771</v>
       </c>
       <c r="K24" s="1">
         <v>791907</v>
       </c>
       <c r="L24" s="7">
+        <f>VLOOKUP($A24,Sheet1!$A$4:$Z$25,COLUMN(L21),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="83">
@@ -8759,12 +9854,14 @@
         <v>19424</v>
       </c>
       <c r="J25" s="7">
-        <v>0</v>
+        <f>VLOOKUP($A25,Sheet1!$A$4:$Z$25,COLUMN(J22),0)</f>
+        <v>23943</v>
       </c>
       <c r="K25" s="1">
         <v>28809</v>
       </c>
       <c r="L25" s="7">
+        <f>VLOOKUP($A25,Sheet1!$A$4:$Z$25,COLUMN(L22),0)</f>
         <v>0</v>
       </c>
       <c r="M25" s="83">
@@ -8799,43 +9896,43 @@
       <c r="A27" s="91"/>
       <c r="B27" s="92">
         <f t="shared" ref="B27:L27" si="3">SUM(B4:B25)</f>
-        <v>8942741</v>
+        <v>8822741</v>
       </c>
       <c r="C27" s="92">
         <f t="shared" si="3"/>
-        <v>385680.74000000005</v>
+        <v>375419.04000000004</v>
       </c>
       <c r="D27" s="92">
         <f t="shared" si="3"/>
-        <v>1235728</v>
+        <v>1140745</v>
       </c>
       <c r="E27" s="92">
         <f t="shared" si="3"/>
-        <v>1747396.2060000002</v>
+        <v>1700864.3260000001</v>
       </c>
       <c r="F27" s="93">
         <f t="shared" si="3"/>
-        <v>3195708.93</v>
+        <v>3063130.93</v>
       </c>
       <c r="G27" s="92">
         <f t="shared" si="3"/>
-        <v>3593461.8099999996</v>
+        <v>3508890.61</v>
       </c>
       <c r="H27" s="92">
         <f t="shared" si="3"/>
-        <v>5083236.0999999996</v>
+        <v>4917917.0999999996</v>
       </c>
       <c r="I27" s="92">
         <f t="shared" si="3"/>
-        <v>6366957.46</v>
+        <v>6273501.46</v>
       </c>
       <c r="J27" s="92">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7528567.9000000004</v>
       </c>
       <c r="K27" s="92">
         <f t="shared" si="3"/>
-        <v>8597339</v>
+        <v>8470373</v>
       </c>
       <c r="L27" s="92">
         <f t="shared" si="3"/>
@@ -8843,15 +9940,15 @@
       </c>
       <c r="M27" s="90">
         <f>F27/E27</f>
-        <v>1.8288404879368267</v>
+        <v>1.8009260839773766</v>
       </c>
       <c r="N27" s="90">
         <f>F27/K27</f>
-        <v>0.37170907533133218</v>
+        <v>0.36162881256823048</v>
       </c>
       <c r="O27" s="90">
         <f>F27/B27</f>
-        <v>0.3573522849426144</v>
+        <v>0.3471858609472952</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="90" customFormat="1">
